--- a/FinModel_Summary.xlsx
+++ b/FinModel_Summary.xlsx
@@ -7,13 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GATP_Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rates" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOR_Conditions" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historical_CF" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GATP_Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GATP_Composition" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rates" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOR_Conditions" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historical_CF" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,12 +24,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="+0.0000;-0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="44">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -129,8 +132,113 @@
     <font>
       <color rgb="00833C0B"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00CFE3F2"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0052514E"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E7B4F"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="0052514E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="0052514E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F3A5F"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000B0B0B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E7B4F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E7B4F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F3A5F"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="0052514E"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000B0B0B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E7B4F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F3A5F"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="22">
     <fill>
       <patternFill/>
     </fill>
@@ -182,8 +290,74 @@
         <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3A5F"/>
+        <bgColor rgb="001F3A5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F2EA"/>
+        <bgColor rgb="00E3F2EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E7B4F"/>
+        <bgColor rgb="001E7B4F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002A7F8E"/>
+        <bgColor rgb="002A7F8E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6F0FB"/>
+        <bgColor rgb="00E6F0FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C9DDF5"/>
+        <bgColor rgb="00C9DDF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDEDE5"/>
+        <bgColor rgb="00FDEDE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9D2C0"/>
+        <bgColor rgb="00F9D2C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDF1DC"/>
+        <bgColor rgb="00FDF1DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F4F7"/>
+        <bgColor rgb="00F2F4F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -238,11 +412,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D5D9DF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D5D9DF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D5D9DF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D5D9DF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -401,6 +589,81 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="11" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="33" fillId="15" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="34" fillId="16" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="33" fillId="17" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="34" fillId="18" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="35" fillId="12" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="33" fillId="19" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="33" fillId="20" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="36" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="15" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="15" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="17" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="17" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="19" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="19" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="42" fillId="12" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="41" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="38" fillId="20" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="21" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -477,6 +740,272 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Fin42: GATP = CRF + OM (PhP/kWh)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'GATP_Summary'!J5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="2A78D6"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="FCFCFB"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'GATP_Summary'!$A$6:$A$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'GATP_Summary'!$J$6:$J$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'GATP_Summary'!M5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="EB6834"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="FCFCFB"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'GATP_Summary'!$A$6:$A$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'GATP_Summary'!$M$6:$M$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>PhP/kWh</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Fin90: GATP = CRF + OM (PhP/kWh)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'GATP_Summary'!J19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="2A78D6"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="FCFCFB"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'GATP_Summary'!$A$20:$A$30</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'GATP_Summary'!$J$20:$J$30</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'GATP_Summary'!M19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="EB6834"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="FCFCFB"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'GATP_Summary'!$A$20:$A$30</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'GATP_Summary'!$M$20:$M$30</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>PhP/kWh</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
@@ -8799,529 +9328,529 @@
 Source: Tariff Breakdown A9 x PhP/US$.</t>
       </text>
     </comment>
-    <comment ref="F77" authorId="0" shapeId="0">
+    <comment ref="F78" authorId="0" shapeId="0">
       <text>
         <t>Equity IRR — Fin42, Lot 1 Existing CCGT - Luzon
 Source: Equals Re when solved.</t>
       </text>
     </comment>
-    <comment ref="G77" authorId="0" shapeId="0">
+    <comment ref="G78" authorId="0" shapeId="0">
       <text>
         <t>Equity IRR — Fin42, Lot 2 Existing CCGT - Luzon
 Source: Equals Re when solved.</t>
       </text>
     </comment>
-    <comment ref="H77" authorId="0" shapeId="0">
+    <comment ref="H78" authorId="0" shapeId="0">
       <text>
         <t>Equity IRR — Fin42, New-Build CCGT - Luzon 1000MW
 Source: Equals Re when solved.</t>
       </text>
     </comment>
-    <comment ref="I77" authorId="0" shapeId="0">
+    <comment ref="I78" authorId="0" shapeId="0">
       <text>
         <t>Equity IRR — Fin42, New-Build OCGT - Luzon 1000MW
 Source: Equals Re when solved.</t>
       </text>
     </comment>
-    <comment ref="J77" authorId="0" shapeId="0">
+    <comment ref="J78" authorId="0" shapeId="0">
       <text>
         <t>Equity IRR — Fin42, New-Build Gas Engine - Luzon 1000MW
 Source: Equals Re when solved.</t>
       </text>
     </comment>
-    <comment ref="K77" authorId="0" shapeId="0">
+    <comment ref="K78" authorId="0" shapeId="0">
       <text>
         <t>Equity IRR — Fin42, New-Build CCGT - Visayas 440MW
 Source: Equals Re when solved.</t>
       </text>
     </comment>
-    <comment ref="L77" authorId="0" shapeId="0">
+    <comment ref="L78" authorId="0" shapeId="0">
       <text>
         <t>Equity IRR — Fin42, New-Build OCGT - Visayas 440MW
 Source: Equals Re when solved.</t>
       </text>
     </comment>
-    <comment ref="M77" authorId="0" shapeId="0">
+    <comment ref="M78" authorId="0" shapeId="0">
       <text>
         <t>Equity IRR — Fin42, New-Build Gas Engine - Visayas 440MW
 Source: Equals Re when solved.</t>
       </text>
     </comment>
-    <comment ref="N77" authorId="0" shapeId="0">
+    <comment ref="N78" authorId="0" shapeId="0">
       <text>
         <t>Equity IRR — Fin42, New-Build CCGT - Visayas 500MW
 Source: Equals Re when solved.</t>
       </text>
     </comment>
-    <comment ref="O77" authorId="0" shapeId="0">
+    <comment ref="O78" authorId="0" shapeId="0">
       <text>
         <t>Equity IRR — Fin42, New-Build OCGT - Visayas 500MW
 Source: Equals Re when solved.</t>
       </text>
     </comment>
-    <comment ref="P77" authorId="0" shapeId="0">
+    <comment ref="P78" authorId="0" shapeId="0">
       <text>
         <t>Equity IRR — Fin42, New-Build Gas Engine - Visayas 500MW
 Source: Equals Re when solved.</t>
       </text>
     </comment>
-    <comment ref="Q77" authorId="0" shapeId="0">
+    <comment ref="Q78" authorId="0" shapeId="0">
       <text>
         <t>Equity IRR — Fin90, Lot 1 Existing CCGT - Luzon
 Source: Equals Re when solved.</t>
       </text>
     </comment>
-    <comment ref="R77" authorId="0" shapeId="0">
+    <comment ref="R78" authorId="0" shapeId="0">
       <text>
         <t>Equity IRR — Fin90, Lot 2 Existing CCGT - Luzon
 Source: Equals Re when solved.</t>
       </text>
     </comment>
-    <comment ref="S77" authorId="0" shapeId="0">
+    <comment ref="S78" authorId="0" shapeId="0">
       <text>
         <t>Equity IRR — Fin90, New-Build CCGT - Luzon 1000MW
 Source: Equals Re when solved.</t>
       </text>
     </comment>
-    <comment ref="T77" authorId="0" shapeId="0">
+    <comment ref="T78" authorId="0" shapeId="0">
       <text>
         <t>Equity IRR — Fin90, New-Build OCGT - Luzon 1000MW
 Source: Equals Re when solved.</t>
       </text>
     </comment>
-    <comment ref="U77" authorId="0" shapeId="0">
+    <comment ref="U78" authorId="0" shapeId="0">
       <text>
         <t>Equity IRR — Fin90, New-Build Gas Engine - Luzon 1000MW
 Source: Equals Re when solved.</t>
       </text>
     </comment>
-    <comment ref="V77" authorId="0" shapeId="0">
+    <comment ref="V78" authorId="0" shapeId="0">
       <text>
         <t>Equity IRR — Fin90, New-Build CCGT - Visayas 440MW
 Source: Equals Re when solved.</t>
       </text>
     </comment>
-    <comment ref="W77" authorId="0" shapeId="0">
+    <comment ref="W78" authorId="0" shapeId="0">
       <text>
         <t>Equity IRR — Fin90, New-Build OCGT - Visayas 440MW
 Source: Equals Re when solved.</t>
       </text>
     </comment>
-    <comment ref="X77" authorId="0" shapeId="0">
+    <comment ref="X78" authorId="0" shapeId="0">
       <text>
         <t>Equity IRR — Fin90, New-Build Gas Engine - Visayas 440MW
 Source: Equals Re when solved.</t>
       </text>
     </comment>
-    <comment ref="Y77" authorId="0" shapeId="0">
+    <comment ref="Y78" authorId="0" shapeId="0">
       <text>
         <t>Equity IRR — Fin90, New-Build CCGT - Visayas 500MW
 Source: Equals Re when solved.</t>
       </text>
     </comment>
-    <comment ref="Z77" authorId="0" shapeId="0">
+    <comment ref="Z78" authorId="0" shapeId="0">
       <text>
         <t>Equity IRR — Fin90, New-Build OCGT - Visayas 500MW
 Source: Equals Re when solved.</t>
       </text>
     </comment>
-    <comment ref="AA77" authorId="0" shapeId="0">
+    <comment ref="AA78" authorId="0" shapeId="0">
       <text>
         <t>Equity IRR — Fin90, New-Build Gas Engine - Visayas 500MW
 Source: Equals Re when solved.</t>
       </text>
     </comment>
-    <comment ref="F78" authorId="0" shapeId="0">
+    <comment ref="F79" authorId="0" shapeId="0">
       <text>
         <t>Project IRR — Fin42, Lot 1 Existing CCGT - Luzon
 Source: Model result.</t>
       </text>
     </comment>
-    <comment ref="G78" authorId="0" shapeId="0">
+    <comment ref="G79" authorId="0" shapeId="0">
       <text>
         <t>Project IRR — Fin42, Lot 2 Existing CCGT - Luzon
 Source: Model result.</t>
       </text>
     </comment>
-    <comment ref="H78" authorId="0" shapeId="0">
+    <comment ref="H79" authorId="0" shapeId="0">
       <text>
         <t>Project IRR — Fin42, New-Build CCGT - Luzon 1000MW
 Source: Model result.</t>
       </text>
     </comment>
-    <comment ref="I78" authorId="0" shapeId="0">
+    <comment ref="I79" authorId="0" shapeId="0">
       <text>
         <t>Project IRR — Fin42, New-Build OCGT - Luzon 1000MW
 Source: Model result.</t>
       </text>
     </comment>
-    <comment ref="J78" authorId="0" shapeId="0">
+    <comment ref="J79" authorId="0" shapeId="0">
       <text>
         <t>Project IRR — Fin42, New-Build Gas Engine - Luzon 1000MW
 Source: Model result.</t>
       </text>
     </comment>
-    <comment ref="K78" authorId="0" shapeId="0">
+    <comment ref="K79" authorId="0" shapeId="0">
       <text>
         <t>Project IRR — Fin42, New-Build CCGT - Visayas 440MW
 Source: Model result.</t>
       </text>
     </comment>
-    <comment ref="L78" authorId="0" shapeId="0">
+    <comment ref="L79" authorId="0" shapeId="0">
       <text>
         <t>Project IRR — Fin42, New-Build OCGT - Visayas 440MW
 Source: Model result.</t>
       </text>
     </comment>
-    <comment ref="M78" authorId="0" shapeId="0">
+    <comment ref="M79" authorId="0" shapeId="0">
       <text>
         <t>Project IRR — Fin42, New-Build Gas Engine - Visayas 440MW
 Source: Model result.</t>
       </text>
     </comment>
-    <comment ref="N78" authorId="0" shapeId="0">
+    <comment ref="N79" authorId="0" shapeId="0">
       <text>
         <t>Project IRR — Fin42, New-Build CCGT - Visayas 500MW
 Source: Model result.</t>
       </text>
     </comment>
-    <comment ref="O78" authorId="0" shapeId="0">
+    <comment ref="O79" authorId="0" shapeId="0">
       <text>
         <t>Project IRR — Fin42, New-Build OCGT - Visayas 500MW
 Source: Model result.</t>
       </text>
     </comment>
-    <comment ref="P78" authorId="0" shapeId="0">
+    <comment ref="P79" authorId="0" shapeId="0">
       <text>
         <t>Project IRR — Fin42, New-Build Gas Engine - Visayas 500MW
 Source: Model result.</t>
       </text>
     </comment>
-    <comment ref="Q78" authorId="0" shapeId="0">
+    <comment ref="Q79" authorId="0" shapeId="0">
       <text>
         <t>Project IRR — Fin90, Lot 1 Existing CCGT - Luzon
 Source: Model result.</t>
       </text>
     </comment>
-    <comment ref="R78" authorId="0" shapeId="0">
+    <comment ref="R79" authorId="0" shapeId="0">
       <text>
         <t>Project IRR — Fin90, Lot 2 Existing CCGT - Luzon
 Source: Model result.</t>
       </text>
     </comment>
-    <comment ref="S78" authorId="0" shapeId="0">
+    <comment ref="S79" authorId="0" shapeId="0">
       <text>
         <t>Project IRR — Fin90, New-Build CCGT - Luzon 1000MW
 Source: Model result.</t>
       </text>
     </comment>
-    <comment ref="T78" authorId="0" shapeId="0">
+    <comment ref="T79" authorId="0" shapeId="0">
       <text>
         <t>Project IRR — Fin90, New-Build OCGT - Luzon 1000MW
 Source: Model result.</t>
       </text>
     </comment>
-    <comment ref="U78" authorId="0" shapeId="0">
+    <comment ref="U79" authorId="0" shapeId="0">
       <text>
         <t>Project IRR — Fin90, New-Build Gas Engine - Luzon 1000MW
 Source: Model result.</t>
       </text>
     </comment>
-    <comment ref="V78" authorId="0" shapeId="0">
+    <comment ref="V79" authorId="0" shapeId="0">
       <text>
         <t>Project IRR — Fin90, New-Build CCGT - Visayas 440MW
 Source: Model result.</t>
       </text>
     </comment>
-    <comment ref="W78" authorId="0" shapeId="0">
+    <comment ref="W79" authorId="0" shapeId="0">
       <text>
         <t>Project IRR — Fin90, New-Build OCGT - Visayas 440MW
 Source: Model result.</t>
       </text>
     </comment>
-    <comment ref="X78" authorId="0" shapeId="0">
+    <comment ref="X79" authorId="0" shapeId="0">
       <text>
         <t>Project IRR — Fin90, New-Build Gas Engine - Visayas 440MW
 Source: Model result.</t>
       </text>
     </comment>
-    <comment ref="Y78" authorId="0" shapeId="0">
+    <comment ref="Y79" authorId="0" shapeId="0">
       <text>
         <t>Project IRR — Fin90, New-Build CCGT - Visayas 500MW
 Source: Model result.</t>
       </text>
     </comment>
-    <comment ref="Z78" authorId="0" shapeId="0">
+    <comment ref="Z79" authorId="0" shapeId="0">
       <text>
         <t>Project IRR — Fin90, New-Build OCGT - Visayas 500MW
 Source: Model result.</t>
       </text>
     </comment>
-    <comment ref="AA78" authorId="0" shapeId="0">
+    <comment ref="AA79" authorId="0" shapeId="0">
       <text>
         <t>Project IRR — Fin90, New-Build Gas Engine - Visayas 500MW
 Source: Model result.</t>
       </text>
     </comment>
-    <comment ref="F79" authorId="0" shapeId="0">
+    <comment ref="F80" authorId="0" shapeId="0">
       <text>
         <t>First-year energy — Fin42, Lot 1 Existing CCGT - Luzon
 Source: Installed MW x CF x 8,760.</t>
       </text>
     </comment>
-    <comment ref="G79" authorId="0" shapeId="0">
+    <comment ref="G80" authorId="0" shapeId="0">
       <text>
         <t>First-year energy — Fin42, Lot 2 Existing CCGT - Luzon
 Source: Installed MW x CF x 8,760.</t>
       </text>
     </comment>
-    <comment ref="H79" authorId="0" shapeId="0">
+    <comment ref="H80" authorId="0" shapeId="0">
       <text>
         <t>First-year energy — Fin42, New-Build CCGT - Luzon 1000MW
 Source: Installed MW x CF x 8,760.</t>
       </text>
     </comment>
-    <comment ref="I79" authorId="0" shapeId="0">
+    <comment ref="I80" authorId="0" shapeId="0">
       <text>
         <t>First-year energy — Fin42, New-Build OCGT - Luzon 1000MW
 Source: Installed MW x CF x 8,760.</t>
       </text>
     </comment>
-    <comment ref="J79" authorId="0" shapeId="0">
+    <comment ref="J80" authorId="0" shapeId="0">
       <text>
         <t>First-year energy — Fin42, New-Build Gas Engine - Luzon 1000MW
 Source: Installed MW x CF x 8,760.</t>
       </text>
     </comment>
-    <comment ref="K79" authorId="0" shapeId="0">
+    <comment ref="K80" authorId="0" shapeId="0">
       <text>
         <t>First-year energy — Fin42, New-Build CCGT - Visayas 440MW
 Source: Installed MW x CF x 8,760.</t>
       </text>
     </comment>
-    <comment ref="L79" authorId="0" shapeId="0">
+    <comment ref="L80" authorId="0" shapeId="0">
       <text>
         <t>First-year energy — Fin42, New-Build OCGT - Visayas 440MW
 Source: Installed MW x CF x 8,760.</t>
       </text>
     </comment>
-    <comment ref="M79" authorId="0" shapeId="0">
+    <comment ref="M80" authorId="0" shapeId="0">
       <text>
         <t>First-year energy — Fin42, New-Build Gas Engine - Visayas 440MW
 Source: Installed MW x CF x 8,760.</t>
       </text>
     </comment>
-    <comment ref="N79" authorId="0" shapeId="0">
+    <comment ref="N80" authorId="0" shapeId="0">
       <text>
         <t>First-year energy — Fin42, New-Build CCGT - Visayas 500MW
 Source: Installed MW x CF x 8,760.</t>
       </text>
     </comment>
-    <comment ref="O79" authorId="0" shapeId="0">
+    <comment ref="O80" authorId="0" shapeId="0">
       <text>
         <t>First-year energy — Fin42, New-Build OCGT - Visayas 500MW
 Source: Installed MW x CF x 8,760.</t>
       </text>
     </comment>
-    <comment ref="P79" authorId="0" shapeId="0">
+    <comment ref="P80" authorId="0" shapeId="0">
       <text>
         <t>First-year energy — Fin42, New-Build Gas Engine - Visayas 500MW
 Source: Installed MW x CF x 8,760.</t>
       </text>
     </comment>
-    <comment ref="Q79" authorId="0" shapeId="0">
+    <comment ref="Q80" authorId="0" shapeId="0">
       <text>
         <t>First-year energy — Fin90, Lot 1 Existing CCGT - Luzon
 Source: Installed MW x CF x 8,760.</t>
       </text>
     </comment>
-    <comment ref="R79" authorId="0" shapeId="0">
+    <comment ref="R80" authorId="0" shapeId="0">
       <text>
         <t>First-year energy — Fin90, Lot 2 Existing CCGT - Luzon
 Source: Installed MW x CF x 8,760.</t>
       </text>
     </comment>
-    <comment ref="S79" authorId="0" shapeId="0">
+    <comment ref="S80" authorId="0" shapeId="0">
       <text>
         <t>First-year energy — Fin90, New-Build CCGT - Luzon 1000MW
 Source: Installed MW x CF x 8,760.</t>
       </text>
     </comment>
-    <comment ref="T79" authorId="0" shapeId="0">
+    <comment ref="T80" authorId="0" shapeId="0">
       <text>
         <t>First-year energy — Fin90, New-Build OCGT - Luzon 1000MW
 Source: Installed MW x CF x 8,760.</t>
       </text>
     </comment>
-    <comment ref="U79" authorId="0" shapeId="0">
+    <comment ref="U80" authorId="0" shapeId="0">
       <text>
         <t>First-year energy — Fin90, New-Build Gas Engine - Luzon 1000MW
 Source: Installed MW x CF x 8,760.</t>
       </text>
     </comment>
-    <comment ref="V79" authorId="0" shapeId="0">
+    <comment ref="V80" authorId="0" shapeId="0">
       <text>
         <t>First-year energy — Fin90, New-Build CCGT - Visayas 440MW
 Source: Installed MW x CF x 8,760.</t>
       </text>
     </comment>
-    <comment ref="W79" authorId="0" shapeId="0">
+    <comment ref="W80" authorId="0" shapeId="0">
       <text>
         <t>First-year energy — Fin90, New-Build OCGT - Visayas 440MW
 Source: Installed MW x CF x 8,760.</t>
       </text>
     </comment>
-    <comment ref="X79" authorId="0" shapeId="0">
+    <comment ref="X80" authorId="0" shapeId="0">
       <text>
         <t>First-year energy — Fin90, New-Build Gas Engine - Visayas 440MW
 Source: Installed MW x CF x 8,760.</t>
       </text>
     </comment>
-    <comment ref="Y79" authorId="0" shapeId="0">
+    <comment ref="Y80" authorId="0" shapeId="0">
       <text>
         <t>First-year energy — Fin90, New-Build CCGT - Visayas 500MW
 Source: Installed MW x CF x 8,760.</t>
       </text>
     </comment>
-    <comment ref="Z79" authorId="0" shapeId="0">
+    <comment ref="Z80" authorId="0" shapeId="0">
       <text>
         <t>First-year energy — Fin90, New-Build OCGT - Visayas 500MW
 Source: Installed MW x CF x 8,760.</t>
       </text>
     </comment>
-    <comment ref="AA79" authorId="0" shapeId="0">
+    <comment ref="AA80" authorId="0" shapeId="0">
       <text>
         <t>First-year energy — Fin90, New-Build Gas Engine - Visayas 500MW
 Source: Installed MW x CF x 8,760.</t>
       </text>
     </comment>
-    <comment ref="F80" authorId="0" shapeId="0">
+    <comment ref="F81" authorId="0" shapeId="0">
       <text>
         <t>Model file — Fin42, Lot 1 Existing CCGT - Luzon
 Source: File in FinModel/Fin42/ (password yolo).</t>
       </text>
     </comment>
-    <comment ref="G80" authorId="0" shapeId="0">
+    <comment ref="G81" authorId="0" shapeId="0">
       <text>
         <t>Model file — Fin42, Lot 2 Existing CCGT - Luzon
 Source: File in FinModel/Fin42/ (password yolo).</t>
       </text>
     </comment>
-    <comment ref="H80" authorId="0" shapeId="0">
+    <comment ref="H81" authorId="0" shapeId="0">
       <text>
         <t>Model file — Fin42, New-Build CCGT - Luzon 1000MW
 Source: File in FinModel/Fin42/ (password yolo).</t>
       </text>
     </comment>
-    <comment ref="I80" authorId="0" shapeId="0">
+    <comment ref="I81" authorId="0" shapeId="0">
       <text>
         <t>Model file — Fin42, New-Build OCGT - Luzon 1000MW
 Source: File in FinModel/Fin42/ (password yolo).</t>
       </text>
     </comment>
-    <comment ref="J80" authorId="0" shapeId="0">
+    <comment ref="J81" authorId="0" shapeId="0">
       <text>
         <t>Model file — Fin42, New-Build Gas Engine - Luzon 1000MW
 Source: File in FinModel/Fin42/ (password yolo).</t>
       </text>
     </comment>
-    <comment ref="K80" authorId="0" shapeId="0">
+    <comment ref="K81" authorId="0" shapeId="0">
       <text>
         <t>Model file — Fin42, New-Build CCGT - Visayas 440MW
 Source: File in FinModel/Fin42/ (password yolo).</t>
       </text>
     </comment>
-    <comment ref="L80" authorId="0" shapeId="0">
+    <comment ref="L81" authorId="0" shapeId="0">
       <text>
         <t>Model file — Fin42, New-Build OCGT - Visayas 440MW
 Source: File in FinModel/Fin42/ (password yolo).</t>
       </text>
     </comment>
-    <comment ref="M80" authorId="0" shapeId="0">
+    <comment ref="M81" authorId="0" shapeId="0">
       <text>
         <t>Model file — Fin42, New-Build Gas Engine - Visayas 440MW
 Source: File in FinModel/Fin42/ (password yolo).</t>
       </text>
     </comment>
-    <comment ref="N80" authorId="0" shapeId="0">
+    <comment ref="N81" authorId="0" shapeId="0">
       <text>
         <t>Model file — Fin42, New-Build CCGT - Visayas 500MW
 Source: File in FinModel/Fin42/ (password yolo).</t>
       </text>
     </comment>
-    <comment ref="O80" authorId="0" shapeId="0">
+    <comment ref="O81" authorId="0" shapeId="0">
       <text>
         <t>Model file — Fin42, New-Build OCGT - Visayas 500MW
 Source: File in FinModel/Fin42/ (password yolo).</t>
       </text>
     </comment>
-    <comment ref="P80" authorId="0" shapeId="0">
+    <comment ref="P81" authorId="0" shapeId="0">
       <text>
         <t>Model file — Fin42, New-Build Gas Engine - Visayas 500MW
 Source: File in FinModel/Fin42/ (password yolo).</t>
       </text>
     </comment>
-    <comment ref="Q80" authorId="0" shapeId="0">
+    <comment ref="Q81" authorId="0" shapeId="0">
       <text>
         <t>Model file — Fin90, Lot 1 Existing CCGT - Luzon
 Source: File in FinModel/Fin90/ (password yolo).</t>
       </text>
     </comment>
-    <comment ref="R80" authorId="0" shapeId="0">
+    <comment ref="R81" authorId="0" shapeId="0">
       <text>
         <t>Model file — Fin90, Lot 2 Existing CCGT - Luzon
 Source: File in FinModel/Fin90/ (password yolo).</t>
       </text>
     </comment>
-    <comment ref="S80" authorId="0" shapeId="0">
+    <comment ref="S81" authorId="0" shapeId="0">
       <text>
         <t>Model file — Fin90, New-Build CCGT - Luzon 1000MW
 Source: File in FinModel/Fin90/ (password yolo).</t>
       </text>
     </comment>
-    <comment ref="T80" authorId="0" shapeId="0">
+    <comment ref="T81" authorId="0" shapeId="0">
       <text>
         <t>Model file — Fin90, New-Build OCGT - Luzon 1000MW
 Source: File in FinModel/Fin90/ (password yolo).</t>
       </text>
     </comment>
-    <comment ref="U80" authorId="0" shapeId="0">
+    <comment ref="U81" authorId="0" shapeId="0">
       <text>
         <t>Model file — Fin90, New-Build Gas Engine - Luzon 1000MW
 Source: File in FinModel/Fin90/ (password yolo).</t>
       </text>
     </comment>
-    <comment ref="V80" authorId="0" shapeId="0">
+    <comment ref="V81" authorId="0" shapeId="0">
       <text>
         <t>Model file — Fin90, New-Build CCGT - Visayas 440MW
 Source: File in FinModel/Fin90/ (password yolo).</t>
       </text>
     </comment>
-    <comment ref="W80" authorId="0" shapeId="0">
+    <comment ref="W81" authorId="0" shapeId="0">
       <text>
         <t>Model file — Fin90, New-Build OCGT - Visayas 440MW
 Source: File in FinModel/Fin90/ (password yolo).</t>
       </text>
     </comment>
-    <comment ref="X80" authorId="0" shapeId="0">
+    <comment ref="X81" authorId="0" shapeId="0">
       <text>
         <t>Model file — Fin90, New-Build Gas Engine - Visayas 440MW
 Source: File in FinModel/Fin90/ (password yolo).</t>
       </text>
     </comment>
-    <comment ref="Y80" authorId="0" shapeId="0">
+    <comment ref="Y81" authorId="0" shapeId="0">
       <text>
         <t>Model file — Fin90, New-Build CCGT - Visayas 500MW
 Source: File in FinModel/Fin90/ (password yolo).</t>
       </text>
     </comment>
-    <comment ref="Z80" authorId="0" shapeId="0">
+    <comment ref="Z81" authorId="0" shapeId="0">
       <text>
         <t>Model file — Fin90, New-Build OCGT - Visayas 500MW
 Source: File in FinModel/Fin90/ (password yolo).</t>
       </text>
     </comment>
-    <comment ref="AA80" authorId="0" shapeId="0">
+    <comment ref="AA81" authorId="0" shapeId="0">
       <text>
         <t>Model file — Fin90, New-Build Gas Engine - Visayas 500MW
 Source: File in FinModel/Fin90/ (password yolo).</t>
@@ -9329,6 +9858,110 @@
     </comment>
   </commentList>
 </comments>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9906000" cy="4724400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>35</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9906000" cy="4114800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>18</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="3420000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>18</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="3420000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9620,790 +10253,2916 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:P59"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="68" t="inlineStr">
+        <is>
+          <t>GAT Price (GATP) dashboard – Mid-Merit Natural Gas Capacity Auction</t>
+        </is>
+      </c>
+      <c r="B1" s="69" t="n"/>
+      <c r="C1" s="69" t="n"/>
+      <c r="D1" s="69" t="n"/>
+      <c r="E1" s="69" t="n"/>
+      <c r="F1" s="69" t="n"/>
+      <c r="G1" s="69" t="n"/>
+      <c r="H1" s="69" t="n"/>
+      <c r="I1" s="69" t="n"/>
+      <c r="J1" s="69" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="70" t="inlineStr">
+        <is>
+          <t>Decision of 19 Oct 2026 (GAIR Sec. 8.6): GATP = CRF + OM. The Capped Landed Logistics Cost (CLLC) is paid through the Fuel Cost, not the GATP. PhP/kWh, excluding fuel.</t>
+        </is>
+      </c>
+      <c r="B2" s="69" t="n"/>
+      <c r="C2" s="69" t="n"/>
+      <c r="D2" s="69" t="n"/>
+      <c r="E2" s="69" t="n"/>
+      <c r="F2" s="69" t="n"/>
+      <c r="G2" s="69" t="n"/>
+      <c r="H2" s="69" t="n"/>
+      <c r="I2" s="69" t="n"/>
+      <c r="J2" s="69" t="n"/>
+      <c r="K2" s="69" t="n"/>
+      <c r="L2" s="69" t="n"/>
+      <c r="M2" s="69" t="n"/>
+      <c r="N2" s="69" t="n"/>
+      <c r="O2" s="69" t="n"/>
+      <c r="P2" s="69" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="71" t="inlineStr">
+        <is>
+          <t>Existing CCGT (Lots 1–2)</t>
+        </is>
+      </c>
+      <c r="C4" s="72" t="n"/>
+      <c r="D4" s="72" t="n"/>
+      <c r="F4" s="71" t="inlineStr">
+        <is>
+          <t>New CCGT</t>
+        </is>
+      </c>
+      <c r="G4" s="72" t="n"/>
+      <c r="H4" s="72" t="n"/>
+      <c r="J4" s="71" t="inlineStr">
+        <is>
+          <t>New OCGT</t>
+        </is>
+      </c>
+      <c r="K4" s="72" t="n"/>
+      <c r="L4" s="72" t="n"/>
+      <c r="N4" s="71" t="inlineStr">
+        <is>
+          <t>New gas engine</t>
+        </is>
+      </c>
+      <c r="O4" s="72" t="n"/>
+      <c r="P4" s="72" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="B5" s="73" t="inlineStr">
+        <is>
+          <t>1.09 – 1.72</t>
+        </is>
+      </c>
+      <c r="C5" s="72" t="n"/>
+      <c r="D5" s="72" t="n"/>
+      <c r="F5" s="73" t="inlineStr">
+        <is>
+          <t>2.04 – 2.99</t>
+        </is>
+      </c>
+      <c r="G5" s="72" t="n"/>
+      <c r="H5" s="72" t="n"/>
+      <c r="J5" s="73" t="inlineStr">
+        <is>
+          <t>1.40 – 1.94</t>
+        </is>
+      </c>
+      <c r="K5" s="72" t="n"/>
+      <c r="L5" s="72" t="n"/>
+      <c r="N5" s="73" t="inlineStr">
+        <is>
+          <t>2.08 – 2.97</t>
+        </is>
+      </c>
+      <c r="O5" s="72" t="n"/>
+      <c r="P5" s="72" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="74" t="inlineStr">
+        <is>
+          <t>PhP/kWh GATP (Fin90 – Fin42)</t>
+        </is>
+      </c>
+      <c r="C6" s="72" t="n"/>
+      <c r="D6" s="72" t="n"/>
+      <c r="F6" s="74" t="inlineStr">
+        <is>
+          <t>PhP/kWh GATP (Fin90 – Fin42)</t>
+        </is>
+      </c>
+      <c r="G6" s="72" t="n"/>
+      <c r="H6" s="72" t="n"/>
+      <c r="J6" s="74" t="inlineStr">
+        <is>
+          <t>PhP/kWh GATP (Fin90 – Fin42)</t>
+        </is>
+      </c>
+      <c r="K6" s="72" t="n"/>
+      <c r="L6" s="72" t="n"/>
+      <c r="N6" s="74" t="inlineStr">
+        <is>
+          <t>PhP/kWh GATP (Fin90 – Fin42)</t>
+        </is>
+      </c>
+      <c r="O6" s="72" t="n"/>
+      <c r="P6" s="72" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="75" t="inlineStr">
+        <is>
+          <t>CRF + OM only</t>
+        </is>
+      </c>
+      <c r="C7" s="76" t="n"/>
+      <c r="D7" s="76" t="n"/>
+      <c r="F7" s="75" t="inlineStr">
+        <is>
+          <t>CRF + OM only</t>
+        </is>
+      </c>
+      <c r="G7" s="76" t="n"/>
+      <c r="H7" s="76" t="n"/>
+      <c r="J7" s="75" t="inlineStr">
+        <is>
+          <t>CRF + OM only</t>
+        </is>
+      </c>
+      <c r="K7" s="76" t="n"/>
+      <c r="L7" s="76" t="n"/>
+      <c r="N7" s="75" t="inlineStr">
+        <is>
+          <t>CRF + OM only</t>
+        </is>
+      </c>
+      <c r="O7" s="76" t="n"/>
+      <c r="P7" s="76" t="n"/>
+    </row>
+    <row r="59">
+      <c r="B59" s="77" t="inlineStr">
+        <is>
+          <t>Lower bound = Fin90 (historical capacity factor); upper bound = Fin42 (TOR 42%). Visayas 440 MW and 500 MW give the same rate (per-kW model). Tables: GATP_Summary.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="68" t="inlineStr">
+        <is>
+          <t>GAT Price build-up by case – PhP/kWh, first year, excluding fuel</t>
+        </is>
+      </c>
+      <c r="B1" s="69" t="n"/>
+      <c r="C1" s="69" t="n"/>
+      <c r="D1" s="69" t="n"/>
+      <c r="E1" s="69" t="n"/>
+      <c r="F1" s="69" t="n"/>
+      <c r="G1" s="69" t="n"/>
+      <c r="H1" s="69" t="n"/>
+      <c r="I1" s="69" t="n"/>
+      <c r="J1" s="69" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="70" t="inlineStr">
+        <is>
+          <t>GATP = CRF + OM (GAIR Sec. 8.6, decision of 19 Oct 2026). CRF = capital recovery + G&amp;A + land lease + local taxes; OM = fixed + variable non-fuel O&amp;M. CLLC moved to the Fuel Cost (Sec. 13.4, 17, 18).</t>
+        </is>
+      </c>
+      <c r="B2" s="69" t="n"/>
+      <c r="C2" s="69" t="n"/>
+      <c r="D2" s="69" t="n"/>
+      <c r="E2" s="69" t="n"/>
+      <c r="F2" s="69" t="n"/>
+      <c r="G2" s="69" t="n"/>
+      <c r="H2" s="69" t="n"/>
+      <c r="I2" s="69" t="n"/>
+      <c r="J2" s="69" t="n"/>
+      <c r="K2" s="69" t="n"/>
+      <c r="L2" s="69" t="n"/>
+      <c r="M2" s="69" t="n"/>
+      <c r="N2" s="69" t="n"/>
+      <c r="O2" s="69" t="n"/>
+      <c r="P2" s="69" t="n"/>
+      <c r="Q2" s="69" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="78" t="inlineStr">
+        <is>
+          <t>Fin42 – TOR capacity factor (42%; Lot 1 adds 24% non-mid-merit energy paid fuel only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="79" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="B5" s="79" t="inlineStr">
+        <is>
+          <t>Grid</t>
+        </is>
+      </c>
+      <c r="C5" s="79" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="D5" s="79" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E5" s="79" t="inlineStr">
+        <is>
+          <t>Capacity factor</t>
+        </is>
+      </c>
+      <c r="F5" s="79" t="inlineStr">
+        <is>
+          <t>Capital recovery</t>
+        </is>
+      </c>
+      <c r="G5" s="79" t="inlineStr">
+        <is>
+          <t>G&amp;A</t>
+        </is>
+      </c>
+      <c r="H5" s="79" t="inlineStr">
+        <is>
+          <t>Land lease</t>
+        </is>
+      </c>
+      <c r="I5" s="79" t="inlineStr">
+        <is>
+          <t>Local taxes, ER 1-94</t>
+        </is>
+      </c>
+      <c r="J5" s="79" t="inlineStr">
+        <is>
+          <t>CRF</t>
+        </is>
+      </c>
+      <c r="K5" s="79" t="inlineStr">
+        <is>
+          <t>Fixed O&amp;M</t>
+        </is>
+      </c>
+      <c r="L5" s="79" t="inlineStr">
+        <is>
+          <t>Variable O&amp;M</t>
+        </is>
+      </c>
+      <c r="M5" s="79" t="inlineStr">
+        <is>
+          <t>OM</t>
+        </is>
+      </c>
+      <c r="N5" s="79" t="inlineStr">
+        <is>
+          <t>GATP = CRF + OM</t>
+        </is>
+      </c>
+      <c r="O5" s="79" t="inlineStr">
+        <is>
+          <t>CLLC → Fuel Cost</t>
+        </is>
+      </c>
+      <c r="P5" s="79" t="inlineStr">
+        <is>
+          <t>Previous GATP (incl. CLLC)</t>
+        </is>
+      </c>
+      <c r="Q5" s="79" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="80" t="inlineStr">
+        <is>
+          <t>Lot 1 Existing CCGT – Luzon 1,400 MW</t>
+        </is>
+      </c>
+      <c r="B6" s="80" t="inlineStr">
+        <is>
+          <t>Luzon</t>
+        </is>
+      </c>
+      <c r="C6" s="80" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D6" s="80" t="inlineStr">
+        <is>
+          <t>Existing CCGT</t>
+        </is>
+      </c>
+      <c r="E6" s="81" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F6" s="82" t="n">
+        <v>1.113210815556322</v>
+      </c>
+      <c r="G6" s="82" t="n">
+        <v>0.04248573913293401</v>
+      </c>
+      <c r="H6" s="82" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I6" s="82" t="n">
+        <v>0.1083414537470184</v>
+      </c>
+      <c r="J6" s="83">
+        <f>SUM(F6:I6)</f>
+        <v/>
+      </c>
+      <c r="K6" s="84" t="n">
+        <v>0.2408352664316718</v>
+      </c>
+      <c r="L6" s="84" t="n">
+        <v>0.2122220862959301</v>
+      </c>
+      <c r="M6" s="85">
+        <f>K6+L6</f>
+        <v/>
+      </c>
+      <c r="N6" s="86">
+        <f>J6+M6</f>
+        <v/>
+      </c>
+      <c r="O6" s="87" t="n">
+        <v>1.216353671233749</v>
+      </c>
+      <c r="P6" s="88" t="n">
+        <v>2.933449032397625</v>
+      </c>
+      <c r="Q6" s="89">
+        <f>IF(ABS(N6-1.7170953612)&lt;0.0001,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="80" t="inlineStr">
+        <is>
+          <t>Lot 2 Existing CCGT – Luzon 500 MW</t>
+        </is>
+      </c>
+      <c r="B7" s="80" t="inlineStr">
+        <is>
+          <t>Luzon</t>
+        </is>
+      </c>
+      <c r="C7" s="80" t="n">
+        <v>500</v>
+      </c>
+      <c r="D7" s="80" t="inlineStr">
+        <is>
+          <t>Existing CCGT</t>
+        </is>
+      </c>
+      <c r="E7" s="81" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F7" s="82" t="n">
+        <v>1.114523660438698</v>
+      </c>
+      <c r="G7" s="82" t="n">
+        <v>0.03800360248121382</v>
+      </c>
+      <c r="H7" s="82" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I7" s="82" t="n">
+        <v>0.1076330035682281</v>
+      </c>
+      <c r="J7" s="83">
+        <f>SUM(F7:I7)</f>
+        <v/>
+      </c>
+      <c r="K7" s="84" t="n">
+        <v>0.2408352664316718</v>
+      </c>
+      <c r="L7" s="84" t="n">
+        <v>0.1383289394592217</v>
+      </c>
+      <c r="M7" s="85">
+        <f>K7+L7</f>
+        <v/>
+      </c>
+      <c r="N7" s="86">
+        <f>J7+M7</f>
+        <v/>
+      </c>
+      <c r="O7" s="87" t="n">
+        <v>0.7740432453305683</v>
+      </c>
+      <c r="P7" s="88" t="n">
+        <v>2.413367717709602</v>
+      </c>
+      <c r="Q7" s="89">
+        <f>IF(ABS(N7-1.6393244724)&lt;0.0001,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="80" t="inlineStr">
+        <is>
+          <t>New CCGT – Luzon 1,000 MW</t>
+        </is>
+      </c>
+      <c r="B8" s="80" t="inlineStr">
+        <is>
+          <t>Luzon</t>
+        </is>
+      </c>
+      <c r="C8" s="80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D8" s="80" t="inlineStr">
+        <is>
+          <t>New CCGT</t>
+        </is>
+      </c>
+      <c r="E8" s="81" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F8" s="82" t="n">
+        <v>2.363809735748692</v>
+      </c>
+      <c r="G8" s="82" t="n">
+        <v>0.05118044000224468</v>
+      </c>
+      <c r="H8" s="82" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I8" s="82" t="n">
+        <v>0.1840119484739745</v>
+      </c>
+      <c r="J8" s="83">
+        <f>SUM(F8:I8)</f>
+        <v/>
+      </c>
+      <c r="K8" s="84" t="n">
+        <v>0.2408352664316718</v>
+      </c>
+      <c r="L8" s="84" t="n">
+        <v>0.1458950043399359</v>
+      </c>
+      <c r="M8" s="85">
+        <f>K8+L8</f>
+        <v/>
+      </c>
+      <c r="N8" s="86">
+        <f>J8+M8</f>
+        <v/>
+      </c>
+      <c r="O8" s="87" t="n">
+        <v>0.7435691018136166</v>
+      </c>
+      <c r="P8" s="88" t="n">
+        <v>3.729301496810136</v>
+      </c>
+      <c r="Q8" s="89">
+        <f>IF(ABS(N8-2.9857323950)&lt;0.0001,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="80" t="inlineStr">
+        <is>
+          <t>New OCGT – Luzon 1,000 MW</t>
+        </is>
+      </c>
+      <c r="B9" s="80" t="inlineStr">
+        <is>
+          <t>Luzon</t>
+        </is>
+      </c>
+      <c r="C9" s="80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D9" s="80" t="inlineStr">
+        <is>
+          <t>New OCGT</t>
+        </is>
+      </c>
+      <c r="E9" s="81" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F9" s="82" t="n">
+        <v>1.323451656678538</v>
+      </c>
+      <c r="G9" s="82" t="n">
+        <v>0.04364718529565494</v>
+      </c>
+      <c r="H9" s="82" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I9" s="82" t="n">
+        <v>0.1207425412735327</v>
+      </c>
+      <c r="J9" s="83">
+        <f>SUM(F9:I9)</f>
+        <v/>
+      </c>
+      <c r="K9" s="84" t="n">
+        <v>0.149314351908768</v>
+      </c>
+      <c r="L9" s="84" t="n">
+        <v>0.3007323832473738</v>
+      </c>
+      <c r="M9" s="85">
+        <f>K9+L9</f>
+        <v/>
+      </c>
+      <c r="N9" s="86">
+        <f>J9+M9</f>
+        <v/>
+      </c>
+      <c r="O9" s="87" t="n">
+        <v>1.194586425864496</v>
+      </c>
+      <c r="P9" s="88" t="n">
+        <v>3.132474544268364</v>
+      </c>
+      <c r="Q9" s="89">
+        <f>IF(ABS(N9-1.9378881184)&lt;0.0001,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="80" t="inlineStr">
+        <is>
+          <t>New gas engine – Luzon 1,000 MW</t>
+        </is>
+      </c>
+      <c r="B10" s="80" t="inlineStr">
+        <is>
+          <t>Luzon</t>
+        </is>
+      </c>
+      <c r="C10" s="80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D10" s="80" t="inlineStr">
+        <is>
+          <t>New gas engine</t>
+        </is>
+      </c>
+      <c r="E10" s="81" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F10" s="82" t="n">
+        <v>2.18615083302484</v>
+      </c>
+      <c r="G10" s="82" t="n">
+        <v>0.06074783022409633</v>
+      </c>
+      <c r="H10" s="82" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I10" s="82" t="n">
+        <v>0.1761848201028166</v>
+      </c>
+      <c r="J10" s="83">
+        <f>SUM(F10:I10)</f>
+        <v/>
+      </c>
+      <c r="K10" s="84" t="n">
+        <v>0.2898455066464321</v>
+      </c>
+      <c r="L10" s="84" t="n">
+        <v>0.262026667571982</v>
+      </c>
+      <c r="M10" s="85">
+        <f>K10+L10</f>
+        <v/>
+      </c>
+      <c r="N10" s="86">
+        <f>J10+M10</f>
+        <v/>
+      </c>
+      <c r="O10" s="87" t="n">
+        <v>0.9751725925424473</v>
+      </c>
+      <c r="P10" s="88" t="n">
+        <v>3.950128250112614</v>
+      </c>
+      <c r="Q10" s="89">
+        <f>IF(ABS(N10-2.9749556576)&lt;0.0001,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="80" t="inlineStr">
+        <is>
+          <t>New CCGT – Visayas 440 MW</t>
+        </is>
+      </c>
+      <c r="B11" s="80" t="inlineStr">
+        <is>
+          <t>Visayas</t>
+        </is>
+      </c>
+      <c r="C11" s="80" t="n">
+        <v>440</v>
+      </c>
+      <c r="D11" s="80" t="inlineStr">
+        <is>
+          <t>New CCGT</t>
+        </is>
+      </c>
+      <c r="E11" s="81" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F11" s="82" t="n">
+        <v>2.363790590846974</v>
+      </c>
+      <c r="G11" s="82" t="n">
+        <v>0.05113090469063662</v>
+      </c>
+      <c r="H11" s="82" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I11" s="82" t="n">
+        <v>0.1840548919626424</v>
+      </c>
+      <c r="J11" s="83">
+        <f>SUM(F11:I11)</f>
+        <v/>
+      </c>
+      <c r="K11" s="84" t="n">
+        <v>0.2408352664316718</v>
+      </c>
+      <c r="L11" s="84" t="n">
+        <v>0.1458655087382131</v>
+      </c>
+      <c r="M11" s="85">
+        <f>K11+L11</f>
+        <v/>
+      </c>
+      <c r="N11" s="86">
+        <f>J11+M11</f>
+        <v/>
+      </c>
+      <c r="O11" s="87" t="n">
+        <v>1.232759300375205</v>
+      </c>
+      <c r="P11" s="88" t="n">
+        <v>4.218436463045343</v>
+      </c>
+      <c r="Q11" s="89">
+        <f>IF(ABS(N11-2.9856771627)&lt;0.0001,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="80" t="inlineStr">
+        <is>
+          <t>New OCGT – Visayas 440 MW</t>
+        </is>
+      </c>
+      <c r="B12" s="80" t="inlineStr">
+        <is>
+          <t>Visayas</t>
+        </is>
+      </c>
+      <c r="C12" s="80" t="n">
+        <v>440</v>
+      </c>
+      <c r="D12" s="80" t="inlineStr">
+        <is>
+          <t>New OCGT</t>
+        </is>
+      </c>
+      <c r="E12" s="81" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F12" s="82" t="n">
+        <v>1.323434963816624</v>
+      </c>
+      <c r="G12" s="82" t="n">
+        <v>0.04359754819458617</v>
+      </c>
+      <c r="H12" s="82" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I12" s="82" t="n">
+        <v>0.1207855703377174</v>
+      </c>
+      <c r="J12" s="83">
+        <f>SUM(F12:I12)</f>
+        <v/>
+      </c>
+      <c r="K12" s="84" t="n">
+        <v>0.149314351908768</v>
+      </c>
+      <c r="L12" s="84" t="n">
+        <v>0.300702829205132</v>
+      </c>
+      <c r="M12" s="85">
+        <f>K12+L12</f>
+        <v/>
+      </c>
+      <c r="N12" s="86">
+        <f>J12+M12</f>
+        <v/>
+      </c>
+      <c r="O12" s="87" t="n">
+        <v>1.980498548143772</v>
+      </c>
+      <c r="P12" s="88" t="n">
+        <v>3.9183338116066</v>
+      </c>
+      <c r="Q12" s="89">
+        <f>IF(ABS(N12-1.9378352635)&lt;0.0001,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="80" t="inlineStr">
+        <is>
+          <t>New gas engine – Visayas 440 MW</t>
+        </is>
+      </c>
+      <c r="B13" s="80" t="inlineStr">
+        <is>
+          <t>Visayas</t>
+        </is>
+      </c>
+      <c r="C13" s="80" t="n">
+        <v>440</v>
+      </c>
+      <c r="D13" s="80" t="inlineStr">
+        <is>
+          <t>New gas engine</t>
+        </is>
+      </c>
+      <c r="E13" s="81" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F13" s="82" t="n">
+        <v>2.186135651897272</v>
+      </c>
+      <c r="G13" s="82" t="n">
+        <v>0.06069814478779453</v>
+      </c>
+      <c r="H13" s="82" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I13" s="82" t="n">
+        <v>0.1762278931945969</v>
+      </c>
+      <c r="J13" s="83">
+        <f>SUM(F13:I13)</f>
+        <v/>
+      </c>
+      <c r="K13" s="84" t="n">
+        <v>0.2898455066464321</v>
+      </c>
+      <c r="L13" s="84" t="n">
+        <v>0.2619970857789685</v>
+      </c>
+      <c r="M13" s="85">
+        <f>K13+L13</f>
+        <v/>
+      </c>
+      <c r="N13" s="86">
+        <f>J13+M13</f>
+        <v/>
+      </c>
+      <c r="O13" s="87" t="n">
+        <v>1.616733508688793</v>
+      </c>
+      <c r="P13" s="88" t="n">
+        <v>4.591637790993857</v>
+      </c>
+      <c r="Q13" s="89">
+        <f>IF(ABS(N13-2.9749042823)&lt;0.0001,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="80" t="inlineStr">
+        <is>
+          <t>New CCGT – Visayas 500 MW</t>
+        </is>
+      </c>
+      <c r="B14" s="80" t="inlineStr">
+        <is>
+          <t>Visayas</t>
+        </is>
+      </c>
+      <c r="C14" s="80" t="n">
+        <v>500</v>
+      </c>
+      <c r="D14" s="80" t="inlineStr">
+        <is>
+          <t>New CCGT</t>
+        </is>
+      </c>
+      <c r="E14" s="81" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F14" s="82" t="n">
+        <v>2.363794693189526</v>
+      </c>
+      <c r="G14" s="82" t="n">
+        <v>0.05114151940047044</v>
+      </c>
+      <c r="H14" s="82" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I14" s="82" t="n">
+        <v>0.1840456897850862</v>
+      </c>
+      <c r="J14" s="83">
+        <f>SUM(F14:I14)</f>
+        <v/>
+      </c>
+      <c r="K14" s="84" t="n">
+        <v>0.2408352664316718</v>
+      </c>
+      <c r="L14" s="84" t="n">
+        <v>0.1458718292244134</v>
+      </c>
+      <c r="M14" s="85">
+        <f>K14+L14</f>
+        <v/>
+      </c>
+      <c r="N14" s="86">
+        <f>J14+M14</f>
+        <v/>
+      </c>
+      <c r="O14" s="87" t="n">
+        <v>1.232759300375206</v>
+      </c>
+      <c r="P14" s="88" t="n">
+        <v>4.218448298406374</v>
+      </c>
+      <c r="Q14" s="89">
+        <f>IF(ABS(N14-2.9856889980)&lt;0.0001,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="80" t="inlineStr">
+        <is>
+          <t>New OCGT – Visayas 500 MW</t>
+        </is>
+      </c>
+      <c r="B15" s="80" t="inlineStr">
+        <is>
+          <t>Visayas</t>
+        </is>
+      </c>
+      <c r="C15" s="80" t="n">
+        <v>500</v>
+      </c>
+      <c r="D15" s="80" t="inlineStr">
+        <is>
+          <t>New OCGT</t>
+        </is>
+      </c>
+      <c r="E15" s="81" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F15" s="82" t="n">
+        <v>1.323438540708331</v>
+      </c>
+      <c r="G15" s="82" t="n">
+        <v>0.04360818471632168</v>
+      </c>
+      <c r="H15" s="82" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I15" s="82" t="n">
+        <v>0.1207763498223527</v>
+      </c>
+      <c r="J15" s="83">
+        <f>SUM(F15:I15)</f>
+        <v/>
+      </c>
+      <c r="K15" s="84" t="n">
+        <v>0.149314351908768</v>
+      </c>
+      <c r="L15" s="84" t="n">
+        <v>0.3007091622142286</v>
+      </c>
+      <c r="M15" s="85">
+        <f>K15+L15</f>
+        <v/>
+      </c>
+      <c r="N15" s="86">
+        <f>J15+M15</f>
+        <v/>
+      </c>
+      <c r="O15" s="87" t="n">
+        <v>1.980498548143771</v>
+      </c>
+      <c r="P15" s="88" t="n">
+        <v>3.918345137513774</v>
+      </c>
+      <c r="Q15" s="89">
+        <f>IF(ABS(N15-1.9378465894)&lt;0.0001,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="80" t="inlineStr">
+        <is>
+          <t>New gas engine – Visayas 500 MW</t>
+        </is>
+      </c>
+      <c r="B16" s="80" t="inlineStr">
+        <is>
+          <t>Visayas</t>
+        </is>
+      </c>
+      <c r="C16" s="80" t="n">
+        <v>500</v>
+      </c>
+      <c r="D16" s="80" t="inlineStr">
+        <is>
+          <t>New gas engine</t>
+        </is>
+      </c>
+      <c r="E16" s="81" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F16" s="82" t="n">
+        <v>2.18613890492919</v>
+      </c>
+      <c r="G16" s="82" t="n">
+        <v>0.06070879166704356</v>
+      </c>
+      <c r="H16" s="82" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I16" s="82" t="n">
+        <v>0.1762186632456875</v>
+      </c>
+      <c r="J16" s="83">
+        <f>SUM(F16:I16)</f>
+        <v/>
+      </c>
+      <c r="K16" s="84" t="n">
+        <v>0.2898455066464321</v>
+      </c>
+      <c r="L16" s="84" t="n">
+        <v>0.2620034247346381</v>
+      </c>
+      <c r="M16" s="85">
+        <f>K16+L16</f>
+        <v/>
+      </c>
+      <c r="N16" s="86">
+        <f>J16+M16</f>
+        <v/>
+      </c>
+      <c r="O16" s="87" t="n">
+        <v>1.616733508688794</v>
+      </c>
+      <c r="P16" s="88" t="n">
+        <v>4.591648799911785</v>
+      </c>
+      <c r="Q16" s="89">
+        <f>IF(ABS(N16-2.9749152912)&lt;0.0001,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="78" t="inlineStr">
+        <is>
+          <t>Fin90 – historical capacity factor (66.8% existing fleet; 63.1% whole fleet for new-build)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="79" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="B19" s="79" t="inlineStr">
+        <is>
+          <t>Grid</t>
+        </is>
+      </c>
+      <c r="C19" s="79" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="D19" s="79" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E19" s="79" t="inlineStr">
+        <is>
+          <t>Capacity factor</t>
+        </is>
+      </c>
+      <c r="F19" s="79" t="inlineStr">
+        <is>
+          <t>Capital recovery</t>
+        </is>
+      </c>
+      <c r="G19" s="79" t="inlineStr">
+        <is>
+          <t>G&amp;A</t>
+        </is>
+      </c>
+      <c r="H19" s="79" t="inlineStr">
+        <is>
+          <t>Land lease</t>
+        </is>
+      </c>
+      <c r="I19" s="79" t="inlineStr">
+        <is>
+          <t>Local taxes, ER 1-94</t>
+        </is>
+      </c>
+      <c r="J19" s="79" t="inlineStr">
+        <is>
+          <t>CRF</t>
+        </is>
+      </c>
+      <c r="K19" s="79" t="inlineStr">
+        <is>
+          <t>Fixed O&amp;M</t>
+        </is>
+      </c>
+      <c r="L19" s="79" t="inlineStr">
+        <is>
+          <t>Variable O&amp;M</t>
+        </is>
+      </c>
+      <c r="M19" s="79" t="inlineStr">
+        <is>
+          <t>OM</t>
+        </is>
+      </c>
+      <c r="N19" s="79" t="inlineStr">
+        <is>
+          <t>GATP = CRF + OM</t>
+        </is>
+      </c>
+      <c r="O19" s="79" t="inlineStr">
+        <is>
+          <t>CLLC → Fuel Cost</t>
+        </is>
+      </c>
+      <c r="P19" s="79" t="inlineStr">
+        <is>
+          <t>Previous GATP (incl. CLLC)</t>
+        </is>
+      </c>
+      <c r="Q19" s="79" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="80" t="inlineStr">
+        <is>
+          <t>Lot 1 Existing CCGT – Luzon 1,400 MW</t>
+        </is>
+      </c>
+      <c r="B20" s="80" t="inlineStr">
+        <is>
+          <t>Luzon</t>
+        </is>
+      </c>
+      <c r="C20" s="80" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D20" s="80" t="inlineStr">
+        <is>
+          <t>Existing CCGT</t>
+        </is>
+      </c>
+      <c r="E20" s="81" t="n">
+        <v>0.6680044139645122</v>
+      </c>
+      <c r="F20" s="82" t="n">
+        <v>0.7000142895800525</v>
+      </c>
+      <c r="G20" s="82" t="n">
+        <v>0.0268053464341559</v>
+      </c>
+      <c r="H20" s="82" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I20" s="82" t="n">
+        <v>0.07938208693776355</v>
+      </c>
+      <c r="J20" s="83">
+        <f>SUM(F20:I20)</f>
+        <v/>
+      </c>
+      <c r="K20" s="84" t="n">
+        <v>0.1514223705513955</v>
+      </c>
+      <c r="L20" s="84" t="n">
+        <v>0.1349810410827766</v>
+      </c>
+      <c r="M20" s="85">
+        <f>K20+L20</f>
+        <v/>
+      </c>
+      <c r="N20" s="86">
+        <f>J20+M20</f>
+        <v/>
+      </c>
+      <c r="O20" s="87" t="n">
+        <v>0.774043245330567</v>
+      </c>
+      <c r="P20" s="88" t="n">
+        <v>1.866648379916711</v>
+      </c>
+      <c r="Q20" s="89">
+        <f>IF(ABS(N20-1.0926051346)&lt;0.0001,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="80" t="inlineStr">
+        <is>
+          <t>Lot 2 Existing CCGT – Luzon 500 MW</t>
+        </is>
+      </c>
+      <c r="B21" s="80" t="inlineStr">
+        <is>
+          <t>Luzon</t>
+        </is>
+      </c>
+      <c r="C21" s="80" t="n">
+        <v>500</v>
+      </c>
+      <c r="D21" s="80" t="inlineStr">
+        <is>
+          <t>Existing CCGT</t>
+        </is>
+      </c>
+      <c r="E21" s="81" t="n">
+        <v>0.6680044139645122</v>
+      </c>
+      <c r="F21" s="82" t="n">
+        <v>0.7000056945691875</v>
+      </c>
+      <c r="G21" s="82" t="n">
+        <v>0.02677369187463277</v>
+      </c>
+      <c r="H21" s="82" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I21" s="82" t="n">
+        <v>0.07940951372560667</v>
+      </c>
+      <c r="J21" s="83">
+        <f>SUM(F21:I21)</f>
+        <v/>
+      </c>
+      <c r="K21" s="84" t="n">
+        <v>0.1514223705513955</v>
+      </c>
+      <c r="L21" s="84" t="n">
+        <v>0.1349621965953666</v>
+      </c>
+      <c r="M21" s="85">
+        <f>K21+L21</f>
+        <v/>
+      </c>
+      <c r="N21" s="86">
+        <f>J21+M21</f>
+        <v/>
+      </c>
+      <c r="O21" s="87" t="n">
+        <v>0.7740432453305666</v>
+      </c>
+      <c r="P21" s="88" t="n">
+        <v>1.866616712646755</v>
+      </c>
+      <c r="Q21" s="89">
+        <f>IF(ABS(N21-1.0925734673)&lt;0.0001,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="80" t="inlineStr">
+        <is>
+          <t>New CCGT – Luzon 1,000 MW</t>
+        </is>
+      </c>
+      <c r="B22" s="80" t="inlineStr">
+        <is>
+          <t>Luzon</t>
+        </is>
+      </c>
+      <c r="C22" s="80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D22" s="80" t="inlineStr">
+        <is>
+          <t>New CCGT</t>
+        </is>
+      </c>
+      <c r="E22" s="81" t="n">
+        <v>0.6312409193029385</v>
+      </c>
+      <c r="F22" s="82" t="n">
+        <v>1.572109954361591</v>
+      </c>
+      <c r="G22" s="82" t="n">
+        <v>0.03664859361280096</v>
+      </c>
+      <c r="H22" s="82" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I22" s="82" t="n">
+        <v>0.1330124098563733</v>
+      </c>
+      <c r="J22" s="83">
+        <f>SUM(F22:I22)</f>
+        <v/>
+      </c>
+      <c r="K22" s="84" t="n">
+        <v>0.1602412150546263</v>
+      </c>
+      <c r="L22" s="84" t="n">
+        <v>0.1403283878152508</v>
+      </c>
+      <c r="M22" s="85">
+        <f>K22+L22</f>
+        <v/>
+      </c>
+      <c r="N22" s="86">
+        <f>J22+M22</f>
+        <v/>
+      </c>
+      <c r="O22" s="87" t="n">
+        <v>0.7435691018136166</v>
+      </c>
+      <c r="P22" s="88" t="n">
+        <v>2.785909662514258</v>
+      </c>
+      <c r="Q22" s="89">
+        <f>IF(ABS(N22-2.0423405607)&lt;0.0001,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="80" t="inlineStr">
+        <is>
+          <t>New OCGT – Luzon 1,000 MW</t>
+        </is>
+      </c>
+      <c r="B23" s="80" t="inlineStr">
+        <is>
+          <t>Luzon</t>
+        </is>
+      </c>
+      <c r="C23" s="80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D23" s="80" t="inlineStr">
+        <is>
+          <t>New OCGT</t>
+        </is>
+      </c>
+      <c r="E23" s="81" t="n">
+        <v>0.6312409193029385</v>
+      </c>
+      <c r="F23" s="82" t="n">
+        <v>0.878930300511378</v>
+      </c>
+      <c r="G23" s="82" t="n">
+        <v>0.03488051578437331</v>
+      </c>
+      <c r="H23" s="82" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I23" s="82" t="n">
+        <v>0.09146626545407177</v>
+      </c>
+      <c r="J23" s="83">
+        <f>SUM(F23:I23)</f>
+        <v/>
+      </c>
+      <c r="K23" s="84" t="n">
+        <v>0.09934721575232117</v>
+      </c>
+      <c r="L23" s="84" t="n">
+        <v>0.2974207031124884</v>
+      </c>
+      <c r="M23" s="85">
+        <f>K23+L23</f>
+        <v/>
+      </c>
+      <c r="N23" s="86">
+        <f>J23+M23</f>
+        <v/>
+      </c>
+      <c r="O23" s="87" t="n">
+        <v>1.194586425864495</v>
+      </c>
+      <c r="P23" s="88" t="n">
+        <v>2.596631426479127</v>
+      </c>
+      <c r="Q23" s="89">
+        <f>IF(ABS(N23-1.4020450006)&lt;0.0001,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="80" t="inlineStr">
+        <is>
+          <t>New gas engine – Luzon 1,000 MW</t>
+        </is>
+      </c>
+      <c r="B24" s="80" t="inlineStr">
+        <is>
+          <t>Luzon</t>
+        </is>
+      </c>
+      <c r="C24" s="80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D24" s="80" t="inlineStr">
+        <is>
+          <t>New gas engine</t>
+        </is>
+      </c>
+      <c r="E24" s="81" t="n">
+        <v>0.6312409193029385</v>
+      </c>
+      <c r="F24" s="82" t="n">
+        <v>1.453204360104791</v>
+      </c>
+      <c r="G24" s="82" t="n">
+        <v>0.04535015293086382</v>
+      </c>
+      <c r="H24" s="82" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I24" s="82" t="n">
+        <v>0.1282009724423545</v>
+      </c>
+      <c r="J24" s="83">
+        <f>SUM(F24:I24)</f>
+        <v/>
+      </c>
+      <c r="K24" s="84" t="n">
+        <v>0.1928504776368587</v>
+      </c>
+      <c r="L24" s="84" t="n">
+        <v>0.2565279293054955</v>
+      </c>
+      <c r="M24" s="85">
+        <f>K24+L24</f>
+        <v/>
+      </c>
+      <c r="N24" s="86">
+        <f>J24+M24</f>
+        <v/>
+      </c>
+      <c r="O24" s="87" t="n">
+        <v>0.9751725925424477</v>
+      </c>
+      <c r="P24" s="88" t="n">
+        <v>3.051306484962811</v>
+      </c>
+      <c r="Q24" s="89">
+        <f>IF(ABS(N24-2.0761338924)&lt;0.0001,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="80" t="inlineStr">
+        <is>
+          <t>New CCGT – Visayas 440 MW</t>
+        </is>
+      </c>
+      <c r="B25" s="80" t="inlineStr">
+        <is>
+          <t>Visayas</t>
+        </is>
+      </c>
+      <c r="C25" s="80" t="n">
+        <v>440</v>
+      </c>
+      <c r="D25" s="80" t="inlineStr">
+        <is>
+          <t>New CCGT</t>
+        </is>
+      </c>
+      <c r="E25" s="81" t="n">
+        <v>0.6312409193029385</v>
+      </c>
+      <c r="F25" s="82" t="n">
+        <v>1.572097216184333</v>
+      </c>
+      <c r="G25" s="82" t="n">
+        <v>0.03661563499076113</v>
+      </c>
+      <c r="H25" s="82" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I25" s="82" t="n">
+        <v>0.1330409825687704</v>
+      </c>
+      <c r="J25" s="83">
+        <f>SUM(F25:I25)</f>
+        <v/>
+      </c>
+      <c r="K25" s="84" t="n">
+        <v>0.1602412150546263</v>
+      </c>
+      <c r="L25" s="84" t="n">
+        <v>0.1403087627365452</v>
+      </c>
+      <c r="M25" s="85">
+        <f>K25+L25</f>
+        <v/>
+      </c>
+      <c r="N25" s="86">
+        <f>J25+M25</f>
+        <v/>
+      </c>
+      <c r="O25" s="87" t="n">
+        <v>1.232759300375205</v>
+      </c>
+      <c r="P25" s="88" t="n">
+        <v>3.275063111910242</v>
+      </c>
+      <c r="Q25" s="89">
+        <f>IF(ABS(N25-2.0423038115)&lt;0.0001,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="80" t="inlineStr">
+        <is>
+          <t>New OCGT – Visayas 440 MW</t>
+        </is>
+      </c>
+      <c r="B26" s="80" t="inlineStr">
+        <is>
+          <t>Visayas</t>
+        </is>
+      </c>
+      <c r="C26" s="80" t="n">
+        <v>440</v>
+      </c>
+      <c r="D26" s="80" t="inlineStr">
+        <is>
+          <t>New OCGT</t>
+        </is>
+      </c>
+      <c r="E26" s="81" t="n">
+        <v>0.6312409193029385</v>
+      </c>
+      <c r="F26" s="82" t="n">
+        <v>0.8789191938137773</v>
+      </c>
+      <c r="G26" s="82" t="n">
+        <v>0.03484748943609427</v>
+      </c>
+      <c r="H26" s="82" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I26" s="82" t="n">
+        <v>0.09149489510466144</v>
+      </c>
+      <c r="J26" s="83">
+        <f>SUM(F26:I26)</f>
+        <v/>
+      </c>
+      <c r="K26" s="84" t="n">
+        <v>0.09934721575232118</v>
+      </c>
+      <c r="L26" s="84" t="n">
+        <v>0.2974010391500267</v>
+      </c>
+      <c r="M26" s="85">
+        <f>K26+L26</f>
+        <v/>
+      </c>
+      <c r="N26" s="86">
+        <f>J26+M26</f>
+        <v/>
+      </c>
+      <c r="O26" s="87" t="n">
+        <v>1.980498548143771</v>
+      </c>
+      <c r="P26" s="88" t="n">
+        <v>3.382508381400652</v>
+      </c>
+      <c r="Q26" s="89">
+        <f>IF(ABS(N26-1.4020098333)&lt;0.0001,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="80" t="inlineStr">
+        <is>
+          <t>New gas engine – Visayas 440 MW</t>
+        </is>
+      </c>
+      <c r="B27" s="80" t="inlineStr">
+        <is>
+          <t>Visayas</t>
+        </is>
+      </c>
+      <c r="C27" s="80" t="n">
+        <v>440</v>
+      </c>
+      <c r="D27" s="80" t="inlineStr">
+        <is>
+          <t>New gas engine</t>
+        </is>
+      </c>
+      <c r="E27" s="81" t="n">
+        <v>0.6312409193029385</v>
+      </c>
+      <c r="F27" s="82" t="n">
+        <v>1.453194259248868</v>
+      </c>
+      <c r="G27" s="82" t="n">
+        <v>0.04531709442244235</v>
+      </c>
+      <c r="H27" s="82" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I27" s="82" t="n">
+        <v>0.1282296313869738</v>
+      </c>
+      <c r="J27" s="83">
+        <f>SUM(F27:I27)</f>
+        <v/>
+      </c>
+      <c r="K27" s="84" t="n">
+        <v>0.1928504776368588</v>
+      </c>
+      <c r="L27" s="84" t="n">
+        <v>0.2565082468788883</v>
+      </c>
+      <c r="M27" s="85">
+        <f>K27+L27</f>
+        <v/>
+      </c>
+      <c r="N27" s="86">
+        <f>J27+M27</f>
+        <v/>
+      </c>
+      <c r="O27" s="87" t="n">
+        <v>1.616733528166195</v>
+      </c>
+      <c r="P27" s="88" t="n">
+        <v>3.692833237740226</v>
+      </c>
+      <c r="Q27" s="89">
+        <f>IF(ABS(N27-2.0760997096)&lt;0.0001,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="80" t="inlineStr">
+        <is>
+          <t>New CCGT – Visayas 500 MW</t>
+        </is>
+      </c>
+      <c r="B28" s="80" t="inlineStr">
+        <is>
+          <t>Visayas</t>
+        </is>
+      </c>
+      <c r="C28" s="80" t="n">
+        <v>500</v>
+      </c>
+      <c r="D28" s="80" t="inlineStr">
+        <is>
+          <t>New CCGT</t>
+        </is>
+      </c>
+      <c r="E28" s="81" t="n">
+        <v>0.6312409193029385</v>
+      </c>
+      <c r="F28" s="82" t="n">
+        <v>1.572099945702999</v>
+      </c>
+      <c r="G28" s="82" t="n">
+        <v>0.03662269755276221</v>
+      </c>
+      <c r="H28" s="82" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I28" s="82" t="n">
+        <v>0.1330348598437451</v>
+      </c>
+      <c r="J28" s="83">
+        <f>SUM(F28:I28)</f>
+        <v/>
+      </c>
+      <c r="K28" s="84" t="n">
+        <v>0.1602412150546263</v>
+      </c>
+      <c r="L28" s="84" t="n">
+        <v>0.1403129681106313</v>
+      </c>
+      <c r="M28" s="85">
+        <f>K28+L28</f>
+        <v/>
+      </c>
+      <c r="N28" s="86">
+        <f>J28+M28</f>
+        <v/>
+      </c>
+      <c r="O28" s="87" t="n">
+        <v>1.232759300375205</v>
+      </c>
+      <c r="P28" s="88" t="n">
+        <v>3.275070986639969</v>
+      </c>
+      <c r="Q28" s="89">
+        <f>IF(ABS(N28-2.0423116863)&lt;0.0001,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="80" t="inlineStr">
+        <is>
+          <t>New OCGT – Visayas 500 MW</t>
+        </is>
+      </c>
+      <c r="B29" s="80" t="inlineStr">
+        <is>
+          <t>Visayas</t>
+        </is>
+      </c>
+      <c r="C29" s="80" t="n">
+        <v>500</v>
+      </c>
+      <c r="D29" s="80" t="inlineStr">
+        <is>
+          <t>New OCGT</t>
+        </is>
+      </c>
+      <c r="E29" s="81" t="n">
+        <v>0.6312409193029385</v>
+      </c>
+      <c r="F29" s="82" t="n">
+        <v>0.8789215737205135</v>
+      </c>
+      <c r="G29" s="82" t="n">
+        <v>0.03485456651077734</v>
+      </c>
+      <c r="H29" s="82" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I29" s="82" t="n">
+        <v>0.09148876017846332</v>
+      </c>
+      <c r="J29" s="83">
+        <f>SUM(F29:I29)</f>
+        <v/>
+      </c>
+      <c r="K29" s="84" t="n">
+        <v>0.09934721575232117</v>
+      </c>
+      <c r="L29" s="84" t="n">
+        <v>0.2974052528562983</v>
+      </c>
+      <c r="M29" s="85">
+        <f>K29+L29</f>
+        <v/>
+      </c>
+      <c r="N29" s="86">
+        <f>J29+M29</f>
+        <v/>
+      </c>
+      <c r="O29" s="87" t="n">
+        <v>1.980498548143772</v>
+      </c>
+      <c r="P29" s="88" t="n">
+        <v>3.382515917162146</v>
+      </c>
+      <c r="Q29" s="89">
+        <f>IF(ABS(N29-1.4020173690)&lt;0.0001,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="80" t="inlineStr">
+        <is>
+          <t>New gas engine – Visayas 500 MW</t>
+        </is>
+      </c>
+      <c r="B30" s="80" t="inlineStr">
+        <is>
+          <t>Visayas</t>
+        </is>
+      </c>
+      <c r="C30" s="80" t="n">
+        <v>500</v>
+      </c>
+      <c r="D30" s="80" t="inlineStr">
+        <is>
+          <t>New gas engine</t>
+        </is>
+      </c>
+      <c r="E30" s="81" t="n">
+        <v>0.6312409193029385</v>
+      </c>
+      <c r="F30" s="82" t="n">
+        <v>1.453196423673517</v>
+      </c>
+      <c r="G30" s="82" t="n">
+        <v>0.04532417838856027</v>
+      </c>
+      <c r="H30" s="82" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I30" s="82" t="n">
+        <v>0.128223490184109</v>
+      </c>
+      <c r="J30" s="83">
+        <f>SUM(F30:I30)</f>
+        <v/>
+      </c>
+      <c r="K30" s="84" t="n">
+        <v>0.1928504776368587</v>
+      </c>
+      <c r="L30" s="84" t="n">
+        <v>0.2565124645417485</v>
+      </c>
+      <c r="M30" s="85">
+        <f>K30+L30</f>
+        <v/>
+      </c>
+      <c r="N30" s="86">
+        <f>J30+M30</f>
+        <v/>
+      </c>
+      <c r="O30" s="87" t="n">
+        <v>1.616733528558621</v>
+      </c>
+      <c r="P30" s="88" t="n">
+        <v>3.692840562983414</v>
+      </c>
+      <c r="Q30" s="89">
+        <f>IF(ABS(N30-2.0761070344)&lt;0.0001,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="90" t="inlineStr">
+        <is>
+          <t>How to read</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="91" t="inlineStr">
+        <is>
+          <t>• GATP is the bid ceiling (TOR Sec. 4.3, 8.3.3). A Price Offer above it is disqualified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="91" t="inlineStr">
+        <is>
+          <t>• CRF and OM add up to the GATP solved in each model (equity NPV = 0 at Re 14%, Sec. 8.4); the Check column confirms it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="91" t="inlineStr">
+        <is>
+          <t>• "CLLC → Fuel Cost" is the logistics cost per kWh that the previous draft carried inside the GATP. It is now paid monthly through the Fuel Cost at actual cost, up to the Sec. 17 caps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="91" t="inlineStr">
+        <is>
+          <t>• Fuel (gas commodity) is never in the GATP. It is paid through the Fuel Cost up to the Gas Price Benchmark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="91" t="inlineStr">
+        <is>
+          <t>• Visayas 440 MW and 500 MW give the same rate because the model is per kW.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>GAT Price (GATP) summary — PhP/kWh, excluding fuel</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="48" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Per the working Rules (franz_som_working draft_1, Secs. 8.6, 13.4 and 17), the GAT Price INCLUDES the Capped Landed Logistics Cost (CLLC: regasification, pipeline, marine/small-scale LNG, storage, processing, metering) and EXCLUDES the gas commodity, which is passed through under Rule 4. The CLLC column shows how much of each GATP is logistics; "GATP excluding CLLC" is the same model re-solved with CLLC = 0 (generation cost only), for comparison. 30-year cost recovery; existing plants have no construction period.</t>
-        </is>
-      </c>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="68" t="inlineStr">
+        <is>
+          <t>What the GAT Price is made of</t>
+        </is>
+      </c>
+      <c r="B1" s="69" t="n"/>
+      <c r="C1" s="69" t="n"/>
+      <c r="D1" s="69" t="n"/>
+      <c r="E1" s="69" t="n"/>
+      <c r="F1" s="69" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="70" t="inlineStr">
+        <is>
+          <t>GAIR Sec. 5, 8.6, 9, 13.4, 17, 18 as decided on 19 Oct 2026; DOE DC2026-06-0013 Sec. 4, 6.1(a), 7.2, 18.2.2; TOR Sec. 4.2, 4.3, 17.</t>
+        </is>
+      </c>
+      <c r="B2" s="69" t="n"/>
+      <c r="C2" s="69" t="n"/>
+      <c r="D2" s="69" t="n"/>
+      <c r="E2" s="69" t="n"/>
+      <c r="F2" s="69" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Fin42 — TOR capacity factor 42%</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>Fin90 — historical capacity factor (Meralco gas fleet)</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-    </row>
-    <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Grid</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>MW</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>CF</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>GATP (Rules: incl. CLLC)</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>of which CLLC</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>GATP excl. CLLC</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>CF</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>GATP (Rules: incl. CLLC)</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>of which CLLC</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>GATP excl. CLLC</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>CLLC cap (USD/MMBtu)</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="inlineStr">
-        <is>
-          <t>Heat rate (Btu/kWh)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
-      <c r="J6" s="7" t="n"/>
-      <c r="K6" s="7" t="n"/>
-      <c r="L6" s="7" t="n"/>
-      <c r="M6" s="7" t="n"/>
-      <c r="N6" s="7" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Lot 1 Existing CCGT - Luzon</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Luzon</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>1400</v>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>Existing CCGT</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>2.933449032397625</v>
-      </c>
-      <c r="G7" s="12" t="n">
-        <v>1.216353671233742</v>
-      </c>
-      <c r="H7" s="13" t="n">
-        <v>1.717095361163883</v>
-      </c>
-      <c r="I7" s="10" t="n">
-        <v>0.6680044139645122</v>
-      </c>
-      <c r="J7" s="11" t="n">
-        <v>1.866648379916711</v>
-      </c>
-      <c r="K7" s="12" t="n">
-        <v>0.7740432453305761</v>
-      </c>
-      <c r="L7" s="13" t="n">
-        <v>1.092605134586135</v>
-      </c>
-      <c r="M7" s="14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N7" s="15" t="n">
-        <v>6350</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Lot 2 Existing CCGT - Luzon</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Luzon</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>500</v>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>Existing CCGT</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>2.413367717709602</v>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>0.7740432453305743</v>
-      </c>
-      <c r="H8" s="13" t="n">
-        <v>1.639324472379028</v>
-      </c>
-      <c r="I8" s="10" t="n">
-        <v>0.6680044139645122</v>
-      </c>
-      <c r="J8" s="11" t="n">
-        <v>1.866616712646755</v>
-      </c>
-      <c r="K8" s="12" t="n">
-        <v>0.7740432453305655</v>
-      </c>
-      <c r="L8" s="13" t="n">
-        <v>1.09257346731619</v>
-      </c>
-      <c r="M8" s="14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N8" s="15" t="n">
-        <v>6350</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>New-build Luzon</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
-      <c r="I9" s="7" t="n"/>
-      <c r="J9" s="7" t="n"/>
-      <c r="K9" s="7" t="n"/>
-      <c r="L9" s="7" t="n"/>
-      <c r="M9" s="7" t="n"/>
-      <c r="N9" s="7" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>New-Build CCGT - Luzon 1000MW</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Luzon</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>New CCGT</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>3.729301496810136</v>
-      </c>
-      <c r="G10" s="12" t="n">
-        <v>0.7435691018136157</v>
-      </c>
-      <c r="H10" s="13" t="n">
-        <v>2.98573239499652</v>
-      </c>
-      <c r="I10" s="10" t="n">
-        <v>0.6312409193029385</v>
-      </c>
-      <c r="J10" s="11" t="n">
-        <v>2.785909662514258</v>
-      </c>
-      <c r="K10" s="12" t="n">
-        <v>0.743569101813617</v>
-      </c>
-      <c r="L10" s="13" t="n">
-        <v>2.042340560700641</v>
-      </c>
-      <c r="M10" s="14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N10" s="15" t="n">
-        <v>6100</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>New-Build OCGT - Luzon 1000MW</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Luzon</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>New OCGT</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>3.132474544268364</v>
-      </c>
-      <c r="G11" s="12" t="n">
-        <v>1.194586425864497</v>
-      </c>
-      <c r="H11" s="13" t="n">
-        <v>1.937888118403867</v>
-      </c>
-      <c r="I11" s="10" t="n">
-        <v>0.6312409193029385</v>
-      </c>
-      <c r="J11" s="11" t="n">
-        <v>2.596631426479127</v>
-      </c>
-      <c r="K11" s="12" t="n">
-        <v>1.194586425864497</v>
-      </c>
-      <c r="L11" s="13" t="n">
-        <v>1.40204500061463</v>
-      </c>
-      <c r="M11" s="14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N11" s="15" t="n">
-        <v>9800</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>New-Build Gas Engine - Luzon 1000MW</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Luzon</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>New gas engine</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="F12" s="11" t="n">
-        <v>3.950128250112614</v>
-      </c>
-      <c r="G12" s="12" t="n">
-        <v>0.9751725925424468</v>
-      </c>
-      <c r="H12" s="13" t="n">
-        <v>2.974955657570167</v>
-      </c>
-      <c r="I12" s="10" t="n">
-        <v>0.6312409193029385</v>
-      </c>
-      <c r="J12" s="11" t="n">
-        <v>3.051306484962811</v>
-      </c>
-      <c r="K12" s="12" t="n">
-        <v>0.9751725925424446</v>
-      </c>
-      <c r="L12" s="13" t="n">
-        <v>2.076133892420367</v>
-      </c>
-      <c r="M12" s="14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N12" s="15" t="n">
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>New-build Visayas</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
-      <c r="I13" s="7" t="n"/>
-      <c r="J13" s="7" t="n"/>
-      <c r="K13" s="7" t="n"/>
-      <c r="L13" s="7" t="n"/>
-      <c r="M13" s="7" t="n"/>
-      <c r="N13" s="7" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>New-Build CCGT - Visayas 440MW</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Visayas (Cebu and/or Panay)</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="n">
-        <v>440</v>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>New CCGT</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>4.218436463045343</v>
-      </c>
-      <c r="G14" s="12" t="n">
-        <v>1.232759300375205</v>
-      </c>
-      <c r="H14" s="13" t="n">
-        <v>2.985677162670138</v>
-      </c>
-      <c r="I14" s="10" t="n">
-        <v>0.6312409193029385</v>
-      </c>
-      <c r="J14" s="11" t="n">
-        <v>3.275063111910242</v>
-      </c>
-      <c r="K14" s="12" t="n">
-        <v>1.232759300375208</v>
-      </c>
-      <c r="L14" s="13" t="n">
-        <v>2.042303811535034</v>
-      </c>
-      <c r="M14" s="14" t="n">
-        <v>3.149999999999999</v>
-      </c>
-      <c r="N14" s="15" t="n">
-        <v>6100</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>New-Build OCGT - Visayas 440MW</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Visayas (Cebu and/or Panay)</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>440</v>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>New OCGT</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>3.9183338116066</v>
-      </c>
-      <c r="G15" s="12" t="n">
-        <v>1.980498548143765</v>
-      </c>
-      <c r="H15" s="13" t="n">
-        <v>1.937835263462835</v>
-      </c>
-      <c r="I15" s="10" t="n">
-        <v>0.6312409193029385</v>
-      </c>
-      <c r="J15" s="11" t="n">
-        <v>3.382508381400652</v>
-      </c>
-      <c r="K15" s="12" t="n">
-        <v>1.980498548143771</v>
-      </c>
-      <c r="L15" s="13" t="n">
-        <v>1.402009833256882</v>
-      </c>
-      <c r="M15" s="14" t="n">
-        <v>3.149999999999999</v>
-      </c>
-      <c r="N15" s="15" t="n">
-        <v>9800</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>New-Build Gas Engine - Visayas 440MW</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Visayas (Cebu and/or Panay)</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="n">
-        <v>440</v>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>New gas engine</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="F16" s="11" t="n">
-        <v>4.591637790993857</v>
-      </c>
-      <c r="G16" s="12" t="n">
-        <v>1.616733508688793</v>
-      </c>
-      <c r="H16" s="13" t="n">
-        <v>2.974904282305064</v>
-      </c>
-      <c r="I16" s="10" t="n">
-        <v>0.6312409193029385</v>
-      </c>
-      <c r="J16" s="11" t="n">
-        <v>3.692833237740226</v>
-      </c>
-      <c r="K16" s="12" t="n">
-        <v>1.616733528166199</v>
-      </c>
-      <c r="L16" s="13" t="n">
-        <v>2.076099709574027</v>
-      </c>
-      <c r="M16" s="14" t="n">
-        <v>3.149999999999999</v>
-      </c>
-      <c r="N16" s="15" t="n">
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>New-Build CCGT - Visayas 500MW</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Visayas (Cebu and/or Panay)</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="n">
-        <v>500</v>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>New CCGT</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="F17" s="11" t="n">
-        <v>4.218448298406374</v>
-      </c>
-      <c r="G17" s="12" t="n">
-        <v>1.232759300375206</v>
-      </c>
-      <c r="H17" s="13" t="n">
-        <v>2.985688998031168</v>
-      </c>
-      <c r="I17" s="10" t="n">
-        <v>0.6312409193029385</v>
-      </c>
-      <c r="J17" s="11" t="n">
-        <v>3.275070986639969</v>
-      </c>
-      <c r="K17" s="12" t="n">
-        <v>1.232759300375207</v>
-      </c>
-      <c r="L17" s="13" t="n">
-        <v>2.042311686264762</v>
-      </c>
-      <c r="M17" s="14" t="n">
-        <v>3.149999999999999</v>
-      </c>
-      <c r="N17" s="15" t="n">
-        <v>6100</v>
+      <c r="A4" s="92" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B4" s="92" t="inlineStr">
+        <is>
+          <t>In the GATP?</t>
+        </is>
+      </c>
+      <c r="C4" s="92" t="inlineStr">
+        <is>
+          <t>Where it is recovered</t>
+        </is>
+      </c>
+      <c r="D4" s="92" t="inlineStr">
+        <is>
+          <t>GAIR section</t>
+        </is>
+      </c>
+      <c r="E4" s="92" t="inlineStr">
+        <is>
+          <t>Model source</t>
+        </is>
+      </c>
+      <c r="F4" s="92" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="93" t="inlineStr">
+        <is>
+          <t>Return of capital (depreciation) and return on equity (Re)</t>
+        </is>
+      </c>
+      <c r="B5" s="94" t="inlineStr">
+        <is>
+          <t>Yes – CRF</t>
+        </is>
+      </c>
+      <c r="C5" s="93" t="inlineStr">
+        <is>
+          <t>GAP (bid price)</t>
+        </is>
+      </c>
+      <c r="D5" s="93" t="inlineStr">
+        <is>
+          <t>Sec. 8.4, 8.6</t>
+        </is>
+      </c>
+      <c r="E5" s="93" t="inlineStr">
+        <is>
+          <t>Tariff Breakdown A4</t>
+        </is>
+      </c>
+      <c r="F5" s="93" t="inlineStr">
+        <is>
+          <t>Solved so that equity NPV = 0 at Re.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="93" t="inlineStr">
+        <is>
+          <t>Interest and financing costs</t>
+        </is>
+      </c>
+      <c r="B6" s="94" t="inlineStr">
+        <is>
+          <t>Yes – CRF</t>
+        </is>
+      </c>
+      <c r="C6" s="93" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+      <c r="D6" s="93" t="inlineStr">
+        <is>
+          <t>Sec. 8.2, 8.8.1</t>
+        </is>
+      </c>
+      <c r="E6" s="93" t="inlineStr">
+        <is>
+          <t>Tariff Breakdown A4</t>
+        </is>
+      </c>
+      <c r="F6" s="93" t="inlineStr">
+        <is>
+          <t>Local and foreign debt tranches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="93" t="inlineStr">
+        <is>
+          <t>Income tax</t>
+        </is>
+      </c>
+      <c r="B7" s="94" t="inlineStr">
+        <is>
+          <t>Yes – CRF</t>
+        </is>
+      </c>
+      <c r="C7" s="93" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+      <c r="D7" s="93" t="inlineStr">
+        <is>
+          <t>Sec. 8.8.5</t>
+        </is>
+      </c>
+      <c r="E7" s="93" t="inlineStr">
+        <is>
+          <t>Tariff Breakdown A4</t>
+        </is>
+      </c>
+      <c r="F7" s="93" t="inlineStr">
+        <is>
+          <t>25% CREATE rate; no incentive assumed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="93" t="inlineStr">
+        <is>
+          <t>Major maintenance / refurbishment</t>
+        </is>
+      </c>
+      <c r="B8" s="94" t="inlineStr">
+        <is>
+          <t>Yes – CRF</t>
+        </is>
+      </c>
+      <c r="C8" s="93" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+      <c r="D8" s="93" t="inlineStr">
+        <is>
+          <t>Sec. 8.8.3, A.21</t>
+        </is>
+      </c>
+      <c r="E8" s="93" t="inlineStr">
+        <is>
+          <t>Operating Period</t>
+        </is>
+      </c>
+      <c r="F8" s="93" t="inlineStr">
+        <is>
+          <t>Capital outflow in the refurbishment year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="93" t="inlineStr">
+        <is>
+          <t>General and administrative (G&amp;A)</t>
+        </is>
+      </c>
+      <c r="B9" s="94" t="inlineStr">
+        <is>
+          <t>Yes – CRF</t>
+        </is>
+      </c>
+      <c r="C9" s="93" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+      <c r="D9" s="93" t="inlineStr">
+        <is>
+          <t>Annex A.6</t>
+        </is>
+      </c>
+      <c r="E9" s="93" t="inlineStr">
+        <is>
+          <t>Financials E12</t>
+        </is>
+      </c>
+      <c r="F9" s="93" t="inlineStr">
+        <is>
+          <t>Overhead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="93" t="inlineStr">
+        <is>
+          <t>Land lease</t>
+        </is>
+      </c>
+      <c r="B10" s="94" t="inlineStr">
+        <is>
+          <t>Yes – CRF</t>
+        </is>
+      </c>
+      <c r="C10" s="93" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+      <c r="D10" s="93" t="inlineStr">
+        <is>
+          <t>Sec. 8.8.3</t>
+        </is>
+      </c>
+      <c r="E10" s="93" t="inlineStr">
+        <is>
+          <t>Financials E13</t>
+        </is>
+      </c>
+      <c r="F10" s="93" t="inlineStr">
+        <is>
+          <t>Zero in these cases (land is in capital cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="93" t="inlineStr">
+        <is>
+          <t>Local taxes and ER 1-94 benefit</t>
+        </is>
+      </c>
+      <c r="B11" s="94" t="inlineStr">
+        <is>
+          <t>Yes – CRF</t>
+        </is>
+      </c>
+      <c r="C11" s="93" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+      <c r="D11" s="93" t="inlineStr">
+        <is>
+          <t>Sec. 8.8.3</t>
+        </is>
+      </c>
+      <c r="E11" s="93" t="inlineStr">
+        <is>
+          <t>Financials E14</t>
+        </is>
+      </c>
+      <c r="F11" s="93" t="inlineStr">
+        <is>
+          <t>RPT, LBT, host-community benefit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="95" t="inlineStr">
+        <is>
+          <t>Fixed O&amp;M</t>
+        </is>
+      </c>
+      <c r="B12" s="96" t="inlineStr">
+        <is>
+          <t>Yes – OM</t>
+        </is>
+      </c>
+      <c r="C12" s="95" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+      <c r="D12" s="95" t="inlineStr">
+        <is>
+          <t>Annex A.4</t>
+        </is>
+      </c>
+      <c r="E12" s="95" t="inlineStr">
+        <is>
+          <t>Financials E10</t>
+        </is>
+      </c>
+      <c r="F12" s="95" t="inlineStr">
+        <is>
+          <t>Stays in the bid: DC Sec. 6.1(a) "constructing and operating".</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="95" t="inlineStr">
+        <is>
+          <t>Variable non-fuel O&amp;M</t>
+        </is>
+      </c>
+      <c r="B13" s="96" t="inlineStr">
+        <is>
+          <t>Yes – OM</t>
+        </is>
+      </c>
+      <c r="C13" s="95" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+      <c r="D13" s="95" t="inlineStr">
+        <is>
+          <t>Annex A.5</t>
+        </is>
+      </c>
+      <c r="E13" s="95" t="inlineStr">
+        <is>
+          <t>Tariff Breakdown A8 + A9</t>
+        </is>
+      </c>
+      <c r="F13" s="95" t="inlineStr">
+        <is>
+          <t>Now excludes logistics (CLLC).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="97" t="inlineStr">
+        <is>
+          <t>Capped Landed Logistics Cost (CLLC)</t>
+        </is>
+      </c>
+      <c r="B14" s="98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C14" s="97" t="inlineStr">
+        <is>
+          <t>Fuel Cost (FC = FCC + CLLC)</t>
+        </is>
+      </c>
+      <c r="D14" s="97" t="inlineStr">
+        <is>
+          <t>Sec. 13.4, 17, 18</t>
+        </is>
+      </c>
+      <c r="E14" s="97" t="inlineStr">
+        <is>
+          <t>GATP Build-up row 20</t>
+        </is>
+      </c>
+      <c r="F14" s="97" t="inlineStr">
+        <is>
+          <t>Paid at actual cost up to the Sec. 17 caps; per Fuel Source Category caps allowed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="97" t="inlineStr">
+        <is>
+          <t>Fuel commodity (Reference Gas Price × heat rate)</t>
+        </is>
+      </c>
+      <c r="B15" s="98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C15" s="97" t="inlineStr">
+        <is>
+          <t>Fuel Cost (FCC)</t>
+        </is>
+      </c>
+      <c r="D15" s="97" t="inlineStr">
+        <is>
+          <t>Sec. 14–16, 18</t>
+        </is>
+      </c>
+      <c r="E15" s="97" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="97" t="inlineStr">
+        <is>
+          <t>Capped by the Gas Price Benchmark and Reference Heat Rate Cap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="97" t="inlineStr">
+        <is>
+          <t>Transmission / interconnection (ATP)</t>
+        </is>
+      </c>
+      <c r="B16" s="98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C16" s="97" t="inlineStr">
+        <is>
+          <t>TNP reimbursement</t>
+        </is>
+      </c>
+      <c r="D16" s="97" t="inlineStr">
+        <is>
+          <t>Sec. 9.3</t>
+        </is>
+      </c>
+      <c r="E16" s="97" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="97" t="inlineStr">
+        <is>
+          <t>Reference plant assumes NGCP builds it.</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>New-Build OCGT - Visayas 500MW</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Visayas (Cebu and/or Panay)</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>500</v>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>New OCGT</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="F18" s="11" t="n">
-        <v>3.918345137513774</v>
-      </c>
-      <c r="G18" s="12" t="n">
-        <v>1.980498548143772</v>
-      </c>
-      <c r="H18" s="13" t="n">
-        <v>1.937846589370002</v>
-      </c>
-      <c r="I18" s="10" t="n">
-        <v>0.6312409193029385</v>
-      </c>
-      <c r="J18" s="11" t="n">
-        <v>3.382515917162146</v>
-      </c>
-      <c r="K18" s="12" t="n">
-        <v>1.980498548143768</v>
-      </c>
-      <c r="L18" s="13" t="n">
-        <v>1.402017369018377</v>
-      </c>
-      <c r="M18" s="14" t="n">
-        <v>3.149999999999999</v>
-      </c>
-      <c r="N18" s="15" t="n">
-        <v>9800</v>
+      <c r="A18" s="91" t="inlineStr">
+        <is>
+          <t>• GATP = CRF + OM. Bidders compete on this number; a Price Offer above it is disqualified.</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>New-Build Gas Engine - Visayas 500MW</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Visayas (Cebu and/or Panay)</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="n">
-        <v>500</v>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>New gas engine</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="F19" s="11" t="n">
-        <v>4.591648799911785</v>
-      </c>
-      <c r="G19" s="12" t="n">
-        <v>1.616733508688794</v>
-      </c>
-      <c r="H19" s="13" t="n">
-        <v>2.974915291222991</v>
-      </c>
-      <c r="I19" s="10" t="n">
-        <v>0.6312409193029385</v>
-      </c>
-      <c r="J19" s="11" t="n">
-        <v>3.692840562983414</v>
-      </c>
-      <c r="K19" s="12" t="n">
-        <v>1.616733528558617</v>
-      </c>
-      <c r="L19" s="13" t="n">
-        <v>2.076107034424797</v>
-      </c>
-      <c r="M19" s="14" t="n">
-        <v>3.149999999999999</v>
-      </c>
-      <c r="N19" s="15" t="n">
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>How to read: GATP is the bid ceiling. A Price Offer above it is disqualified. Fuel (gas commodity) is not in the GATP; it is recovered monthly up to the Gas Price Benchmark.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Lot 1, Fin42: CLLC is higher (1.22) because logistics on the 24% non-mid-merit energy (paid fuel only, TOR 4.2.2) is carried by the GAP-paid energy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Visayas CLLC (US$3.15/MMBtu) includes marine/small-scale LNG and storage; OCGT and gas engines burn more gas per kWh, so their CLLC per kWh is larger.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>If the Commission decides to pass logistics through outside the GATP, the "GATP excl. CLLC" columns are the ceilings, and the Rules (Secs. 8.6, 13.4, 17) would need to change.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Rates are per kW, so Visayas 440 MW and 500 MW give the same GATP. Detail: Rates, Parameters (inputs with sources), TOR_Conditions, Historical_CF, References.</t>
+      <c r="A19" s="91" t="inlineStr">
+        <is>
+          <t>• Settlement: MMSA = Energy Delivered × (GAP + FC), DOE DC Sec. 7.2. FC = FCC + CLLC, each component at the lesser of actual prudent cost and its cap.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A22:N22"/>
-    <mergeCell ref="A21:N21"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="I4:L4"/>
-    <mergeCell ref="A24:N24"/>
-    <mergeCell ref="A25:N25"/>
-    <mergeCell ref="A23:N23"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="68" t="inlineStr">
+        <is>
+          <t>GAT Price by lot and variation – PhP/kWh, excluding fuel, 30-year cost recovery</t>
+        </is>
+      </c>
+      <c r="B1" s="69" t="n"/>
+      <c r="C1" s="69" t="n"/>
+      <c r="D1" s="69" t="n"/>
+      <c r="E1" s="69" t="n"/>
+      <c r="F1" s="69" t="n"/>
+      <c r="G1" s="69" t="n"/>
+      <c r="H1" s="69" t="n"/>
+      <c r="I1" s="69" t="n"/>
+      <c r="J1" s="69" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="70" t="inlineStr">
+        <is>
+          <t>GATP = CRF + OM (decision of 19 Oct 2026). Previous-draft values kept for comparison.</t>
+        </is>
+      </c>
+      <c r="B2" s="69" t="n"/>
+      <c r="C2" s="69" t="n"/>
+      <c r="D2" s="69" t="n"/>
+      <c r="E2" s="69" t="n"/>
+      <c r="F2" s="69" t="n"/>
+      <c r="G2" s="69" t="n"/>
+      <c r="H2" s="69" t="n"/>
+      <c r="I2" s="69" t="n"/>
+      <c r="J2" s="69" t="n"/>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="79" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="B4" s="79" t="inlineStr">
+        <is>
+          <t>TOR capacity factor</t>
+        </is>
+      </c>
+      <c r="C4" s="79" t="inlineStr">
+        <is>
+          <t>TOR supply period</t>
+        </is>
+      </c>
+      <c r="D4" s="79" t="inlineStr">
+        <is>
+          <t>Construction (months)</t>
+        </is>
+      </c>
+      <c r="E4" s="79" t="inlineStr">
+        <is>
+          <t>Recovery period (yrs)</t>
+        </is>
+      </c>
+      <c r="F4" s="79" t="inlineStr">
+        <is>
+          <t>Fin42 GATP</t>
+        </is>
+      </c>
+      <c r="G4" s="79" t="inlineStr">
+        <is>
+          <t>Fin90 GATP</t>
+        </is>
+      </c>
+      <c r="H4" s="79" t="inlineStr">
+        <is>
+          <t>Fin90 minus Fin42</t>
+        </is>
+      </c>
+      <c r="I4" s="79" t="inlineStr">
+        <is>
+          <t>Fin42 previous (incl. CLLC)</t>
+        </is>
+      </c>
+      <c r="J4" s="79" t="inlineStr">
+        <is>
+          <t>Fin90 previous (incl. CLLC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="99" t="inlineStr">
+        <is>
+          <t>Lot 1 Existing CCGT – Luzon 1,400 MW</t>
+        </is>
+      </c>
+      <c r="B5" s="99" t="inlineStr">
+        <is>
+          <t>38%–42% + 22%–24% non-mid-merit</t>
+        </is>
+      </c>
+      <c r="C5" s="99" t="inlineStr">
+        <is>
+          <t>5 + 5 yrs</t>
+        </is>
+      </c>
+      <c r="D5" s="99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="99" t="n">
+        <v>30</v>
+      </c>
+      <c r="F5" s="100" t="n">
+        <v>1.717095361163876</v>
+      </c>
+      <c r="G5" s="100" t="n">
+        <v>1.092605134586144</v>
+      </c>
+      <c r="H5" s="101">
+        <f>G5-F5</f>
+        <v/>
+      </c>
+      <c r="I5" s="102" t="n">
+        <v>2.933449032397625</v>
+      </c>
+      <c r="J5" s="102" t="n">
+        <v>1.866648379916711</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="99" t="inlineStr">
+        <is>
+          <t>Lot 2 Existing CCGT – Luzon 500 MW</t>
+        </is>
+      </c>
+      <c r="B6" s="99" t="inlineStr">
+        <is>
+          <t>37%–42%</t>
+        </is>
+      </c>
+      <c r="C6" s="99" t="inlineStr">
+        <is>
+          <t>10 yrs</t>
+        </is>
+      </c>
+      <c r="D6" s="99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="99" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" s="100" t="n">
+        <v>1.639324472379034</v>
+      </c>
+      <c r="G6" s="100" t="n">
+        <v>1.092573467316189</v>
+      </c>
+      <c r="H6" s="101">
+        <f>G6-F6</f>
+        <v/>
+      </c>
+      <c r="I6" s="102" t="n">
+        <v>2.413367717709602</v>
+      </c>
+      <c r="J6" s="102" t="n">
+        <v>1.866616712646755</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="99" t="inlineStr">
+        <is>
+          <t>New CCGT – Luzon 1,000 MW</t>
+        </is>
+      </c>
+      <c r="B7" s="99" t="inlineStr">
+        <is>
+          <t>37%–42%</t>
+        </is>
+      </c>
+      <c r="C7" s="99" t="inlineStr">
+        <is>
+          <t>20 yrs</t>
+        </is>
+      </c>
+      <c r="D7" s="99" t="n">
+        <v>36</v>
+      </c>
+      <c r="E7" s="99" t="n">
+        <v>30</v>
+      </c>
+      <c r="F7" s="100" t="n">
+        <v>2.985732394996519</v>
+      </c>
+      <c r="G7" s="100" t="n">
+        <v>2.042340560700642</v>
+      </c>
+      <c r="H7" s="101">
+        <f>G7-F7</f>
+        <v/>
+      </c>
+      <c r="I7" s="102" t="n">
+        <v>3.729301496810136</v>
+      </c>
+      <c r="J7" s="102" t="n">
+        <v>2.785909662514258</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="99" t="inlineStr">
+        <is>
+          <t>New OCGT – Luzon 1,000 MW</t>
+        </is>
+      </c>
+      <c r="B8" s="99" t="inlineStr">
+        <is>
+          <t>37%–42%</t>
+        </is>
+      </c>
+      <c r="C8" s="99" t="inlineStr">
+        <is>
+          <t>20 yrs</t>
+        </is>
+      </c>
+      <c r="D8" s="99" t="n">
+        <v>24</v>
+      </c>
+      <c r="E8" s="99" t="n">
+        <v>30</v>
+      </c>
+      <c r="F8" s="100" t="n">
+        <v>1.937888118403868</v>
+      </c>
+      <c r="G8" s="100" t="n">
+        <v>1.402045000614633</v>
+      </c>
+      <c r="H8" s="101">
+        <f>G8-F8</f>
+        <v/>
+      </c>
+      <c r="I8" s="102" t="n">
+        <v>3.132474544268364</v>
+      </c>
+      <c r="J8" s="102" t="n">
+        <v>2.596631426479127</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="99" t="inlineStr">
+        <is>
+          <t>New gas engine – Luzon 1,000 MW</t>
+        </is>
+      </c>
+      <c r="B9" s="99" t="inlineStr">
+        <is>
+          <t>37%–42%</t>
+        </is>
+      </c>
+      <c r="C9" s="99" t="inlineStr">
+        <is>
+          <t>20 yrs</t>
+        </is>
+      </c>
+      <c r="D9" s="99" t="n">
+        <v>18</v>
+      </c>
+      <c r="E9" s="99" t="n">
+        <v>30</v>
+      </c>
+      <c r="F9" s="100" t="n">
+        <v>2.974955657570167</v>
+      </c>
+      <c r="G9" s="100" t="n">
+        <v>2.076133892420363</v>
+      </c>
+      <c r="H9" s="101">
+        <f>G9-F9</f>
+        <v/>
+      </c>
+      <c r="I9" s="102" t="n">
+        <v>3.950128250112614</v>
+      </c>
+      <c r="J9" s="102" t="n">
+        <v>3.051306484962811</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="99" t="inlineStr">
+        <is>
+          <t>New CCGT – Visayas 440 MW</t>
+        </is>
+      </c>
+      <c r="B10" s="99" t="inlineStr">
+        <is>
+          <t>37%–42%</t>
+        </is>
+      </c>
+      <c r="C10" s="99" t="inlineStr">
+        <is>
+          <t>20 yrs</t>
+        </is>
+      </c>
+      <c r="D10" s="99" t="n">
+        <v>36</v>
+      </c>
+      <c r="E10" s="99" t="n">
+        <v>30</v>
+      </c>
+      <c r="F10" s="100" t="n">
+        <v>2.985677162670138</v>
+      </c>
+      <c r="G10" s="100" t="n">
+        <v>2.042303811535037</v>
+      </c>
+      <c r="H10" s="101">
+        <f>G10-F10</f>
+        <v/>
+      </c>
+      <c r="I10" s="102" t="n">
+        <v>4.218436463045343</v>
+      </c>
+      <c r="J10" s="102" t="n">
+        <v>3.275063111910242</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="99" t="inlineStr">
+        <is>
+          <t>New OCGT – Visayas 440 MW</t>
+        </is>
+      </c>
+      <c r="B11" s="99" t="inlineStr">
+        <is>
+          <t>37%–42%</t>
+        </is>
+      </c>
+      <c r="C11" s="99" t="inlineStr">
+        <is>
+          <t>20 yrs</t>
+        </is>
+      </c>
+      <c r="D11" s="99" t="n">
+        <v>24</v>
+      </c>
+      <c r="E11" s="99" t="n">
+        <v>30</v>
+      </c>
+      <c r="F11" s="100" t="n">
+        <v>1.937835263462828</v>
+      </c>
+      <c r="G11" s="100" t="n">
+        <v>1.402009833256881</v>
+      </c>
+      <c r="H11" s="101">
+        <f>G11-F11</f>
+        <v/>
+      </c>
+      <c r="I11" s="102" t="n">
+        <v>3.9183338116066</v>
+      </c>
+      <c r="J11" s="102" t="n">
+        <v>3.382508381400652</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="99" t="inlineStr">
+        <is>
+          <t>New gas engine – Visayas 440 MW</t>
+        </is>
+      </c>
+      <c r="B12" s="99" t="inlineStr">
+        <is>
+          <t>37%–42%</t>
+        </is>
+      </c>
+      <c r="C12" s="99" t="inlineStr">
+        <is>
+          <t>20 yrs</t>
+        </is>
+      </c>
+      <c r="D12" s="99" t="n">
+        <v>18</v>
+      </c>
+      <c r="E12" s="99" t="n">
+        <v>30</v>
+      </c>
+      <c r="F12" s="100" t="n">
+        <v>2.974904282305064</v>
+      </c>
+      <c r="G12" s="100" t="n">
+        <v>2.076099709574031</v>
+      </c>
+      <c r="H12" s="101">
+        <f>G12-F12</f>
+        <v/>
+      </c>
+      <c r="I12" s="102" t="n">
+        <v>4.591637790993857</v>
+      </c>
+      <c r="J12" s="102" t="n">
+        <v>3.692833237740226</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="99" t="inlineStr">
+        <is>
+          <t>New CCGT – Visayas 500 MW</t>
+        </is>
+      </c>
+      <c r="B13" s="99" t="inlineStr">
+        <is>
+          <t>37%–42%</t>
+        </is>
+      </c>
+      <c r="C13" s="99" t="inlineStr">
+        <is>
+          <t>20 yrs</t>
+        </is>
+      </c>
+      <c r="D13" s="99" t="n">
+        <v>36</v>
+      </c>
+      <c r="E13" s="99" t="n">
+        <v>30</v>
+      </c>
+      <c r="F13" s="100" t="n">
+        <v>2.985688998031168</v>
+      </c>
+      <c r="G13" s="100" t="n">
+        <v>2.042311686264764</v>
+      </c>
+      <c r="H13" s="101">
+        <f>G13-F13</f>
+        <v/>
+      </c>
+      <c r="I13" s="102" t="n">
+        <v>4.218448298406374</v>
+      </c>
+      <c r="J13" s="102" t="n">
+        <v>3.275070986639969</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="99" t="inlineStr">
+        <is>
+          <t>New OCGT – Visayas 500 MW</t>
+        </is>
+      </c>
+      <c r="B14" s="99" t="inlineStr">
+        <is>
+          <t>37%–42%</t>
+        </is>
+      </c>
+      <c r="C14" s="99" t="inlineStr">
+        <is>
+          <t>20 yrs</t>
+        </is>
+      </c>
+      <c r="D14" s="99" t="n">
+        <v>24</v>
+      </c>
+      <c r="E14" s="99" t="n">
+        <v>30</v>
+      </c>
+      <c r="F14" s="100" t="n">
+        <v>1.937846589370002</v>
+      </c>
+      <c r="G14" s="100" t="n">
+        <v>1.402017369018373</v>
+      </c>
+      <c r="H14" s="101">
+        <f>G14-F14</f>
+        <v/>
+      </c>
+      <c r="I14" s="102" t="n">
+        <v>3.918345137513774</v>
+      </c>
+      <c r="J14" s="102" t="n">
+        <v>3.382515917162146</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="99" t="inlineStr">
+        <is>
+          <t>New gas engine – Visayas 500 MW</t>
+        </is>
+      </c>
+      <c r="B15" s="99" t="inlineStr">
+        <is>
+          <t>37%–42%</t>
+        </is>
+      </c>
+      <c r="C15" s="99" t="inlineStr">
+        <is>
+          <t>20 yrs</t>
+        </is>
+      </c>
+      <c r="D15" s="99" t="n">
+        <v>18</v>
+      </c>
+      <c r="E15" s="99" t="n">
+        <v>30</v>
+      </c>
+      <c r="F15" s="100" t="n">
+        <v>2.974915291222991</v>
+      </c>
+      <c r="G15" s="100" t="n">
+        <v>2.076107034424793</v>
+      </c>
+      <c r="H15" s="101">
+        <f>G15-F15</f>
+        <v/>
+      </c>
+      <c r="I15" s="102" t="n">
+        <v>4.591648799911785</v>
+      </c>
+      <c r="J15" s="102" t="n">
+        <v>3.692840562983414</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10416,128 +13175,128 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="103" t="inlineStr">
         <is>
           <t>FinModel: GAT Price (GATP) for every DOE TOR lot and variation  (revised 20 Oct 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Rates are PhP/kWh, excluding fuel (fuel is recovered through the Fuel Cost Pass-Through).</t>
+      <c r="A2" s="104" t="inlineStr">
+        <is>
+          <t>GATP = CRF + OM (GAIR Sec. 8.6, decision of 19 Oct 2026). The Capped Landed Logistics Cost (CLLC) is no longer in the GATP; it is paid through the Fuel Cost (FC = FCC + CLLC). Rates are PhP/kWh, excluding fuel.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="17" t="inlineStr">
-        <is>
-          <t>BASIS (revised)</t>
+      <c r="A3" s="105" t="inlineStr">
+        <is>
+          <t>WHAT CHANGED ON 20 OCT 2026</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>• Cost recovery over 30 years for every plant, existing and new-build: the plant's economic life, as the ERC sets it, even where the TOR contract is shorter (Lot 1: 5 yrs; Lot 2: 10 yrs; new-build: 20 yrs). The earlier "_SupplyPeriod" variants are withdrawn.</t>
+      <c r="A4" s="106" t="inlineStr">
+        <is>
+          <t>• All 22 models (Fin42 and Fin90) were re-solved with the CLLC removed from the variable O&amp;M input (F37). Each new GATP matches the earlier "GATP excl. CLLC" re-solve to within 1e-14.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>• Existing plants (Lots 1 and 2, e.g. First Gen's Santa Rita and San Lorenzo): zero construction period, because the plant is already built. The capital is spent at year 0 and the plant earns from year 1, with no interest during construction. The naruto model needed a small formula fix to accept 0 months (Construction Period row 92 and the C8 input check); new-build cases are unaffected.</t>
+      <c r="A5" s="106" t="inlineStr">
+        <is>
+          <t>• Each model has a new "GATP Build-up" sheet: CRF and OM components (linked to the model), the CLLC now in the Fuel Cost, and the previous-draft GATP for comparison, with a chart.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="106" t="inlineStr">
+        <is>
+          <t>• Passwords and protection are unchanged ("yolo" to open). The COMPUTE GAT PRICE button still runs the solver macro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="105" t="inlineStr">
+        <is>
+          <t>BASIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1">
+      <c r="A8" s="106" t="inlineStr">
+        <is>
+          <t>• Cost recovery over 30 years for every plant: the ERC economic life, even where the TOR contract is shorter (Lot 1: 5 + 5 yrs; Lot 2: 10 yrs; new-build: 20 yrs).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="106" t="inlineStr">
+        <is>
+          <t>• Existing plants (Lots 1 and 2): zero construction period; capital at year 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="105" t="inlineStr">
         <is>
           <t>FOLDERS</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Fin42/  capacity factor from the DOE TOR: 42%, the top of every TOR band. For Lot 1, the 22%–24% non-mid-merit energy is paid fuel only (TOR 4.2.2), so its variable O&amp;M and logistics (24%) are carried by the GAP-paid energy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Fin90/  actual historical capacity factor of Meralco's gas suppliers, Jan 2024–Sep 2026: 66.8% for the existing fleet (Santa Rita, San Lorenzo, Ilijan) used for Lots 1 and 2; 63.1% for the whole fleet including EERI, used for new-build. The historical figure is about 63%–67%, not 90%; the folder keeps the name requested.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Each folder holds 11 models (2 existing lots + 9 new-build variations: CCGT, OCGT and gas engine in Luzon 1,000 MW, Visayas 440 MW and Visayas 500 MW).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
-        <is>
-          <t>THE MODELS</t>
-        </is>
-      </c>
-    </row>
     <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Each file is the "naruto" template (whisper/naruto.xlsm) with the inputs filled in and solved: F15 calibrates cost to the target capital cost and F30 (GAT Price, PhP/kWh) sets equity NPV = 0 at the required return. C102 shows "SOLVED". Same passwords as naruto ("yolo" to open). All 22 files were re-opened and recalculated: same rate and "SOLVED" in each.</t>
+      <c r="A11" s="106" t="inlineStr">
+        <is>
+          <t>Fin42/  TOR capacity factor 42% (top of every TOR band). Lot 1 adds 24% non-mid-merit energy paid fuel only (TOR 4.2.2); its variable O&amp;M is carried by GAP-paid energy.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="106" t="inlineStr">
+        <is>
+          <t>Fin90/  actual historical capacity factor of Meralco's gas suppliers, Jan 2024–Sep 2026: 66.8% existing fleet (Lots 1, 2); 63.1% whole fleet (new-build). The folder keeps the requested name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="105" t="inlineStr">
         <is>
           <t>TABS</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="45" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>GATP_Summary: the headline ceilings, with and without logistics (CLLC).  Rates: rates side by side and cost split.  Parameters: every model input per file, grouped by section and colour-coded, with a comment on each value giving its source.  TOR_Conditions, Historical_CF, References.</t>
-        </is>
-      </c>
-    </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="106" t="inlineStr">
+        <is>
+          <t>Dashboard: GATP ranges and charts.  GATP_Summary: CRF and OM build-up per case.  GATP_Composition: what is in and out of the GATP.  Rates: GATP side by side, with previous values.  Parameters: every model input per file (changed rows shaded yellow).  TOR_Conditions, Historical_CF, References.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="105" t="inlineStr">
         <is>
           <t>CAVEATS</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>1. OCGT and gas engines look cheap here because fuel is excluded; their higher heat rate shows up in fuel. Compare technologies on GAT Price + fuel.</t>
-        </is>
-      </c>
-    </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="106" t="inlineStr">
+        <is>
+          <t>1. OCGT and gas engines look cheap because fuel is excluded; their higher heat rate shows up in the Fuel Cost (and, now, in the CLLC per kWh).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="106" t="inlineStr">
         <is>
           <t>2. Visayas 440 MW and 500 MW give the same rate: the model is per kW.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>3. Lots 1 and 2 differ only through the Lot 1 non-mid-merit cost in Fin42; in Fin90 they are identical.</t>
-        </is>
-      </c>
-    </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>4. OCGT and gas-engine design life is usually 20–25 years; they are set to 30 years here to follow the 30-year ERC recovery rule.</t>
+      <c r="A18" s="106" t="inlineStr">
+        <is>
+          <t>3. OCGT and gas-engine design life is usually 20–25 years; set to 30 years to follow the ERC recovery rule.</t>
         </is>
       </c>
     </row>
@@ -10546,1406 +13305,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="18" t="inlineStr">
-        <is>
-          <t>GAT Price by lot and variation (PhP/kWh, excluding fuel; 30-year cost recovery)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>TOR capacity factor</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>TOR delivery year</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>TOR supply period</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>Construction (months)</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>Recovery period (yrs)</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>Fin42 CF</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>Fin42 GATP</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>Fin90 CF (historical)</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>Fin90 GATP</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>Fin90 minus Fin42</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>Lot 1 Existing CCGT - Luzon</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>38%–42% + 22%–24% non-mid-merit</t>
-        </is>
-      </c>
-      <c r="C4" s="19" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D4" s="19" t="inlineStr">
-        <is>
-          <t>5 + 5 yrs</t>
-        </is>
-      </c>
-      <c r="E4" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="G4" s="20" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H4" s="21" t="n">
-        <v>2.933449032397625</v>
-      </c>
-      <c r="I4" s="20" t="n">
-        <v>0.6680044139645122</v>
-      </c>
-      <c r="J4" s="21" t="n">
-        <v>1.866648379916711</v>
-      </c>
-      <c r="K4" s="22" t="n">
-        <v>-1.066800652480914</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>Lot 2 Existing CCGT - Luzon</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>37%–42%</t>
-        </is>
-      </c>
-      <c r="C5" s="19" t="n">
-        <v>2027</v>
-      </c>
-      <c r="D5" s="19" t="inlineStr">
-        <is>
-          <t>10 yrs</t>
-        </is>
-      </c>
-      <c r="E5" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="G5" s="20" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H5" s="21" t="n">
-        <v>2.413367717709602</v>
-      </c>
-      <c r="I5" s="20" t="n">
-        <v>0.6680044139645122</v>
-      </c>
-      <c r="J5" s="21" t="n">
-        <v>1.866616712646755</v>
-      </c>
-      <c r="K5" s="22" t="n">
-        <v>-0.5467510050628466</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>New-Build CCGT - Luzon 1000MW</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>37%–42%</t>
-        </is>
-      </c>
-      <c r="C6" s="19" t="n">
-        <v>2031</v>
-      </c>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>20 yrs</t>
-        </is>
-      </c>
-      <c r="E6" s="19" t="n">
-        <v>36</v>
-      </c>
-      <c r="F6" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="G6" s="20" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H6" s="21" t="n">
-        <v>3.729301496810136</v>
-      </c>
-      <c r="I6" s="20" t="n">
-        <v>0.6312409193029385</v>
-      </c>
-      <c r="J6" s="21" t="n">
-        <v>2.785909662514258</v>
-      </c>
-      <c r="K6" s="22" t="n">
-        <v>-0.9433918342958774</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>New-Build OCGT - Luzon 1000MW</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>37%–42%</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="n">
-        <v>2031</v>
-      </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>20 yrs</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>24</v>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="G7" s="20" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H7" s="21" t="n">
-        <v>3.132474544268364</v>
-      </c>
-      <c r="I7" s="20" t="n">
-        <v>0.6312409193029385</v>
-      </c>
-      <c r="J7" s="21" t="n">
-        <v>2.596631426479127</v>
-      </c>
-      <c r="K7" s="22" t="n">
-        <v>-0.5358431177892364</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>New-Build Gas Engine - Luzon 1000MW</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>37%–42%</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="n">
-        <v>2031</v>
-      </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>20 yrs</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="n">
-        <v>18</v>
-      </c>
-      <c r="F8" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="G8" s="20" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H8" s="21" t="n">
-        <v>3.950128250112614</v>
-      </c>
-      <c r="I8" s="20" t="n">
-        <v>0.6312409193029385</v>
-      </c>
-      <c r="J8" s="21" t="n">
-        <v>3.051306484962811</v>
-      </c>
-      <c r="K8" s="22" t="n">
-        <v>-0.8988217651498029</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>New-Build CCGT - Visayas 440MW</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>37%–42%</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="n">
-        <v>2028</v>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>20 yrs</t>
-        </is>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>36</v>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="G9" s="20" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H9" s="21" t="n">
-        <v>4.218436463045343</v>
-      </c>
-      <c r="I9" s="20" t="n">
-        <v>0.6312409193029385</v>
-      </c>
-      <c r="J9" s="21" t="n">
-        <v>3.275063111910242</v>
-      </c>
-      <c r="K9" s="22" t="n">
-        <v>-0.9433733511351012</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>New-Build OCGT - Visayas 440MW</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>37%–42%</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="n">
-        <v>2028</v>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>20 yrs</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>24</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="G10" s="20" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H10" s="21" t="n">
-        <v>3.9183338116066</v>
-      </c>
-      <c r="I10" s="20" t="n">
-        <v>0.6312409193029385</v>
-      </c>
-      <c r="J10" s="21" t="n">
-        <v>3.382508381400652</v>
-      </c>
-      <c r="K10" s="22" t="n">
-        <v>-0.5358254302059478</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>New-Build Gas Engine - Visayas 440MW</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>37%–42%</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="n">
-        <v>2028</v>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>20 yrs</t>
-        </is>
-      </c>
-      <c r="E11" s="19" t="n">
-        <v>18</v>
-      </c>
-      <c r="F11" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="G11" s="20" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H11" s="21" t="n">
-        <v>4.591637790993857</v>
-      </c>
-      <c r="I11" s="20" t="n">
-        <v>0.6312409193029385</v>
-      </c>
-      <c r="J11" s="21" t="n">
-        <v>3.692833237740226</v>
-      </c>
-      <c r="K11" s="22" t="n">
-        <v>-0.8988045532536315</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>New-Build CCGT - Visayas 500MW</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>37%–42%</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="n">
-        <v>2031</v>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>20 yrs</t>
-        </is>
-      </c>
-      <c r="E12" s="19" t="n">
-        <v>36</v>
-      </c>
-      <c r="F12" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="G12" s="20" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H12" s="21" t="n">
-        <v>4.218448298406374</v>
-      </c>
-      <c r="I12" s="20" t="n">
-        <v>0.6312409193029385</v>
-      </c>
-      <c r="J12" s="21" t="n">
-        <v>3.275070986639969</v>
-      </c>
-      <c r="K12" s="22" t="n">
-        <v>-0.9433773117664046</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>New-Build OCGT - Visayas 500MW</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>37%–42%</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="n">
-        <v>2031</v>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>20 yrs</t>
-        </is>
-      </c>
-      <c r="E13" s="19" t="n">
-        <v>24</v>
-      </c>
-      <c r="F13" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="G13" s="20" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H13" s="21" t="n">
-        <v>3.918345137513774</v>
-      </c>
-      <c r="I13" s="20" t="n">
-        <v>0.6312409193029385</v>
-      </c>
-      <c r="J13" s="21" t="n">
-        <v>3.382515917162146</v>
-      </c>
-      <c r="K13" s="22" t="n">
-        <v>-0.5358292203516277</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>New-Build Gas Engine - Visayas 500MW</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>37%–42%</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="n">
-        <v>2031</v>
-      </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>20 yrs</t>
-        </is>
-      </c>
-      <c r="E14" s="19" t="n">
-        <v>18</v>
-      </c>
-      <c r="F14" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="G14" s="20" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H14" s="21" t="n">
-        <v>4.591648799911785</v>
-      </c>
-      <c r="I14" s="20" t="n">
-        <v>0.6312409193029385</v>
-      </c>
-      <c r="J14" s="21" t="n">
-        <v>3.692840562983414</v>
-      </c>
-      <c r="K14" s="22" t="n">
-        <v>-0.898808236928371</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="23" t="inlineStr">
-        <is>
-          <t>Cost split (first-year components from the model's Tariff Breakdown tab; capital recovery is the residual), PhP/kWh</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Folder</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Capital recovery, financing, tax, return</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Fixed O&amp;M, G&amp;A, taxes</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Variable O&amp;M</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>Logistics (CLLC)</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>GATP</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>Equity IRR</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>Project IRR</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>Pre-tax WACC</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="24" t="inlineStr">
-        <is>
-          <t>Lot 1 Existing CCGT - Luzon</t>
-        </is>
-      </c>
-      <c r="B19" s="24" t="inlineStr">
-        <is>
-          <t>Fin42</t>
-        </is>
-      </c>
-      <c r="C19" s="25" t="n">
-        <v>1.092450384441328</v>
-      </c>
-      <c r="D19" s="25" t="n">
-        <v>0.4034326540540674</v>
-      </c>
-      <c r="E19" s="25" t="n">
-        <v>0.2477570596165102</v>
-      </c>
-      <c r="F19" s="25" t="n">
-        <v>1.189808934285714</v>
-      </c>
-      <c r="G19" s="26" t="n">
-        <v>2.933449032397625</v>
-      </c>
-      <c r="H19" s="27" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I19" s="27" t="n">
-        <v>0.117964273244369</v>
-      </c>
-      <c r="J19" s="27" t="n">
-        <v>0.112</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="28" t="inlineStr">
-        <is>
-          <t>Lot 1 Existing CCGT - Luzon</t>
-        </is>
-      </c>
-      <c r="B20" s="28" t="inlineStr">
-        <is>
-          <t>Fin90</t>
-        </is>
-      </c>
-      <c r="C20" s="29" t="n">
-        <v>0.686803106143241</v>
-      </c>
-      <c r="D20" s="29" t="n">
-        <v>0.2650999278503244</v>
-      </c>
-      <c r="E20" s="29" t="n">
-        <v>0.1575942059231478</v>
-      </c>
-      <c r="F20" s="29" t="n">
-        <v>0.7571511400000001</v>
-      </c>
-      <c r="G20" s="30" t="n">
-        <v>1.866648379916711</v>
-      </c>
-      <c r="H20" s="31" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I20" s="31" t="n">
-        <v>0.11796383504052</v>
-      </c>
-      <c r="J20" s="31" t="n">
-        <v>0.112</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="24" t="inlineStr">
-        <is>
-          <t>Lot 2 Existing CCGT - Luzon</t>
-        </is>
-      </c>
-      <c r="B21" s="24" t="inlineStr">
-        <is>
-          <t>Fin42</t>
-        </is>
-      </c>
-      <c r="C21" s="25" t="n">
-        <v>1.101312477001886</v>
-      </c>
-      <c r="D21" s="25" t="n">
-        <v>0.393961996408123</v>
-      </c>
-      <c r="E21" s="25" t="n">
-        <v>0.1609421042995921</v>
-      </c>
-      <c r="F21" s="25" t="n">
-        <v>0.7571511399999999</v>
-      </c>
-      <c r="G21" s="26" t="n">
-        <v>2.413367717709602</v>
-      </c>
-      <c r="H21" s="27" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I21" s="27" t="n">
-        <v>0.118056271649446</v>
-      </c>
-      <c r="J21" s="27" t="n">
-        <v>0.112</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="28" t="inlineStr">
-        <is>
-          <t>Lot 2 Existing CCGT - Luzon</t>
-        </is>
-      </c>
-      <c r="B22" s="28" t="inlineStr">
-        <is>
-          <t>Fin90</t>
-        </is>
-      </c>
-      <c r="C22" s="29" t="n">
-        <v>0.6867945111323761</v>
-      </c>
-      <c r="D22" s="29" t="n">
-        <v>0.2650957000786444</v>
-      </c>
-      <c r="E22" s="29" t="n">
-        <v>0.1575753614357395</v>
-      </c>
-      <c r="F22" s="29" t="n">
-        <v>0.7571511400000001</v>
-      </c>
-      <c r="G22" s="30" t="n">
-        <v>1.866616712646755</v>
-      </c>
-      <c r="H22" s="31" t="n">
-        <v>0.139999999999999</v>
-      </c>
-      <c r="I22" s="31" t="n">
-        <v>0.117953638502882</v>
-      </c>
-      <c r="J22" s="31" t="n">
-        <v>0.112</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="24" t="inlineStr">
-        <is>
-          <t>New-Build CCGT - Luzon 1000MW</t>
-        </is>
-      </c>
-      <c r="B23" s="24" t="inlineStr">
-        <is>
-          <t>Fin42</t>
-        </is>
-      </c>
-      <c r="C23" s="25" t="n">
-        <v>2.351118677644035</v>
-      </c>
-      <c r="D23" s="25" t="n">
-        <v>0.4832228920661205</v>
-      </c>
-      <c r="E23" s="25" t="n">
-        <v>0.1676178870999773</v>
-      </c>
-      <c r="F23" s="25" t="n">
-        <v>0.72734204</v>
-      </c>
-      <c r="G23" s="26" t="n">
-        <v>3.729301496810136</v>
-      </c>
-      <c r="H23" s="27" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I23" s="27" t="n">
-        <v>0.11062505734442</v>
-      </c>
-      <c r="J23" s="27" t="n">
-        <v>0.112</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="28" t="inlineStr">
-        <is>
-          <t>New-Build CCGT - Luzon 1000MW</t>
-        </is>
-      </c>
-      <c r="B24" s="28" t="inlineStr">
-        <is>
-          <t>Fin90</t>
-        </is>
-      </c>
-      <c r="C24" s="29" t="n">
-        <v>1.559418896256934</v>
-      </c>
-      <c r="D24" s="29" t="n">
-        <v>0.3370974556820299</v>
-      </c>
-      <c r="E24" s="29" t="n">
-        <v>0.1620512705752893</v>
-      </c>
-      <c r="F24" s="29" t="n">
-        <v>0.72734204</v>
-      </c>
-      <c r="G24" s="30" t="n">
-        <v>2.785909662514258</v>
-      </c>
-      <c r="H24" s="31" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I24" s="31" t="n">
-        <v>0.110578234901689</v>
-      </c>
-      <c r="J24" s="31" t="n">
-        <v>0.112</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="24" t="inlineStr">
-        <is>
-          <t>New-Build OCGT - Luzon 1000MW</t>
-        </is>
-      </c>
-      <c r="B25" s="24" t="inlineStr">
-        <is>
-          <t>Fin42</t>
-        </is>
-      </c>
-      <c r="C25" s="25" t="n">
-        <v>1.303062743657943</v>
-      </c>
-      <c r="D25" s="25" t="n">
-        <v>0.3252636398141273</v>
-      </c>
-      <c r="E25" s="25" t="n">
-        <v>0.3356314407962908</v>
-      </c>
-      <c r="F25" s="25" t="n">
-        <v>1.16851672</v>
-      </c>
-      <c r="G25" s="26" t="n">
-        <v>3.132474544268364</v>
-      </c>
-      <c r="H25" s="27" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I25" s="27" t="n">
-        <v>0.113877294670823</v>
-      </c>
-      <c r="J25" s="27" t="n">
-        <v>0.112</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="28" t="inlineStr">
-        <is>
-          <t>New-Build OCGT - Luzon 1000MW</t>
-        </is>
-      </c>
-      <c r="B26" s="28" t="inlineStr">
-        <is>
-          <t>Fin90</t>
-        </is>
-      </c>
-      <c r="C26" s="29" t="n">
-        <v>0.8585413874907835</v>
-      </c>
-      <c r="D26" s="29" t="n">
-        <v>0.2372535583269379</v>
-      </c>
-      <c r="E26" s="29" t="n">
-        <v>0.3323197606614079</v>
-      </c>
-      <c r="F26" s="29" t="n">
-        <v>1.16851672</v>
-      </c>
-      <c r="G26" s="30" t="n">
-        <v>2.596631426479127</v>
-      </c>
-      <c r="H26" s="31" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I26" s="31" t="n">
-        <v>0.113739743325391</v>
-      </c>
-      <c r="J26" s="31" t="n">
-        <v>0.112</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="24" t="inlineStr">
-        <is>
-          <t>New-Build Gas Engine - Luzon 1000MW</t>
-        </is>
-      </c>
-      <c r="B27" s="24" t="inlineStr">
-        <is>
-          <t>Fin42</t>
-        </is>
-      </c>
-      <c r="C27" s="25" t="n">
-        <v>2.169506822395788</v>
-      </c>
-      <c r="D27" s="25" t="n">
-        <v>0.5362145335743013</v>
-      </c>
-      <c r="E27" s="25" t="n">
-        <v>0.2905156941425279</v>
-      </c>
-      <c r="F27" s="25" t="n">
-        <v>0.9538912000000001</v>
-      </c>
-      <c r="G27" s="26" t="n">
-        <v>3.950128250112614</v>
-      </c>
-      <c r="H27" s="27" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I27" s="27" t="n">
-        <v>0.112752607467852</v>
-      </c>
-      <c r="J27" s="27" t="n">
-        <v>0.112</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="28" t="inlineStr">
-        <is>
-          <t>New-Build Gas Engine - Luzon 1000MW</t>
-        </is>
-      </c>
-      <c r="B28" s="28" t="inlineStr">
-        <is>
-          <t>Fin90</t>
-        </is>
-      </c>
-      <c r="C28" s="29" t="n">
-        <v>1.436560349475735</v>
-      </c>
-      <c r="D28" s="29" t="n">
-        <v>0.3758379796110337</v>
-      </c>
-      <c r="E28" s="29" t="n">
-        <v>0.2850169558760416</v>
-      </c>
-      <c r="F28" s="29" t="n">
-        <v>0.9538911999999999</v>
-      </c>
-      <c r="G28" s="30" t="n">
-        <v>3.051306484962811</v>
-      </c>
-      <c r="H28" s="31" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I28" s="31" t="n">
-        <v>0.112683434109201</v>
-      </c>
-      <c r="J28" s="31" t="n">
-        <v>0.112</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="24" t="inlineStr">
-        <is>
-          <t>New-Build CCGT - Visayas 440MW</t>
-        </is>
-      </c>
-      <c r="B29" s="24" t="inlineStr">
-        <is>
-          <t>Fin42</t>
-        </is>
-      </c>
-      <c r="C29" s="25" t="n">
-        <v>2.342750152410311</v>
-      </c>
-      <c r="D29" s="25" t="n">
-        <v>0.4879500088999101</v>
-      </c>
-      <c r="E29" s="25" t="n">
-        <v>0.1818797617351213</v>
-      </c>
-      <c r="F29" s="25" t="n">
-        <v>1.20585654</v>
-      </c>
-      <c r="G29" s="26" t="n">
-        <v>4.218436463045343</v>
-      </c>
-      <c r="H29" s="27" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I29" s="27" t="n">
-        <v>0.110567285612016</v>
-      </c>
-      <c r="J29" s="27" t="n">
-        <v>0.112</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="28" t="inlineStr">
-        <is>
-          <t>New-Build CCGT - Visayas 440MW</t>
-        </is>
-      </c>
-      <c r="B30" s="28" t="inlineStr">
-        <is>
-          <t>Fin90</t>
-        </is>
-      </c>
-      <c r="C30" s="29" t="n">
-        <v>1.551056777747667</v>
-      </c>
-      <c r="D30" s="29" t="n">
-        <v>0.3418267784291173</v>
-      </c>
-      <c r="E30" s="29" t="n">
-        <v>0.1763230157334588</v>
-      </c>
-      <c r="F30" s="29" t="n">
-        <v>1.20585654</v>
-      </c>
-      <c r="G30" s="30" t="n">
-        <v>3.275063111910242</v>
-      </c>
-      <c r="H30" s="31" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I30" s="31" t="n">
-        <v>0.110493253967895</v>
-      </c>
-      <c r="J30" s="31" t="n">
-        <v>0.112</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="24" t="inlineStr">
-        <is>
-          <t>New-Build OCGT - Visayas 440MW</t>
-        </is>
-      </c>
-      <c r="B31" s="24" t="inlineStr">
-        <is>
-          <t>Fin42</t>
-        </is>
-      </c>
-      <c r="C31" s="25" t="n">
-        <v>1.289632292229853</v>
-      </c>
-      <c r="D31" s="25" t="n">
-        <v>0.3328620063405143</v>
-      </c>
-      <c r="E31" s="25" t="n">
-        <v>0.3585617930362333</v>
-      </c>
-      <c r="F31" s="25" t="n">
-        <v>1.93727772</v>
-      </c>
-      <c r="G31" s="26" t="n">
-        <v>3.9183338116066</v>
-      </c>
-      <c r="H31" s="27" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I31" s="27" t="n">
-        <v>0.113723206811988</v>
-      </c>
-      <c r="J31" s="27" t="n">
-        <v>0.112</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="28" t="inlineStr">
-        <is>
-          <t>New-Build OCGT - Visayas 440MW</t>
-        </is>
-      </c>
-      <c r="B32" s="28" t="inlineStr">
-        <is>
-          <t>Fin90</t>
-        </is>
-      </c>
-      <c r="C32" s="29" t="n">
-        <v>0.8451165222270034</v>
-      </c>
-      <c r="D32" s="29" t="n">
-        <v>0.2448541361925196</v>
-      </c>
-      <c r="E32" s="29" t="n">
-        <v>0.3552600029811286</v>
-      </c>
-      <c r="F32" s="29" t="n">
-        <v>1.93727772</v>
-      </c>
-      <c r="G32" s="30" t="n">
-        <v>3.382508381400652</v>
-      </c>
-      <c r="H32" s="31" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I32" s="31" t="n">
-        <v>0.113508925018704</v>
-      </c>
-      <c r="J32" s="31" t="n">
-        <v>0.112</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="24" t="inlineStr">
-        <is>
-          <t>New-Build Gas Engine - Visayas 440MW</t>
-        </is>
-      </c>
-      <c r="B33" s="24" t="inlineStr">
-        <is>
-          <t>Fin42</t>
-        </is>
-      </c>
-      <c r="C33" s="25" t="n">
-        <v>2.158541634275416</v>
-      </c>
-      <c r="D33" s="25" t="n">
-        <v>0.5424160637304091</v>
-      </c>
-      <c r="E33" s="25" t="n">
-        <v>0.3092288929880294</v>
-      </c>
-      <c r="F33" s="25" t="n">
-        <v>1.5814512</v>
-      </c>
-      <c r="G33" s="26" t="n">
-        <v>4.591637790993857</v>
-      </c>
-      <c r="H33" s="27" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I33" s="27" t="n">
-        <v>0.11267476417135</v>
-      </c>
-      <c r="J33" s="27" t="n">
-        <v>0.112</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="28" t="inlineStr">
-        <is>
-          <t>New-Build Gas Engine - Visayas 440MW</t>
-        </is>
-      </c>
-      <c r="B34" s="28" t="inlineStr">
-        <is>
-          <t>Fin90</t>
-        </is>
-      </c>
-      <c r="C34" s="29" t="n">
-        <v>1.425600260915937</v>
-      </c>
-      <c r="D34" s="29" t="n">
-        <v>0.382041722736336</v>
-      </c>
-      <c r="E34" s="29" t="n">
-        <v>0.303740054087954</v>
-      </c>
-      <c r="F34" s="29" t="n">
-        <v>1.5814512</v>
-      </c>
-      <c r="G34" s="30" t="n">
-        <v>3.692833237740226</v>
-      </c>
-      <c r="H34" s="31" t="n">
-        <v>0.140000002983082</v>
-      </c>
-      <c r="I34" s="31" t="n">
-        <v>0.112568027450008</v>
-      </c>
-      <c r="J34" s="31" t="n">
-        <v>0.112</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="24" t="inlineStr">
-        <is>
-          <t>New-Build CCGT - Visayas 500MW</t>
-        </is>
-      </c>
-      <c r="B35" s="24" t="inlineStr">
-        <is>
-          <t>Fin42</t>
-        </is>
-      </c>
-      <c r="C35" s="25" t="n">
-        <v>2.34275425475286</v>
-      </c>
-      <c r="D35" s="25" t="n">
-        <v>0.4879514214321875</v>
-      </c>
-      <c r="E35" s="25" t="n">
-        <v>0.1818860822213251</v>
-      </c>
-      <c r="F35" s="25" t="n">
-        <v>1.20585654</v>
-      </c>
-      <c r="G35" s="26" t="n">
-        <v>4.218448298406374</v>
-      </c>
-      <c r="H35" s="27" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I35" s="27" t="n">
-        <v>0.11056824170446</v>
-      </c>
-      <c r="J35" s="27" t="n">
-        <v>0.112</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="28" t="inlineStr">
-        <is>
-          <t>New-Build CCGT - Visayas 500MW</t>
-        </is>
-      </c>
-      <c r="B36" s="28" t="inlineStr">
-        <is>
-          <t>Fin90</t>
-        </is>
-      </c>
-      <c r="C36" s="29" t="n">
-        <v>1.551059507266337</v>
-      </c>
-      <c r="D36" s="29" t="n">
-        <v>0.3418277182660929</v>
-      </c>
-      <c r="E36" s="29" t="n">
-        <v>0.176327221107542</v>
-      </c>
-      <c r="F36" s="29" t="n">
-        <v>1.20585654</v>
-      </c>
-      <c r="G36" s="30" t="n">
-        <v>3.275070986639969</v>
-      </c>
-      <c r="H36" s="31" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I36" s="31" t="n">
-        <v>0.110494212971933</v>
-      </c>
-      <c r="J36" s="31" t="n">
-        <v>0.112</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="24" t="inlineStr">
-        <is>
-          <t>New-Build OCGT - Visayas 500MW</t>
-        </is>
-      </c>
-      <c r="B37" s="24" t="inlineStr">
-        <is>
-          <t>Fin42</t>
-        </is>
-      </c>
-      <c r="C37" s="25" t="n">
-        <v>1.289635869121561</v>
-      </c>
-      <c r="D37" s="25" t="n">
-        <v>0.3328634223468854</v>
-      </c>
-      <c r="E37" s="25" t="n">
-        <v>0.3585681260453282</v>
-      </c>
-      <c r="F37" s="25" t="n">
-        <v>1.93727772</v>
-      </c>
-      <c r="G37" s="26" t="n">
-        <v>3.918345137513774</v>
-      </c>
-      <c r="H37" s="27" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I37" s="27" t="n">
-        <v>0.113724995258009</v>
-      </c>
-      <c r="J37" s="27" t="n">
-        <v>0.112</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="28" t="inlineStr">
-        <is>
-          <t>New-Build OCGT - Visayas 500MW</t>
-        </is>
-      </c>
-      <c r="B38" s="28" t="inlineStr">
-        <is>
-          <t>Fin90</t>
-        </is>
-      </c>
-      <c r="C38" s="29" t="n">
-        <v>0.8451189021337423</v>
-      </c>
-      <c r="D38" s="29" t="n">
-        <v>0.2448550783410045</v>
-      </c>
-      <c r="E38" s="29" t="n">
-        <v>0.3552642166874009</v>
-      </c>
-      <c r="F38" s="29" t="n">
-        <v>1.93727772</v>
-      </c>
-      <c r="G38" s="30" t="n">
-        <v>3.382515917162146</v>
-      </c>
-      <c r="H38" s="31" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I38" s="31" t="n">
-        <v>0.113510730525212</v>
-      </c>
-      <c r="J38" s="31" t="n">
-        <v>0.112</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="24" t="inlineStr">
-        <is>
-          <t>New-Build Gas Engine - Visayas 500MW</t>
-        </is>
-      </c>
-      <c r="B39" s="24" t="inlineStr">
-        <is>
-          <t>Fin42</t>
-        </is>
-      </c>
-      <c r="C39" s="25" t="n">
-        <v>2.158544887307337</v>
-      </c>
-      <c r="D39" s="25" t="n">
-        <v>0.5424174806607494</v>
-      </c>
-      <c r="E39" s="25" t="n">
-        <v>0.3092352319437006</v>
-      </c>
-      <c r="F39" s="25" t="n">
-        <v>1.5814512</v>
-      </c>
-      <c r="G39" s="26" t="n">
-        <v>4.591648799911785</v>
-      </c>
-      <c r="H39" s="27" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I39" s="27" t="n">
-        <v>0.112675794777446</v>
-      </c>
-      <c r="J39" s="27" t="n">
-        <v>0.112</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="28" t="inlineStr">
-        <is>
-          <t>New-Build Gas Engine - Visayas 500MW</t>
-        </is>
-      </c>
-      <c r="B40" s="28" t="inlineStr">
-        <is>
-          <t>Fin90</t>
-        </is>
-      </c>
-      <c r="C40" s="29" t="n">
-        <v>1.425602425729216</v>
-      </c>
-      <c r="D40" s="29" t="n">
-        <v>0.3820426655033868</v>
-      </c>
-      <c r="E40" s="29" t="n">
-        <v>0.3037442717508103</v>
-      </c>
-      <c r="F40" s="29" t="n">
-        <v>1.5814512</v>
-      </c>
-      <c r="G40" s="30" t="n">
-        <v>3.692840562983414</v>
-      </c>
-      <c r="H40" s="31" t="n">
-        <v>0.140000003043171</v>
-      </c>
-      <c r="I40" s="31" t="n">
-        <v>0.11256906283893</v>
-      </c>
-      <c r="J40" s="31" t="n">
-        <v>0.112</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AA80"/>
+  <dimension ref="A1:AA81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12018,6 +13384,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
@@ -15093,7 +16460,7 @@
       </c>
       <c r="B40" s="44" t="inlineStr">
         <is>
-          <t>Variable O&amp;M incl. logistics (model input)</t>
+          <t>Variable O&amp;M excl. logistics (model input)</t>
         </is>
       </c>
       <c r="C40" s="45" t="inlineStr">
@@ -15108,74 +16475,74 @@
       </c>
       <c r="E40" s="46" t="inlineStr">
         <is>
-          <t>(VOM + CLLC x heat rate / 1,000) x 8,760 x energy CF / 1,000.</t>
-        </is>
-      </c>
-      <c r="F40" s="47" t="n">
-        <v>81.31820399999998</v>
-      </c>
-      <c r="G40" s="47" t="n">
-        <v>51.74794799999999</v>
-      </c>
-      <c r="H40" s="47" t="n">
-        <v>50.000328</v>
-      </c>
-      <c r="I40" s="47" t="n">
-        <v>85.06310400000001</v>
-      </c>
-      <c r="J40" s="47" t="n">
-        <v>69.90480000000001</v>
-      </c>
-      <c r="K40" s="47" t="n">
-        <v>78.05422799999999</v>
-      </c>
-      <c r="L40" s="47" t="n">
-        <v>130.133304</v>
-      </c>
-      <c r="M40" s="47" t="n">
-        <v>106.6968</v>
-      </c>
-      <c r="N40" s="47" t="n">
-        <v>78.05422799999999</v>
-      </c>
-      <c r="O40" s="47" t="n">
-        <v>130.133304</v>
-      </c>
-      <c r="P40" s="47" t="n">
-        <v>106.6968</v>
-      </c>
-      <c r="Q40" s="47" t="n">
-        <v>82.30442304191916</v>
-      </c>
-      <c r="R40" s="47" t="n">
-        <v>82.30442304191916</v>
-      </c>
-      <c r="S40" s="47" t="n">
-        <v>75.14822145754394</v>
-      </c>
-      <c r="T40" s="47" t="n">
-        <v>127.8459808755273</v>
-      </c>
-      <c r="U40" s="47" t="n">
-        <v>105.0637386087811</v>
-      </c>
-      <c r="V40" s="47" t="n">
-        <v>117.3119586623837</v>
-      </c>
-      <c r="W40" s="47" t="n">
-        <v>195.5844439259256</v>
-      </c>
-      <c r="X40" s="47" t="n">
-        <v>160.3604431397185</v>
-      </c>
-      <c r="Y40" s="47" t="n">
-        <v>117.3119586623837</v>
-      </c>
-      <c r="Z40" s="47" t="n">
-        <v>195.5844439259256</v>
-      </c>
-      <c r="AA40" s="47" t="n">
-        <v>160.3604431397185</v>
+          <t>VOM x 8,760 x energy CF / 1,000. Logistics (CLLC) removed: it is paid through the Fuel Cost (GAIR Sec. 8.6, decision of 19 Oct 2026).</t>
+        </is>
+      </c>
+      <c r="F40" s="107" t="n">
+        <v>11.5632</v>
+      </c>
+      <c r="G40" s="107" t="n">
+        <v>7.3584</v>
+      </c>
+      <c r="H40" s="107" t="n">
+        <v>7.3584</v>
+      </c>
+      <c r="I40" s="107" t="n">
+        <v>16.5564</v>
+      </c>
+      <c r="J40" s="107" t="n">
+        <v>13.98096</v>
+      </c>
+      <c r="K40" s="107" t="n">
+        <v>7.358400000000002</v>
+      </c>
+      <c r="L40" s="107" t="n">
+        <v>16.5564</v>
+      </c>
+      <c r="M40" s="107" t="n">
+        <v>13.98096</v>
+      </c>
+      <c r="N40" s="107" t="n">
+        <v>7.358400000000002</v>
+      </c>
+      <c r="O40" s="107" t="n">
+        <v>16.5564</v>
+      </c>
+      <c r="P40" s="107" t="n">
+        <v>13.98096</v>
+      </c>
+      <c r="Q40" s="107" t="n">
+        <v>11.70343733265825</v>
+      </c>
+      <c r="R40" s="107" t="n">
+        <v>11.70343733265825</v>
+      </c>
+      <c r="S40" s="107" t="n">
+        <v>11.05934090618748</v>
+      </c>
+      <c r="T40" s="107" t="n">
+        <v>24.88351703892183</v>
+      </c>
+      <c r="U40" s="107" t="n">
+        <v>21.01274772175622</v>
+      </c>
+      <c r="V40" s="107" t="n">
+        <v>11.05934090618748</v>
+      </c>
+      <c r="W40" s="107" t="n">
+        <v>24.88351703892184</v>
+      </c>
+      <c r="X40" s="107" t="n">
+        <v>21.01274772175622</v>
+      </c>
+      <c r="Y40" s="107" t="n">
+        <v>11.05934090618748</v>
+      </c>
+      <c r="Z40" s="107" t="n">
+        <v>24.88351703892184</v>
+      </c>
+      <c r="AA40" s="107" t="n">
+        <v>21.01274772175622</v>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
@@ -17982,7 +19349,7 @@
       </c>
       <c r="B73" s="55" t="inlineStr">
         <is>
-          <t>GAT Price (excl. fuel)</t>
+          <t>GAT Price = CRF + OM (excl. fuel and CLLC)</t>
         </is>
       </c>
       <c r="C73" s="45" t="inlineStr">
@@ -17997,74 +19364,74 @@
       </c>
       <c r="E73" s="46" t="inlineStr">
         <is>
-          <t>Solved: equity NPV = 0 at Re (Goal Seek G28 = 0 by changing F30). Main result.</t>
-        </is>
-      </c>
-      <c r="F73" s="60" t="n">
-        <v>2.933449032397625</v>
-      </c>
-      <c r="G73" s="60" t="n">
-        <v>2.413367717709602</v>
-      </c>
-      <c r="H73" s="60" t="n">
-        <v>3.729301496810136</v>
-      </c>
-      <c r="I73" s="60" t="n">
-        <v>3.132474544268364</v>
-      </c>
-      <c r="J73" s="60" t="n">
-        <v>3.950128250112614</v>
-      </c>
-      <c r="K73" s="60" t="n">
-        <v>4.218436463045343</v>
-      </c>
-      <c r="L73" s="60" t="n">
-        <v>3.9183338116066</v>
-      </c>
-      <c r="M73" s="60" t="n">
-        <v>4.591637790993857</v>
-      </c>
-      <c r="N73" s="60" t="n">
-        <v>4.218448298406374</v>
-      </c>
-      <c r="O73" s="60" t="n">
-        <v>3.918345137513774</v>
-      </c>
-      <c r="P73" s="60" t="n">
-        <v>4.591648799911785</v>
-      </c>
-      <c r="Q73" s="60" t="n">
-        <v>1.866648379916711</v>
-      </c>
-      <c r="R73" s="60" t="n">
-        <v>1.866616712646755</v>
-      </c>
-      <c r="S73" s="60" t="n">
-        <v>2.785909662514258</v>
-      </c>
-      <c r="T73" s="60" t="n">
-        <v>2.596631426479127</v>
-      </c>
-      <c r="U73" s="60" t="n">
-        <v>3.051306484962811</v>
-      </c>
-      <c r="V73" s="60" t="n">
-        <v>3.275063111910242</v>
-      </c>
-      <c r="W73" s="60" t="n">
-        <v>3.382508381400652</v>
-      </c>
-      <c r="X73" s="60" t="n">
-        <v>3.692833237740226</v>
-      </c>
-      <c r="Y73" s="60" t="n">
-        <v>3.275070986639969</v>
-      </c>
-      <c r="Z73" s="60" t="n">
-        <v>3.382515917162146</v>
-      </c>
-      <c r="AA73" s="60" t="n">
-        <v>3.692840562983414</v>
+          <t>Re-solved 20 Oct 2026 without the CLLC: equity NPV = 0 at Re (Goal Seek G28 = 0 by changing F30).</t>
+        </is>
+      </c>
+      <c r="F73" s="108" t="n">
+        <v>1.717095361163876</v>
+      </c>
+      <c r="G73" s="108" t="n">
+        <v>1.639324472379034</v>
+      </c>
+      <c r="H73" s="108" t="n">
+        <v>2.985732394996519</v>
+      </c>
+      <c r="I73" s="108" t="n">
+        <v>1.937888118403868</v>
+      </c>
+      <c r="J73" s="108" t="n">
+        <v>2.974955657570167</v>
+      </c>
+      <c r="K73" s="108" t="n">
+        <v>2.985677162670138</v>
+      </c>
+      <c r="L73" s="108" t="n">
+        <v>1.937835263462828</v>
+      </c>
+      <c r="M73" s="108" t="n">
+        <v>2.974904282305064</v>
+      </c>
+      <c r="N73" s="108" t="n">
+        <v>2.985688998031168</v>
+      </c>
+      <c r="O73" s="108" t="n">
+        <v>1.937846589370002</v>
+      </c>
+      <c r="P73" s="108" t="n">
+        <v>2.974915291222991</v>
+      </c>
+      <c r="Q73" s="108" t="n">
+        <v>1.092605134586144</v>
+      </c>
+      <c r="R73" s="108" t="n">
+        <v>1.092573467316189</v>
+      </c>
+      <c r="S73" s="108" t="n">
+        <v>2.042340560700642</v>
+      </c>
+      <c r="T73" s="108" t="n">
+        <v>1.402045000614633</v>
+      </c>
+      <c r="U73" s="108" t="n">
+        <v>2.076133892420363</v>
+      </c>
+      <c r="V73" s="108" t="n">
+        <v>2.042303811535037</v>
+      </c>
+      <c r="W73" s="108" t="n">
+        <v>1.402009833256881</v>
+      </c>
+      <c r="X73" s="108" t="n">
+        <v>2.076099709574031</v>
+      </c>
+      <c r="Y73" s="108" t="n">
+        <v>2.042311686264764</v>
+      </c>
+      <c r="Z73" s="108" t="n">
+        <v>1.402017369018373</v>
+      </c>
+      <c r="AA73" s="108" t="n">
+        <v>2.076107034424793</v>
       </c>
     </row>
     <row r="74" ht="30" customHeight="1">
@@ -18093,71 +19460,71 @@
           <t>Tariff Breakdown A4 x PhP/US$.</t>
         </is>
       </c>
-      <c r="F74" s="61" t="n">
-        <v>1.092450384441328</v>
-      </c>
-      <c r="G74" s="61" t="n">
-        <v>1.101312477001886</v>
-      </c>
-      <c r="H74" s="61" t="n">
-        <v>2.351118677644035</v>
-      </c>
-      <c r="I74" s="61" t="n">
-        <v>1.303062743657943</v>
-      </c>
-      <c r="J74" s="61" t="n">
-        <v>2.169506822395788</v>
-      </c>
-      <c r="K74" s="61" t="n">
-        <v>2.342750152410311</v>
-      </c>
-      <c r="L74" s="61" t="n">
-        <v>1.289632292229853</v>
-      </c>
-      <c r="M74" s="61" t="n">
-        <v>2.158541634275416</v>
-      </c>
-      <c r="N74" s="61" t="n">
-        <v>2.34275425475286</v>
-      </c>
-      <c r="O74" s="61" t="n">
-        <v>1.289635869121561</v>
-      </c>
-      <c r="P74" s="61" t="n">
-        <v>2.158544887307337</v>
-      </c>
-      <c r="Q74" s="61" t="n">
-        <v>0.686803106143241</v>
-      </c>
-      <c r="R74" s="61" t="n">
-        <v>0.6867945111323761</v>
-      </c>
-      <c r="S74" s="61" t="n">
-        <v>1.559418896256934</v>
-      </c>
-      <c r="T74" s="61" t="n">
-        <v>0.8585413874907835</v>
-      </c>
-      <c r="U74" s="61" t="n">
-        <v>1.436560349475735</v>
-      </c>
-      <c r="V74" s="61" t="n">
-        <v>1.551056777747667</v>
-      </c>
-      <c r="W74" s="61" t="n">
-        <v>0.8451165222270034</v>
-      </c>
-      <c r="X74" s="61" t="n">
-        <v>1.425600260915937</v>
-      </c>
-      <c r="Y74" s="61" t="n">
-        <v>1.551059507266337</v>
-      </c>
-      <c r="Z74" s="61" t="n">
-        <v>0.8451189021337423</v>
-      </c>
-      <c r="AA74" s="61" t="n">
-        <v>1.425602425729216</v>
+      <c r="F74" s="109" t="n">
+        <v>1.113210815556322</v>
+      </c>
+      <c r="G74" s="109" t="n">
+        <v>1.114523660438698</v>
+      </c>
+      <c r="H74" s="109" t="n">
+        <v>2.363809735748692</v>
+      </c>
+      <c r="I74" s="109" t="n">
+        <v>1.323451656678538</v>
+      </c>
+      <c r="J74" s="109" t="n">
+        <v>2.18615083302484</v>
+      </c>
+      <c r="K74" s="109" t="n">
+        <v>2.363790590846974</v>
+      </c>
+      <c r="L74" s="109" t="n">
+        <v>1.323434963816624</v>
+      </c>
+      <c r="M74" s="109" t="n">
+        <v>2.186135651897272</v>
+      </c>
+      <c r="N74" s="109" t="n">
+        <v>2.363794693189526</v>
+      </c>
+      <c r="O74" s="109" t="n">
+        <v>1.323438540708331</v>
+      </c>
+      <c r="P74" s="109" t="n">
+        <v>2.18613890492919</v>
+      </c>
+      <c r="Q74" s="109" t="n">
+        <v>0.7000142895800525</v>
+      </c>
+      <c r="R74" s="109" t="n">
+        <v>0.7000056945691875</v>
+      </c>
+      <c r="S74" s="109" t="n">
+        <v>1.572109954361591</v>
+      </c>
+      <c r="T74" s="109" t="n">
+        <v>0.878930300511378</v>
+      </c>
+      <c r="U74" s="109" t="n">
+        <v>1.453204360104791</v>
+      </c>
+      <c r="V74" s="109" t="n">
+        <v>1.572097216184333</v>
+      </c>
+      <c r="W74" s="109" t="n">
+        <v>0.8789191938137773</v>
+      </c>
+      <c r="X74" s="109" t="n">
+        <v>1.453194259248868</v>
+      </c>
+      <c r="Y74" s="109" t="n">
+        <v>1.572099945702999</v>
+      </c>
+      <c r="Z74" s="109" t="n">
+        <v>0.8789215737205135</v>
+      </c>
+      <c r="AA74" s="109" t="n">
+        <v>1.453196423673517</v>
       </c>
     </row>
     <row r="75" ht="30" customHeight="1">
@@ -18186,71 +19553,71 @@
           <t>Tariff Breakdown A5 x PhP/US$.</t>
         </is>
       </c>
-      <c r="F75" s="61" t="n">
-        <v>0.4034326540540674</v>
-      </c>
-      <c r="G75" s="61" t="n">
-        <v>0.393961996408123</v>
-      </c>
-      <c r="H75" s="61" t="n">
-        <v>0.4832228920661205</v>
-      </c>
-      <c r="I75" s="61" t="n">
-        <v>0.3252636398141273</v>
-      </c>
-      <c r="J75" s="61" t="n">
-        <v>0.5362145335743013</v>
-      </c>
-      <c r="K75" s="61" t="n">
-        <v>0.4879500088999101</v>
-      </c>
-      <c r="L75" s="61" t="n">
-        <v>0.3328620063405143</v>
-      </c>
-      <c r="M75" s="61" t="n">
-        <v>0.5424160637304091</v>
-      </c>
-      <c r="N75" s="61" t="n">
-        <v>0.4879514214321875</v>
-      </c>
-      <c r="O75" s="61" t="n">
-        <v>0.3328634223468854</v>
-      </c>
-      <c r="P75" s="61" t="n">
-        <v>0.5424174806607494</v>
-      </c>
-      <c r="Q75" s="61" t="n">
-        <v>0.2650999278503244</v>
-      </c>
-      <c r="R75" s="61" t="n">
-        <v>0.2650957000786444</v>
-      </c>
-      <c r="S75" s="61" t="n">
-        <v>0.3370974556820299</v>
-      </c>
-      <c r="T75" s="61" t="n">
-        <v>0.2372535583269379</v>
-      </c>
-      <c r="U75" s="61" t="n">
-        <v>0.3758379796110337</v>
-      </c>
-      <c r="V75" s="61" t="n">
-        <v>0.3418267784291173</v>
-      </c>
-      <c r="W75" s="61" t="n">
-        <v>0.2448541361925196</v>
-      </c>
-      <c r="X75" s="61" t="n">
-        <v>0.382041722736336</v>
-      </c>
-      <c r="Y75" s="61" t="n">
-        <v>0.3418277182660929</v>
-      </c>
-      <c r="Z75" s="61" t="n">
-        <v>0.2448550783410045</v>
-      </c>
-      <c r="AA75" s="61" t="n">
-        <v>0.3820426655033868</v>
+      <c r="F75" s="109" t="n">
+        <v>0.3916624593116242</v>
+      </c>
+      <c r="G75" s="109" t="n">
+        <v>0.3864718724811137</v>
+      </c>
+      <c r="H75" s="109" t="n">
+        <v>0.476027654907891</v>
+      </c>
+      <c r="I75" s="109" t="n">
+        <v>0.3137040784779557</v>
+      </c>
+      <c r="J75" s="109" t="n">
+        <v>0.5267781569733451</v>
+      </c>
+      <c r="K75" s="109" t="n">
+        <v>0.4760210630849508</v>
+      </c>
+      <c r="L75" s="109" t="n">
+        <v>0.3136974704410716</v>
+      </c>
+      <c r="M75" s="109" t="n">
+        <v>0.5267715446288235</v>
+      </c>
+      <c r="N75" s="109" t="n">
+        <v>0.4760224756172284</v>
+      </c>
+      <c r="O75" s="109" t="n">
+        <v>0.3136988864474425</v>
+      </c>
+      <c r="P75" s="109" t="n">
+        <v>0.5267729615591632</v>
+      </c>
+      <c r="Q75" s="109" t="n">
+        <v>0.257609803923315</v>
+      </c>
+      <c r="R75" s="109" t="n">
+        <v>0.2576055761516349</v>
+      </c>
+      <c r="S75" s="109" t="n">
+        <v>0.3299022185238005</v>
+      </c>
+      <c r="T75" s="109" t="n">
+        <v>0.2256939969907663</v>
+      </c>
+      <c r="U75" s="109" t="n">
+        <v>0.3664016030100771</v>
+      </c>
+      <c r="V75" s="109" t="n">
+        <v>0.3298978326141578</v>
+      </c>
+      <c r="W75" s="109" t="n">
+        <v>0.2256896002930769</v>
+      </c>
+      <c r="X75" s="109" t="n">
+        <v>0.3663972034462749</v>
+      </c>
+      <c r="Y75" s="109" t="n">
+        <v>0.3298987724511336</v>
+      </c>
+      <c r="Z75" s="109" t="n">
+        <v>0.2256905424415618</v>
+      </c>
+      <c r="AA75" s="109" t="n">
+        <v>0.366398146209528</v>
       </c>
     </row>
     <row r="76" ht="30" customHeight="1">
@@ -18261,7 +19628,7 @@
       </c>
       <c r="B76" s="44" t="inlineStr">
         <is>
-          <t>Variable O&amp;M + logistics (first year)</t>
+          <t>Variable O&amp;M, excl. logistics (first year)</t>
         </is>
       </c>
       <c r="C76" s="45" t="inlineStr">
@@ -18276,167 +19643,167 @@
       </c>
       <c r="E76" s="46" t="inlineStr">
         <is>
-          <t>Tariff Breakdown A9 x PhP/US$.</t>
-        </is>
-      </c>
-      <c r="F76" s="61" t="n">
-        <v>1.437565993902224</v>
-      </c>
-      <c r="G76" s="61" t="n">
-        <v>0.918093244299592</v>
-      </c>
-      <c r="H76" s="61" t="n">
-        <v>0.8949599270999773</v>
-      </c>
-      <c r="I76" s="61" t="n">
-        <v>1.504148160796291</v>
-      </c>
-      <c r="J76" s="61" t="n">
-        <v>1.244406894142528</v>
-      </c>
-      <c r="K76" s="61" t="n">
-        <v>1.387736301735121</v>
-      </c>
-      <c r="L76" s="61" t="n">
-        <v>2.295839513036233</v>
-      </c>
-      <c r="M76" s="61" t="n">
-        <v>1.890680092988029</v>
-      </c>
-      <c r="N76" s="61" t="n">
-        <v>1.387742622221325</v>
-      </c>
-      <c r="O76" s="61" t="n">
-        <v>2.295845846045328</v>
-      </c>
-      <c r="P76" s="61" t="n">
-        <v>1.8906864319437</v>
-      </c>
-      <c r="Q76" s="61" t="n">
-        <v>0.9147453459231478</v>
-      </c>
-      <c r="R76" s="61" t="n">
-        <v>0.9147265014357395</v>
-      </c>
-      <c r="S76" s="61" t="n">
-        <v>0.8893933105752894</v>
-      </c>
-      <c r="T76" s="61" t="n">
-        <v>1.500836480661408</v>
-      </c>
-      <c r="U76" s="61" t="n">
-        <v>1.238908155876042</v>
-      </c>
-      <c r="V76" s="61" t="n">
-        <v>1.382179555733458</v>
-      </c>
-      <c r="W76" s="61" t="n">
-        <v>2.292537722981129</v>
-      </c>
-      <c r="X76" s="61" t="n">
-        <v>1.885191254087954</v>
-      </c>
-      <c r="Y76" s="61" t="n">
-        <v>1.382183761107542</v>
-      </c>
-      <c r="Z76" s="61" t="n">
-        <v>2.292541936687401</v>
-      </c>
-      <c r="AA76" s="61" t="n">
-        <v>1.88519547175081</v>
+          <t>Tariff Breakdown (A8 + A9) x PhP/US$.</t>
+        </is>
+      </c>
+      <c r="F76" s="109" t="n">
+        <v>0.2122220862959301</v>
+      </c>
+      <c r="G76" s="109" t="n">
+        <v>0.1383289394592217</v>
+      </c>
+      <c r="H76" s="109" t="n">
+        <v>0.1458950043399359</v>
+      </c>
+      <c r="I76" s="109" t="n">
+        <v>0.3007323832473738</v>
+      </c>
+      <c r="J76" s="109" t="n">
+        <v>0.262026667571982</v>
+      </c>
+      <c r="K76" s="109" t="n">
+        <v>0.1458655087382131</v>
+      </c>
+      <c r="L76" s="109" t="n">
+        <v>0.300702829205132</v>
+      </c>
+      <c r="M76" s="109" t="n">
+        <v>0.2619970857789685</v>
+      </c>
+      <c r="N76" s="109" t="n">
+        <v>0.1458718292244134</v>
+      </c>
+      <c r="O76" s="109" t="n">
+        <v>0.3007091622142286</v>
+      </c>
+      <c r="P76" s="109" t="n">
+        <v>0.2620034247346381</v>
+      </c>
+      <c r="Q76" s="109" t="n">
+        <v>0.1349810410827766</v>
+      </c>
+      <c r="R76" s="109" t="n">
+        <v>0.1349621965953666</v>
+      </c>
+      <c r="S76" s="109" t="n">
+        <v>0.1403283878152508</v>
+      </c>
+      <c r="T76" s="109" t="n">
+        <v>0.2974207031124884</v>
+      </c>
+      <c r="U76" s="109" t="n">
+        <v>0.2565279293054955</v>
+      </c>
+      <c r="V76" s="109" t="n">
+        <v>0.1403087627365452</v>
+      </c>
+      <c r="W76" s="109" t="n">
+        <v>0.2974010391500267</v>
+      </c>
+      <c r="X76" s="109" t="n">
+        <v>0.2565082468788883</v>
+      </c>
+      <c r="Y76" s="109" t="n">
+        <v>0.1403129681106313</v>
+      </c>
+      <c r="Z76" s="109" t="n">
+        <v>0.2974052528562983</v>
+      </c>
+      <c r="AA76" s="109" t="n">
+        <v>0.2565124645417485</v>
       </c>
     </row>
     <row r="77" ht="30" customHeight="1">
-      <c r="A77" s="43" t="inlineStr">
+      <c r="A77" t="inlineStr">
         <is>
           <t>Results</t>
         </is>
       </c>
-      <c r="B77" s="44" t="inlineStr">
-        <is>
-          <t>Equity IRR</t>
-        </is>
-      </c>
-      <c r="C77" s="45" t="inlineStr">
-        <is>
-          <t>G30</t>
-        </is>
-      </c>
-      <c r="D77" s="45" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E77" s="46" t="inlineStr">
-        <is>
-          <t>Equals Re when solved.</t>
-        </is>
-      </c>
-      <c r="F77" s="58" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="G77" s="58" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="H77" s="58" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I77" s="58" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="J77" s="58" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="K77" s="58" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="L77" s="58" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="M77" s="58" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="N77" s="58" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="O77" s="58" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="P77" s="58" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="Q77" s="58" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="R77" s="58" t="n">
-        <v>0.139999999999999</v>
-      </c>
-      <c r="S77" s="58" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="T77" s="58" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="U77" s="58" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="V77" s="58" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="W77" s="58" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="X77" s="58" t="n">
-        <v>0.140000002983082</v>
-      </c>
-      <c r="Y77" s="58" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="Z77" s="58" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AA77" s="58" t="n">
-        <v>0.140000003043171</v>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>CLLC now paid through the Fuel Cost (first year)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>GATP Build-up C26</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>PhP/kWh</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Previous GATP minus the re-solved GATP: logistics moved out of the GAT Price.</t>
+        </is>
+      </c>
+      <c r="F77" s="110" t="n">
+        <v>1.216353671233749</v>
+      </c>
+      <c r="G77" s="110" t="n">
+        <v>0.7740432453305683</v>
+      </c>
+      <c r="H77" s="110" t="n">
+        <v>0.7435691018136166</v>
+      </c>
+      <c r="I77" s="110" t="n">
+        <v>1.194586425864496</v>
+      </c>
+      <c r="J77" s="110" t="n">
+        <v>0.9751725925424473</v>
+      </c>
+      <c r="K77" s="110" t="n">
+        <v>1.232759300375205</v>
+      </c>
+      <c r="L77" s="110" t="n">
+        <v>1.980498548143772</v>
+      </c>
+      <c r="M77" s="110" t="n">
+        <v>1.616733508688793</v>
+      </c>
+      <c r="N77" s="110" t="n">
+        <v>1.232759300375206</v>
+      </c>
+      <c r="O77" s="110" t="n">
+        <v>1.980498548143771</v>
+      </c>
+      <c r="P77" s="110" t="n">
+        <v>1.616733508688794</v>
+      </c>
+      <c r="Q77" s="110" t="n">
+        <v>0.774043245330567</v>
+      </c>
+      <c r="R77" s="110" t="n">
+        <v>0.7740432453305666</v>
+      </c>
+      <c r="S77" s="110" t="n">
+        <v>0.7435691018136166</v>
+      </c>
+      <c r="T77" s="110" t="n">
+        <v>1.194586425864495</v>
+      </c>
+      <c r="U77" s="110" t="n">
+        <v>0.9751725925424477</v>
+      </c>
+      <c r="V77" s="110" t="n">
+        <v>1.232759300375205</v>
+      </c>
+      <c r="W77" s="110" t="n">
+        <v>1.980498548143771</v>
+      </c>
+      <c r="X77" s="110" t="n">
+        <v>1.616733528166195</v>
+      </c>
+      <c r="Y77" s="110" t="n">
+        <v>1.232759300375205</v>
+      </c>
+      <c r="Z77" s="110" t="n">
+        <v>1.980498548143772</v>
+      </c>
+      <c r="AA77" s="110" t="n">
+        <v>1.616733528558621</v>
       </c>
     </row>
     <row r="78" ht="30" customHeight="1">
@@ -18447,12 +19814,12 @@
       </c>
       <c r="B78" s="44" t="inlineStr">
         <is>
-          <t>Project IRR</t>
+          <t>Equity IRR</t>
         </is>
       </c>
       <c r="C78" s="45" t="inlineStr">
         <is>
-          <t>G32</t>
+          <t>G30</t>
         </is>
       </c>
       <c r="D78" s="45" t="inlineStr">
@@ -18462,74 +19829,74 @@
       </c>
       <c r="E78" s="46" t="inlineStr">
         <is>
-          <t>Model result.</t>
+          <t>Equals Re when solved.</t>
         </is>
       </c>
       <c r="F78" s="58" t="n">
-        <v>0.117964273244369</v>
+        <v>0.14</v>
       </c>
       <c r="G78" s="58" t="n">
-        <v>0.118056271649446</v>
+        <v>0.14</v>
       </c>
       <c r="H78" s="58" t="n">
-        <v>0.11062505734442</v>
+        <v>0.14</v>
       </c>
       <c r="I78" s="58" t="n">
-        <v>0.113877294670823</v>
+        <v>0.14</v>
       </c>
       <c r="J78" s="58" t="n">
-        <v>0.112752607467852</v>
+        <v>0.14</v>
       </c>
       <c r="K78" s="58" t="n">
-        <v>0.110567285612016</v>
+        <v>0.14</v>
       </c>
       <c r="L78" s="58" t="n">
-        <v>0.113723206811988</v>
+        <v>0.14</v>
       </c>
       <c r="M78" s="58" t="n">
-        <v>0.11267476417135</v>
+        <v>0.14</v>
       </c>
       <c r="N78" s="58" t="n">
-        <v>0.11056824170446</v>
+        <v>0.14</v>
       </c>
       <c r="O78" s="58" t="n">
-        <v>0.113724995258009</v>
+        <v>0.14</v>
       </c>
       <c r="P78" s="58" t="n">
-        <v>0.112675794777446</v>
+        <v>0.14</v>
       </c>
       <c r="Q78" s="58" t="n">
-        <v>0.11796383504052</v>
+        <v>0.14</v>
       </c>
       <c r="R78" s="58" t="n">
-        <v>0.117953638502882</v>
+        <v>0.139999999999999</v>
       </c>
       <c r="S78" s="58" t="n">
-        <v>0.110578234901689</v>
+        <v>0.14</v>
       </c>
       <c r="T78" s="58" t="n">
-        <v>0.113739743325391</v>
+        <v>0.14</v>
       </c>
       <c r="U78" s="58" t="n">
-        <v>0.112683434109201</v>
+        <v>0.14</v>
       </c>
       <c r="V78" s="58" t="n">
-        <v>0.110493253967895</v>
+        <v>0.14</v>
       </c>
       <c r="W78" s="58" t="n">
-        <v>0.113508925018704</v>
+        <v>0.14</v>
       </c>
       <c r="X78" s="58" t="n">
-        <v>0.112568027450008</v>
+        <v>0.140000002983082</v>
       </c>
       <c r="Y78" s="58" t="n">
-        <v>0.110494212971933</v>
+        <v>0.14</v>
       </c>
       <c r="Z78" s="58" t="n">
-        <v>0.113510730525212</v>
+        <v>0.14</v>
       </c>
       <c r="AA78" s="58" t="n">
-        <v>0.11256906283893</v>
+        <v>0.140000003043171</v>
       </c>
     </row>
     <row r="79" ht="30" customHeight="1">
@@ -18540,89 +19907,89 @@
       </c>
       <c r="B79" s="44" t="inlineStr">
         <is>
-          <t>First-year energy</t>
+          <t>Project IRR</t>
         </is>
       </c>
       <c r="C79" s="45" t="inlineStr">
         <is>
-          <t>F12</t>
+          <t>G32</t>
         </is>
       </c>
       <c r="D79" s="45" t="inlineStr">
         <is>
-          <t>MWh</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E79" s="46" t="inlineStr">
         <is>
-          <t>Installed MW x CF x 8,760.</t>
-        </is>
-      </c>
-      <c r="F79" s="62" t="n">
-        <v>5150880</v>
-      </c>
-      <c r="G79" s="62" t="n">
-        <v>1839600</v>
-      </c>
-      <c r="H79" s="62" t="n">
-        <v>3679200</v>
-      </c>
-      <c r="I79" s="62" t="n">
-        <v>3679200</v>
-      </c>
-      <c r="J79" s="62" t="n">
-        <v>3679200</v>
-      </c>
-      <c r="K79" s="62" t="n">
-        <v>1618848</v>
-      </c>
-      <c r="L79" s="62" t="n">
-        <v>1618848</v>
-      </c>
-      <c r="M79" s="62" t="n">
-        <v>1618848</v>
-      </c>
-      <c r="N79" s="62" t="n">
-        <v>1839600</v>
-      </c>
-      <c r="O79" s="62" t="n">
-        <v>1839600</v>
-      </c>
-      <c r="P79" s="62" t="n">
-        <v>1839600</v>
-      </c>
-      <c r="Q79" s="63" t="n">
-        <v>8192406.13286078</v>
-      </c>
-      <c r="R79" s="63" t="n">
-        <v>2925859.33316456</v>
-      </c>
-      <c r="S79" s="63" t="n">
-        <v>5529670.45309374</v>
-      </c>
-      <c r="T79" s="63" t="n">
-        <v>5529670.45309374</v>
-      </c>
-      <c r="U79" s="63" t="n">
-        <v>5529670.45309374</v>
-      </c>
-      <c r="V79" s="63" t="n">
-        <v>2433054.99936125</v>
-      </c>
-      <c r="W79" s="63" t="n">
-        <v>2433054.99936125</v>
-      </c>
-      <c r="X79" s="63" t="n">
-        <v>2433054.99936125</v>
-      </c>
-      <c r="Y79" s="63" t="n">
-        <v>2764835.22654687</v>
-      </c>
-      <c r="Z79" s="63" t="n">
-        <v>2764835.22654687</v>
-      </c>
-      <c r="AA79" s="63" t="n">
-        <v>2764835.22654687</v>
+          <t>Model result.</t>
+        </is>
+      </c>
+      <c r="F79" s="58" t="n">
+        <v>0.117964273244369</v>
+      </c>
+      <c r="G79" s="58" t="n">
+        <v>0.118056271649446</v>
+      </c>
+      <c r="H79" s="58" t="n">
+        <v>0.11062505734442</v>
+      </c>
+      <c r="I79" s="58" t="n">
+        <v>0.113877294670823</v>
+      </c>
+      <c r="J79" s="58" t="n">
+        <v>0.112752607467852</v>
+      </c>
+      <c r="K79" s="58" t="n">
+        <v>0.110567285612016</v>
+      </c>
+      <c r="L79" s="58" t="n">
+        <v>0.113723206811988</v>
+      </c>
+      <c r="M79" s="58" t="n">
+        <v>0.11267476417135</v>
+      </c>
+      <c r="N79" s="58" t="n">
+        <v>0.11056824170446</v>
+      </c>
+      <c r="O79" s="58" t="n">
+        <v>0.113724995258009</v>
+      </c>
+      <c r="P79" s="58" t="n">
+        <v>0.112675794777446</v>
+      </c>
+      <c r="Q79" s="58" t="n">
+        <v>0.11796383504052</v>
+      </c>
+      <c r="R79" s="58" t="n">
+        <v>0.117953638502882</v>
+      </c>
+      <c r="S79" s="58" t="n">
+        <v>0.110578234901689</v>
+      </c>
+      <c r="T79" s="58" t="n">
+        <v>0.113739743325391</v>
+      </c>
+      <c r="U79" s="58" t="n">
+        <v>0.112683434109201</v>
+      </c>
+      <c r="V79" s="58" t="n">
+        <v>0.110493253967895</v>
+      </c>
+      <c r="W79" s="58" t="n">
+        <v>0.113508925018704</v>
+      </c>
+      <c r="X79" s="58" t="n">
+        <v>0.112568027450008</v>
+      </c>
+      <c r="Y79" s="58" t="n">
+        <v>0.110494212971933</v>
+      </c>
+      <c r="Z79" s="58" t="n">
+        <v>0.113510730525212</v>
+      </c>
+      <c r="AA79" s="58" t="n">
+        <v>0.11256906283893</v>
       </c>
     </row>
     <row r="80" ht="30" customHeight="1">
@@ -18633,126 +20000,219 @@
       </c>
       <c r="B80" s="44" t="inlineStr">
         <is>
+          <t>First-year energy</t>
+        </is>
+      </c>
+      <c r="C80" s="45" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
+      <c r="D80" s="45" t="inlineStr">
+        <is>
+          <t>MWh</t>
+        </is>
+      </c>
+      <c r="E80" s="46" t="inlineStr">
+        <is>
+          <t>Installed MW x CF x 8,760.</t>
+        </is>
+      </c>
+      <c r="F80" s="62" t="n">
+        <v>5150880</v>
+      </c>
+      <c r="G80" s="62" t="n">
+        <v>1839600</v>
+      </c>
+      <c r="H80" s="62" t="n">
+        <v>3679200</v>
+      </c>
+      <c r="I80" s="62" t="n">
+        <v>3679200</v>
+      </c>
+      <c r="J80" s="62" t="n">
+        <v>3679200</v>
+      </c>
+      <c r="K80" s="62" t="n">
+        <v>1618848</v>
+      </c>
+      <c r="L80" s="62" t="n">
+        <v>1618848</v>
+      </c>
+      <c r="M80" s="62" t="n">
+        <v>1618848</v>
+      </c>
+      <c r="N80" s="62" t="n">
+        <v>1839600</v>
+      </c>
+      <c r="O80" s="62" t="n">
+        <v>1839600</v>
+      </c>
+      <c r="P80" s="62" t="n">
+        <v>1839600</v>
+      </c>
+      <c r="Q80" s="63" t="n">
+        <v>8192406.13286078</v>
+      </c>
+      <c r="R80" s="63" t="n">
+        <v>2925859.33316456</v>
+      </c>
+      <c r="S80" s="63" t="n">
+        <v>5529670.45309374</v>
+      </c>
+      <c r="T80" s="63" t="n">
+        <v>5529670.45309374</v>
+      </c>
+      <c r="U80" s="63" t="n">
+        <v>5529670.45309374</v>
+      </c>
+      <c r="V80" s="63" t="n">
+        <v>2433054.99936125</v>
+      </c>
+      <c r="W80" s="63" t="n">
+        <v>2433054.99936125</v>
+      </c>
+      <c r="X80" s="63" t="n">
+        <v>2433054.99936125</v>
+      </c>
+      <c r="Y80" s="63" t="n">
+        <v>2764835.22654687</v>
+      </c>
+      <c r="Z80" s="63" t="n">
+        <v>2764835.22654687</v>
+      </c>
+      <c r="AA80" s="63" t="n">
+        <v>2764835.22654687</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="43" t="inlineStr">
+        <is>
+          <t>Results</t>
+        </is>
+      </c>
+      <c r="B81" s="44" t="inlineStr">
+        <is>
           <t>Model file</t>
         </is>
       </c>
-      <c r="C80" s="45" t="inlineStr">
+      <c r="C81" s="45" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D80" s="45" t="inlineStr"/>
-      <c r="E80" s="46" t="inlineStr">
+      <c r="D81" s="45" t="inlineStr"/>
+      <c r="E81" s="46" t="inlineStr">
         <is>
           <t>Varies by case — see the comment on each value.</t>
         </is>
       </c>
-      <c r="F80" s="53" t="inlineStr">
+      <c r="F81" s="53" t="inlineStr">
         <is>
           <t>Fin42_Lot1_Existing_CCGT_Luzon_1400MW.xlsm</t>
         </is>
       </c>
-      <c r="G80" s="53" t="inlineStr">
+      <c r="G81" s="53" t="inlineStr">
         <is>
           <t>Fin42_Lot2_Existing_CCGT_Luzon_500MW.xlsm</t>
         </is>
       </c>
-      <c r="H80" s="53" t="inlineStr">
+      <c r="H81" s="53" t="inlineStr">
         <is>
           <t>Fin42_NewBuild_CCGT_Luzon_1000MW.xlsm</t>
         </is>
       </c>
-      <c r="I80" s="53" t="inlineStr">
+      <c r="I81" s="53" t="inlineStr">
         <is>
           <t>Fin42_NewBuild_OCGT_Luzon_1000MW.xlsm</t>
         </is>
       </c>
-      <c r="J80" s="53" t="inlineStr">
+      <c r="J81" s="53" t="inlineStr">
         <is>
           <t>Fin42_NewBuild_GasEngine_Luzon_1000MW.xlsm</t>
         </is>
       </c>
-      <c r="K80" s="53" t="inlineStr">
+      <c r="K81" s="53" t="inlineStr">
         <is>
           <t>Fin42_NewBuild_CCGT_Visayas_440MW.xlsm</t>
         </is>
       </c>
-      <c r="L80" s="53" t="inlineStr">
+      <c r="L81" s="53" t="inlineStr">
         <is>
           <t>Fin42_NewBuild_OCGT_Visayas_440MW.xlsm</t>
         </is>
       </c>
-      <c r="M80" s="53" t="inlineStr">
+      <c r="M81" s="53" t="inlineStr">
         <is>
           <t>Fin42_NewBuild_GasEngine_Visayas_440MW.xlsm</t>
         </is>
       </c>
-      <c r="N80" s="53" t="inlineStr">
+      <c r="N81" s="53" t="inlineStr">
         <is>
           <t>Fin42_NewBuild_CCGT_Visayas_500MW.xlsm</t>
         </is>
       </c>
-      <c r="O80" s="53" t="inlineStr">
+      <c r="O81" s="53" t="inlineStr">
         <is>
           <t>Fin42_NewBuild_OCGT_Visayas_500MW.xlsm</t>
         </is>
       </c>
-      <c r="P80" s="53" t="inlineStr">
+      <c r="P81" s="53" t="inlineStr">
         <is>
           <t>Fin42_NewBuild_GasEngine_Visayas_500MW.xlsm</t>
         </is>
       </c>
-      <c r="Q80" s="53" t="inlineStr">
+      <c r="Q81" s="53" t="inlineStr">
         <is>
           <t>Fin90_Lot1_Existing_CCGT_Luzon_1400MW.xlsm</t>
         </is>
       </c>
-      <c r="R80" s="53" t="inlineStr">
+      <c r="R81" s="53" t="inlineStr">
         <is>
           <t>Fin90_Lot2_Existing_CCGT_Luzon_500MW.xlsm</t>
         </is>
       </c>
-      <c r="S80" s="53" t="inlineStr">
+      <c r="S81" s="53" t="inlineStr">
         <is>
           <t>Fin90_NewBuild_CCGT_Luzon_1000MW.xlsm</t>
         </is>
       </c>
-      <c r="T80" s="53" t="inlineStr">
+      <c r="T81" s="53" t="inlineStr">
         <is>
           <t>Fin90_NewBuild_OCGT_Luzon_1000MW.xlsm</t>
         </is>
       </c>
-      <c r="U80" s="53" t="inlineStr">
+      <c r="U81" s="53" t="inlineStr">
         <is>
           <t>Fin90_NewBuild_GasEngine_Luzon_1000MW.xlsm</t>
         </is>
       </c>
-      <c r="V80" s="53" t="inlineStr">
+      <c r="V81" s="53" t="inlineStr">
         <is>
           <t>Fin90_NewBuild_CCGT_Visayas_440MW.xlsm</t>
         </is>
       </c>
-      <c r="W80" s="53" t="inlineStr">
+      <c r="W81" s="53" t="inlineStr">
         <is>
           <t>Fin90_NewBuild_OCGT_Visayas_440MW.xlsm</t>
         </is>
       </c>
-      <c r="X80" s="53" t="inlineStr">
+      <c r="X81" s="53" t="inlineStr">
         <is>
           <t>Fin90_NewBuild_GasEngine_Visayas_440MW.xlsm</t>
         </is>
       </c>
-      <c r="Y80" s="53" t="inlineStr">
+      <c r="Y81" s="53" t="inlineStr">
         <is>
           <t>Fin90_NewBuild_CCGT_Visayas_500MW.xlsm</t>
         </is>
       </c>
-      <c r="Z80" s="53" t="inlineStr">
+      <c r="Z81" s="53" t="inlineStr">
         <is>
           <t>Fin90_NewBuild_OCGT_Visayas_500MW.xlsm</t>
         </is>
       </c>
-      <c r="AA80" s="53" t="inlineStr">
+      <c r="AA81" s="53" t="inlineStr">
         <is>
           <t>Fin90_NewBuild_GasEngine_Visayas_500MW.xlsm</t>
         </is>
@@ -18773,7 +20233,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19105,7 +20565,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19889,7 +21349,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/FinModel_Summary.xlsx
+++ b/FinModel_Summary.xlsx
@@ -17237,70 +17237,70 @@
       </c>
       <c r="F155" s="123" t="inlineStr"/>
       <c r="G155" s="150" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H155" s="150" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I155" s="151" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J155" s="151" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K155" s="151" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L155" s="151" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M155" s="151" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N155" s="151" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O155" s="151" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P155" s="151" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q155" s="151" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R155" s="150" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S155" s="150" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T155" s="151" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U155" s="151" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V155" s="151" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W155" s="151" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="X155" s="151" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y155" s="151" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z155" s="151" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA155" s="151" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB155" s="151" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" ht="15" customHeight="1">
@@ -18092,6 +18092,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -18374,10 +18375,11 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>How the TOR enters the models: capacity factor (Fin42 = 42%, top of band); Lot 1 non-mid-merit energy paid fuel only (TOR 4.2.2); grid (Visayas logistics caps); technology (TOR 2.6 lists CCGT, OCGT, reciprocating engines).</t>
+          <t>How the TOR enters the models: capacity factor (Fin42 = 42%, top of band); Lot 1 non-mid-merit energy paid fuel only (TOR 4.2.2); grid (Visayas logistics caps now affect only the Fuel Cost, not the GATP, after the 19 Oct 2026 decision); technology (TOR 2.6 lists CCGT, OCGT, reciprocating engines).</t>
         </is>
       </c>
     </row>
@@ -19187,7 +19189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -19440,6 +19442,23 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>New-build capital cost (working assumption, 20 Oct 2026): CCGT US$1,200/kW, gas engine US$1,100/kW, OCGT US$700/kW</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>Market-level working values chosen 20 Oct 2026 in response to Wärtsilä and Quezon Power comments (GAIR matrix rows 119, 412); to be sourced in the Reference Parameters Resolution</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>models Fin42/Fin90, cell O34</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/FinModel_Summary.xlsx
+++ b/FinModel_Summary.xlsx
@@ -1646,7 +1646,7 @@
     <row r="2">
       <c r="A2" s="70" t="inlineStr">
         <is>
-          <t>Decision of 19 Oct 2026 (GAIR Sec. 8.6): GATP = CRF + OM; CLLC paid through the Fuel Cost. New-build capex: CCGT US$1,200/kW, gas engine US$1,100/kW, OCGT US$700/kW. PhP/kWh, excluding fuel.</t>
+          <t>Decision of 19 Oct 2026 (GAIR Sec. 8.6): GATP = CRF + OM; CLLC paid through the Fuel Cost. Capex (market +25%): existing CCGT US$600/kW; new CCGT US$1,500/kW, gas engine US$1,375/kW, OCGT US$875/kW. PhP/kWh, excluding fuel.</t>
         </is>
       </c>
       <c r="B2" s="69" t="n"/>
@@ -1698,28 +1698,28 @@
     <row r="5" ht="30" customHeight="1">
       <c r="B5" s="73" t="inlineStr">
         <is>
-          <t>1.09 – 1.72</t>
+          <t>1.35 – 2.12</t>
         </is>
       </c>
       <c r="C5" s="72" t="n"/>
       <c r="D5" s="72" t="n"/>
       <c r="F5" s="73" t="inlineStr">
         <is>
-          <t>2.61 – 3.84</t>
+          <t>3.18 – 4.70</t>
         </is>
       </c>
       <c r="G5" s="72" t="n"/>
       <c r="H5" s="72" t="n"/>
       <c r="J5" s="73" t="inlineStr">
         <is>
-          <t>1.73 – 2.44</t>
+          <t>2.06 – 2.92</t>
         </is>
       </c>
       <c r="K5" s="72" t="n"/>
       <c r="L5" s="72" t="n"/>
       <c r="N5" s="73" t="inlineStr">
         <is>
-          <t>2.54 – 3.68</t>
+          <t>3.05 – 4.45</t>
         </is>
       </c>
       <c r="O5" s="72" t="n"/>
@@ -1989,16 +1989,16 @@
         <v>0.42</v>
       </c>
       <c r="F6" s="82" t="n">
-        <v>1.113210815556326</v>
+        <v>1.486830198990387</v>
       </c>
       <c r="G6" s="82" t="n">
-        <v>0.04248573913293401</v>
+        <v>0.04777779558966159</v>
       </c>
       <c r="H6" s="82" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="82" t="n">
-        <v>0.1083414537470186</v>
+        <v>0.1328416046460465</v>
       </c>
       <c r="J6" s="83">
         <f>SUM(F6:I6)</f>
@@ -2008,7 +2008,7 @@
         <v>0.2408352664316716</v>
       </c>
       <c r="L6" s="84" t="n">
-        <v>0.2122220862959302</v>
+        <v>0.215260421728373</v>
       </c>
       <c r="M6" s="85">
         <f>K6+L6</f>
@@ -2025,7 +2025,7 @@
         <v>2.933449032397625</v>
       </c>
       <c r="Q6" s="89">
-        <f>IF(ABS(N6-1.7170953612)&lt;0.0001,"OK","CHECK")</f>
+        <f>IF(ABS(N6-2.1235452874)&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -2052,16 +2052,16 @@
         <v>0.42</v>
       </c>
       <c r="F7" s="82" t="n">
-        <v>1.114523660438694</v>
+        <v>1.488143043872764</v>
       </c>
       <c r="G7" s="82" t="n">
-        <v>0.03800360248121382</v>
+        <v>0.04329565893794141</v>
       </c>
       <c r="H7" s="82" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="82" t="n">
-        <v>0.107633003568228</v>
+        <v>0.1321331544672561</v>
       </c>
       <c r="J7" s="83">
         <f>SUM(F7:I7)</f>
@@ -2071,7 +2071,7 @@
         <v>0.2408352664316718</v>
       </c>
       <c r="L7" s="84" t="n">
-        <v>0.1383289394592217</v>
+        <v>0.1413672748916645</v>
       </c>
       <c r="M7" s="85">
         <f>K7+L7</f>
@@ -2088,7 +2088,7 @@
         <v>2.413367717709602</v>
       </c>
       <c r="Q7" s="89">
-        <f>IF(ABS(N7-1.6393244724)&lt;0.0001,"OK","CHECK")</f>
+        <f>IF(ABS(N7-2.0457743986)&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         <v>0.42</v>
       </c>
       <c r="F8" s="82" t="n">
-        <v>3.153855737078547</v>
+        <v>3.94390173844531</v>
       </c>
       <c r="G8" s="82" t="n">
-        <v>0.06085164375219657</v>
+        <v>0.07052284750191348</v>
       </c>
       <c r="H8" s="82" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="82" t="n">
-        <v>0.2339831193583159</v>
+        <v>0.2839542902423469</v>
       </c>
       <c r="J8" s="83">
         <f>SUM(F8:I8)</f>
@@ -2134,7 +2134,7 @@
         <v>0.2408352664316718</v>
       </c>
       <c r="L8" s="84" t="n">
-        <v>0.1514475454490726</v>
+        <v>0.1570000865580744</v>
       </c>
       <c r="M8" s="85">
         <f>K8+L8</f>
@@ -2151,7 +2151,7 @@
         <v>3.729301496810136</v>
       </c>
       <c r="Q8" s="89">
-        <f>IF(ABS(N8-3.8409733121)&lt;0.0001,"OK","CHECK")</f>
+        <f>IF(ABS(N8-4.6962142292)&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -2178,16 +2178,16 @@
         <v>0.42</v>
       </c>
       <c r="F9" s="82" t="n">
-        <v>1.784194928369909</v>
+        <v>2.23213977590294</v>
       </c>
       <c r="G9" s="82" t="n">
-        <v>0.04962773710894557</v>
+        <v>0.05544216248294227</v>
       </c>
       <c r="H9" s="82" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="82" t="n">
-        <v>0.1504877984741485</v>
+        <v>0.1794067985308676</v>
       </c>
       <c r="J9" s="83">
         <f>SUM(F9:I9)</f>
@@ -2197,7 +2197,7 @@
         <v>0.149314351908768</v>
       </c>
       <c r="L9" s="84" t="n">
-        <v>0.3041660054372468</v>
+        <v>0.3075042492329361</v>
       </c>
       <c r="M9" s="85">
         <f>K9+L9</f>
@@ -2214,7 +2214,7 @@
         <v>3.132474544268364</v>
       </c>
       <c r="Q9" s="89">
-        <f>IF(ABS(N9-2.4377908213)&lt;0.0001,"OK","CHECK")</f>
+        <f>IF(ABS(N9-2.9238073381)&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -2241,16 +2241,16 @@
         <v>0.42</v>
       </c>
       <c r="F10" s="82" t="n">
-        <v>2.831870076237649</v>
+        <v>3.542161243792975</v>
       </c>
       <c r="G10" s="82" t="n">
-        <v>0.06917736992517988</v>
+        <v>0.07844986359632908</v>
       </c>
       <c r="H10" s="82" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="82" t="n">
-        <v>0.2174797461027427</v>
+        <v>0.2629041647027586</v>
       </c>
       <c r="J10" s="83">
         <f>SUM(F10:I10)</f>
@@ -2260,7 +2260,7 @@
         <v>0.2898455066464321</v>
       </c>
       <c r="L10" s="84" t="n">
-        <v>0.2668663304445173</v>
+        <v>0.2721899596042816</v>
       </c>
       <c r="M10" s="85">
         <f>K10+L10</f>
@@ -2277,7 +2277,7 @@
         <v>3.950128250112614</v>
       </c>
       <c r="Q10" s="89">
-        <f>IF(ABS(N10-3.6752390294)&lt;0.0001,"OK","CHECK")</f>
+        <f>IF(ABS(N10-4.4455507383)&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -2304,16 +2304,16 @@
         <v>0.42</v>
       </c>
       <c r="F11" s="82" t="n">
-        <v>3.153836591657454</v>
+        <v>3.943882592731354</v>
       </c>
       <c r="G11" s="82" t="n">
-        <v>0.06080210844138251</v>
+        <v>0.07047331219180548</v>
       </c>
       <c r="H11" s="82" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="82" t="n">
-        <v>0.2340260628416754</v>
+        <v>0.2839972337237082</v>
       </c>
       <c r="J11" s="83">
         <f>SUM(F11:I11)</f>
@@ -2323,7 +2323,7 @@
         <v>0.2408352664316717</v>
       </c>
       <c r="L11" s="84" t="n">
-        <v>0.1514180498478056</v>
+        <v>0.1569705909572128</v>
       </c>
       <c r="M11" s="85">
         <f>K11+L11</f>
@@ -2340,7 +2340,7 @@
         <v>4.218436463045343</v>
       </c>
       <c r="Q11" s="89">
-        <f>IF(ABS(N11-3.8409180792)&lt;0.0001,"OK","CHECK")</f>
+        <f>IF(ABS(N11-4.6961589960)&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -2367,16 +2367,16 @@
         <v>0.42</v>
       </c>
       <c r="F12" s="82" t="n">
-        <v>1.784178234915861</v>
+        <v>2.232123082103706</v>
       </c>
       <c r="G12" s="82" t="n">
-        <v>0.04957810000815011</v>
+        <v>0.05539252538226503</v>
       </c>
       <c r="H12" s="82" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="82" t="n">
-        <v>0.1505308275318445</v>
+        <v>0.1794498275846172</v>
       </c>
       <c r="J12" s="83">
         <f>SUM(F12:I12)</f>
@@ -2386,7 +2386,7 @@
         <v>0.149314351908768</v>
       </c>
       <c r="L12" s="84" t="n">
-        <v>0.304136451395162</v>
+        <v>0.3074746951909192</v>
       </c>
       <c r="M12" s="85">
         <f>K12+L12</f>
@@ -2403,7 +2403,7 @@
         <v>3.9183338116066</v>
       </c>
       <c r="Q12" s="89">
-        <f>IF(ABS(N12-2.4377379658)&lt;0.0001,"OK","CHECK")</f>
+        <f>IF(ABS(N12-2.9237544822)&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -2430,16 +2430,16 @@
         <v>0.42</v>
       </c>
       <c r="F13" s="82" t="n">
-        <v>2.831854894884217</v>
+        <v>3.542146062279643</v>
       </c>
       <c r="G13" s="82" t="n">
-        <v>0.06912768448910267</v>
+        <v>0.07840017816032213</v>
       </c>
       <c r="H13" s="82" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="82" t="n">
-        <v>0.2175228191925891</v>
+        <v>0.2629472377908854</v>
       </c>
       <c r="J13" s="83">
         <f>SUM(F13:I13)</f>
@@ -2449,7 +2449,7 @@
         <v>0.2898455066464321</v>
       </c>
       <c r="L13" s="84" t="n">
-        <v>0.2668367486516327</v>
+        <v>0.2721603778114374</v>
       </c>
       <c r="M13" s="85">
         <f>K13+L13</f>
@@ -2466,7 +2466,7 @@
         <v>4.591637790993857</v>
       </c>
       <c r="Q13" s="89">
-        <f>IF(ABS(N13-3.6751876539)&lt;0.0001,"OK","CHECK")</f>
+        <f>IF(ABS(N13-4.4454993627)&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -2493,16 +2493,16 @@
         <v>0.42</v>
       </c>
       <c r="F14" s="82" t="n">
-        <v>3.153840694143365</v>
+        <v>3.94388669530116</v>
       </c>
       <c r="G14" s="82" t="n">
-        <v>0.06081272315097044</v>
+        <v>0.07048392690121993</v>
       </c>
       <c r="H14" s="82" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="82" t="n">
-        <v>0.2340168606654816</v>
+        <v>0.2839880315481977</v>
       </c>
       <c r="J14" s="83">
         <f>SUM(F14:I14)</f>
@@ -2512,7 +2512,7 @@
         <v>0.2408352664316718</v>
       </c>
       <c r="L14" s="84" t="n">
-        <v>0.1514243703338647</v>
+        <v>0.1569769114431724</v>
       </c>
       <c r="M14" s="85">
         <f>K14+L14</f>
@@ -2529,7 +2529,7 @@
         <v>4.218448298406374</v>
       </c>
       <c r="Q14" s="89">
-        <f>IF(ABS(N14-3.8409299147)&lt;0.0001,"OK","CHECK")</f>
+        <f>IF(ABS(N14-4.6961708316)&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -2556,16 +2556,16 @@
         <v>0.42</v>
       </c>
       <c r="F15" s="82" t="n">
-        <v>1.784181811973243</v>
+        <v>2.232126659257657</v>
       </c>
       <c r="G15" s="82" t="n">
-        <v>0.04958873652980943</v>
+        <v>0.05540316190389129</v>
       </c>
       <c r="H15" s="82" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="82" t="n">
-        <v>0.1505216070182965</v>
+        <v>0.1794406070721735</v>
       </c>
       <c r="J15" s="83">
         <f>SUM(F15:I15)</f>
@@ -2575,7 +2575,7 @@
         <v>0.149314351908768</v>
       </c>
       <c r="L15" s="84" t="n">
-        <v>0.3041427844042148</v>
+        <v>0.307481028199953</v>
       </c>
       <c r="M15" s="85">
         <f>K15+L15</f>
@@ -2592,7 +2592,7 @@
         <v>3.918345137513774</v>
       </c>
       <c r="Q15" s="89">
-        <f>IF(ABS(N15-2.4377492918)&lt;0.0001,"OK","CHECK")</f>
+        <f>IF(ABS(N15-2.9237658083)&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -2619,16 +2619,16 @@
         <v>0.42</v>
       </c>
       <c r="F16" s="82" t="n">
-        <v>2.831858147979329</v>
+        <v>3.54214931541949</v>
       </c>
       <c r="G16" s="82" t="n">
-        <v>0.06913833136828895</v>
+        <v>0.07841082503948879</v>
       </c>
       <c r="H16" s="82" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="82" t="n">
-        <v>0.2175135892442209</v>
+        <v>0.2629380078429988</v>
       </c>
       <c r="J16" s="83">
         <f>SUM(F16:I16)</f>
@@ -2638,7 +2638,7 @@
         <v>0.2898455066464321</v>
       </c>
       <c r="L16" s="84" t="n">
-        <v>0.2668430876072663</v>
+        <v>0.2721667167670597</v>
       </c>
       <c r="M16" s="85">
         <f>K16+L16</f>
@@ -2655,7 +2655,7 @@
         <v>4.591648799911785</v>
       </c>
       <c r="Q16" s="89">
-        <f>IF(ABS(N16-3.6751986628)&lt;0.0001,"OK","CHECK")</f>
+        <f>IF(ABS(N16-4.4455103717)&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -2776,16 +2776,16 @@
         <v>0.6680044139645122</v>
       </c>
       <c r="F20" s="82" t="n">
-        <v>0.700014289580048</v>
+        <v>0.9349231281474634</v>
       </c>
       <c r="G20" s="82" t="n">
-        <v>0.02680534643415587</v>
+        <v>0.03013266533409306</v>
       </c>
       <c r="H20" s="82" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="82" t="n">
-        <v>0.07938208693776358</v>
+        <v>0.09478627164445091</v>
       </c>
       <c r="J20" s="83">
         <f>SUM(F20:I20)</f>
@@ -2795,7 +2795,7 @@
         <v>0.1514223705513954</v>
       </c>
       <c r="L20" s="84" t="n">
-        <v>0.1349810410827771</v>
+        <v>0.1368913591210255</v>
       </c>
       <c r="M20" s="85">
         <f>K20+L20</f>
@@ -2812,7 +2812,7 @@
         <v>1.866648379916711</v>
       </c>
       <c r="Q20" s="89">
-        <f>IF(ABS(N20-1.0926051346)&lt;0.0001,"OK","CHECK")</f>
+        <f>IF(ABS(N20-1.3481557948)&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -2839,16 +2839,16 @@
         <v>0.6680044139645122</v>
       </c>
       <c r="F21" s="82" t="n">
-        <v>0.700005694569188</v>
+        <v>0.9349145331365989</v>
       </c>
       <c r="G21" s="82" t="n">
-        <v>0.02677369187463278</v>
+        <v>0.03010101077456997</v>
       </c>
       <c r="H21" s="82" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="82" t="n">
-        <v>0.07940951372560666</v>
+        <v>0.09481369843229404</v>
       </c>
       <c r="J21" s="83">
         <f>SUM(F21:I21)</f>
@@ -2858,7 +2858,7 @@
         <v>0.1514223705513955</v>
       </c>
       <c r="L21" s="84" t="n">
-        <v>0.1349621965953671</v>
+        <v>0.1368725146336156</v>
       </c>
       <c r="M21" s="85">
         <f>K21+L21</f>
@@ -2875,7 +2875,7 @@
         <v>1.866616712646755</v>
       </c>
       <c r="Q21" s="89">
-        <f>IF(ABS(N21-1.0925734673)&lt;0.0001,"OK","CHECK")</f>
+        <f>IF(ABS(N21-1.3481241275)&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -2902,16 +2902,16 @@
         <v>0.6312409193029385</v>
       </c>
       <c r="F22" s="82" t="n">
-        <v>2.097771885348189</v>
+        <v>2.623433816359344</v>
       </c>
       <c r="G22" s="82" t="n">
-        <v>0.04308338807996767</v>
+        <v>0.04951818254697807</v>
       </c>
       <c r="H22" s="82" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="82" t="n">
-        <v>0.1662610335270309</v>
+        <v>0.199509657197482</v>
       </c>
       <c r="J22" s="83">
         <f>SUM(F22:I22)</f>
@@ -2921,7 +2921,7 @@
         <v>0.1602412150546261</v>
       </c>
       <c r="L22" s="84" t="n">
-        <v>0.1440228049458968</v>
+        <v>0.1477172220764529</v>
       </c>
       <c r="M22" s="85">
         <f>K22+L22</f>
@@ -2938,7 +2938,7 @@
         <v>2.785909662514258</v>
       </c>
       <c r="Q22" s="89">
-        <f>IF(ABS(N22-2.6113803270)&lt;0.0001,"OK","CHECK")</f>
+        <f>IF(ABS(N22-3.1804200932)&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -2965,16 +2965,16 @@
         <v>0.6312409193029385</v>
       </c>
       <c r="F23" s="82" t="n">
-        <v>1.185488649618506</v>
+        <v>1.483531489065016</v>
       </c>
       <c r="G23" s="82" t="n">
-        <v>0.03885971245045097</v>
+        <v>0.04272837587578042</v>
       </c>
       <c r="H23" s="82" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="82" t="n">
-        <v>0.1112574539563226</v>
+        <v>0.1304988872227758</v>
       </c>
       <c r="J23" s="83">
         <f>SUM(F23:I23)</f>
@@ -2984,7 +2984,7 @@
         <v>0.0993472157523211</v>
       </c>
       <c r="L23" s="84" t="n">
-        <v>0.299705284602134</v>
+        <v>0.3019264054948317</v>
       </c>
       <c r="M23" s="85">
         <f>K23+L23</f>
@@ -3001,7 +3001,7 @@
         <v>2.596631426479127</v>
       </c>
       <c r="Q23" s="89">
-        <f>IF(ABS(N23-1.7346583164)&lt;0.0001,"OK","CHECK")</f>
+        <f>IF(ABS(N23-2.0580323734)&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -3028,16 +3028,16 @@
         <v>0.6312409193029385</v>
       </c>
       <c r="F24" s="82" t="n">
-        <v>1.882837601322518</v>
+        <v>2.355434166676148</v>
       </c>
       <c r="G24" s="82" t="n">
-        <v>0.05095879864154527</v>
+        <v>0.05712830892326653</v>
       </c>
       <c r="H24" s="82" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="82" t="n">
-        <v>0.1556768036022249</v>
+        <v>0.185900217878147</v>
       </c>
       <c r="J24" s="83">
         <f>SUM(F24:I24)</f>
@@ -3047,7 +3047,7 @@
         <v>0.1928504776368586</v>
       </c>
       <c r="L24" s="84" t="n">
-        <v>0.259748028548601</v>
+        <v>0.2632901377160011</v>
       </c>
       <c r="M24" s="85">
         <f>K24+L24</f>
@@ -3064,7 +3064,7 @@
         <v>3.051306484962811</v>
       </c>
       <c r="Q24" s="89">
-        <f>IF(ABS(N24-2.5420717098)&lt;0.0001,"OK","CHECK")</f>
+        <f>IF(ABS(N24-3.0546033088)&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -3091,16 +3091,16 @@
         <v>0.6312409193029385</v>
       </c>
       <c r="F25" s="82" t="n">
-        <v>2.097759146825363</v>
+        <v>2.62342107764166</v>
       </c>
       <c r="G25" s="82" t="n">
-        <v>0.04305042945845613</v>
+        <v>0.04948522392593631</v>
       </c>
       <c r="H25" s="82" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="82" t="n">
-        <v>0.166289606235896</v>
+        <v>0.1995382299050175</v>
       </c>
       <c r="J25" s="83">
         <f>SUM(F25:I25)</f>
@@ -3110,7 +3110,7 @@
         <v>0.1602412150546261</v>
       </c>
       <c r="L25" s="84" t="n">
-        <v>0.1440031798674944</v>
+        <v>0.1476975969983202</v>
       </c>
       <c r="M25" s="85">
         <f>K25+L25</f>
@@ -3127,7 +3127,7 @@
         <v>3.275063111910242</v>
       </c>
       <c r="Q25" s="89">
-        <f>IF(ABS(N25-2.6113435774)&lt;0.0001,"OK","CHECK")</f>
+        <f>IF(ABS(N25-3.1803833435)&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -3154,16 +3154,16 @@
         <v>0.6312409193029385</v>
       </c>
       <c r="F26" s="82" t="n">
-        <v>1.185477542526925</v>
+        <v>1.483520381743764</v>
       </c>
       <c r="G26" s="82" t="n">
-        <v>0.03882668610235376</v>
+        <v>0.04269534952776186</v>
       </c>
       <c r="H26" s="82" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="82" t="n">
-        <v>0.1112860836025951</v>
+        <v>0.1305275168664224</v>
       </c>
       <c r="J26" s="83">
         <f>SUM(F26:I26)</f>
@@ -3173,7 +3173,7 @@
         <v>0.0993472157523211</v>
       </c>
       <c r="L26" s="84" t="n">
-        <v>0.2996856206397765</v>
+        <v>0.3019067415325195</v>
       </c>
       <c r="M26" s="85">
         <f>K26+L26</f>
@@ -3190,7 +3190,7 @@
         <v>3.382508381400652</v>
       </c>
       <c r="Q26" s="89">
-        <f>IF(ABS(N26-1.7346231486)&lt;0.0001,"OK","CHECK")</f>
+        <f>IF(ABS(N26-2.0579972054)&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -3217,16 +3217,16 @@
         <v>0.6312409193029385</v>
       </c>
       <c r="F27" s="82" t="n">
-        <v>1.882827500316316</v>
+        <v>2.355424065563553</v>
       </c>
       <c r="G27" s="82" t="n">
-        <v>0.05092574013327326</v>
+        <v>0.05709525041504129</v>
       </c>
       <c r="H27" s="82" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="82" t="n">
-        <v>0.1557054625455575</v>
+        <v>0.1859288768203355</v>
       </c>
       <c r="J27" s="83">
         <f>SUM(F27:I27)</f>
@@ -3236,7 +3236,7 @@
         <v>0.1928504776368586</v>
       </c>
       <c r="L27" s="84" t="n">
-        <v>0.2597283461220796</v>
+        <v>0.2632704552895065</v>
       </c>
       <c r="M27" s="85">
         <f>K27+L27</f>
@@ -3253,7 +3253,7 @@
         <v>3.692833237740226</v>
       </c>
       <c r="Q27" s="89">
-        <f>IF(ABS(N27-2.5420375268)&lt;0.0001,"OK","CHECK")</f>
+        <f>IF(ABS(N27-3.0545691257)&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -3280,16 +3280,16 @@
         <v>0.6312409193029385</v>
       </c>
       <c r="F28" s="82" t="n">
-        <v>2.097761876439413</v>
+        <v>2.623423807311532</v>
       </c>
       <c r="G28" s="82" t="n">
-        <v>0.04305749202029362</v>
+        <v>0.04949228648765837</v>
       </c>
       <c r="H28" s="82" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="82" t="n">
-        <v>0.1662834835117771</v>
+        <v>0.1995321071813534</v>
       </c>
       <c r="J28" s="83">
         <f>SUM(F28:I28)</f>
@@ -3299,7 +3299,7 @@
         <v>0.1602412150546261</v>
       </c>
       <c r="L28" s="84" t="n">
-        <v>0.1440073852414866</v>
+        <v>0.1477018023722461</v>
       </c>
       <c r="M28" s="85">
         <f>K28+L28</f>
@@ -3316,7 +3316,7 @@
         <v>3.275070986639969</v>
       </c>
       <c r="Q28" s="89">
-        <f>IF(ABS(N28-2.6113514523)&lt;0.0001,"OK","CHECK")</f>
+        <f>IF(ABS(N28-3.1803912184)&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -3343,16 +3343,16 @@
         <v>0.6312409193029385</v>
       </c>
       <c r="F29" s="82" t="n">
-        <v>1.185479922543897</v>
+        <v>1.483522761824987</v>
       </c>
       <c r="G29" s="82" t="n">
-        <v>0.03883376317698627</v>
+        <v>0.04270242660237237</v>
       </c>
       <c r="H29" s="82" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="82" t="n">
-        <v>0.1112799486776057</v>
+        <v>0.1305213819421677</v>
       </c>
       <c r="J29" s="83">
         <f>SUM(F29:I29)</f>
@@ -3362,7 +3362,7 @@
         <v>0.0993472157523211</v>
       </c>
       <c r="L29" s="84" t="n">
-        <v>0.299689834346019</v>
+        <v>0.3019109552387494</v>
       </c>
       <c r="M29" s="85">
         <f>K29+L29</f>
@@ -3379,7 +3379,7 @@
         <v>3.382515917162146</v>
       </c>
       <c r="Q29" s="89">
-        <f>IF(ABS(N29-1.7346306845)&lt;0.0001,"OK","CHECK")</f>
+        <f>IF(ABS(N29-2.0580047414)&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -3406,16 +3406,16 @@
         <v>0.6312409193029385</v>
       </c>
       <c r="F30" s="82" t="n">
-        <v>1.882829664783011</v>
+        <v>2.355426230060016</v>
       </c>
       <c r="G30" s="82" t="n">
-        <v>0.05093282409934952</v>
+        <v>0.05710233438110449</v>
       </c>
       <c r="H30" s="82" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="82" t="n">
-        <v>0.1556993213430528</v>
+        <v>0.1859227356181512</v>
       </c>
       <c r="J30" s="83">
         <f>SUM(F30:I30)</f>
@@ -3425,7 +3425,7 @@
         <v>0.1928504776368586</v>
       </c>
       <c r="L30" s="84" t="n">
-        <v>0.2597325637849158</v>
+        <v>0.2632746729523353</v>
       </c>
       <c r="M30" s="85">
         <f>K30+L30</f>
@@ -3442,7 +3442,7 @@
         <v>3.692840562983414</v>
       </c>
       <c r="Q30" s="89">
-        <f>IF(ABS(N30-2.5420448516)&lt;0.0001,"OK","CHECK")</f>
+        <f>IF(ABS(N30-3.0545764506)&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
     <row r="2">
       <c r="A2" s="70" t="inlineStr">
         <is>
-          <t>GATP = CRF + OM (decision of 19 Oct 2026); new-build capex at market levels. Previous-draft values kept for comparison.</t>
+          <t>GATP = CRF + OM (decision of 19 Oct 2026); capex at market +25%. Previous-draft values kept for comparison.</t>
         </is>
       </c>
       <c r="B2" s="69" t="n"/>
@@ -4098,10 +4098,10 @@
         <v>30</v>
       </c>
       <c r="F5" s="100" t="n">
-        <v>1.71709536116388</v>
+        <v>2.12354528738614</v>
       </c>
       <c r="G5" s="100" t="n">
-        <v>1.09260513458614</v>
+        <v>1.348155794798428</v>
       </c>
       <c r="H5" s="101">
         <f>G5-F5</f>
@@ -4137,10 +4137,10 @@
         <v>30</v>
       </c>
       <c r="F6" s="100" t="n">
-        <v>1.63932447237903</v>
+        <v>2.045774398601298</v>
       </c>
       <c r="G6" s="100" t="n">
-        <v>1.09257346731619</v>
+        <v>1.348124127528474</v>
       </c>
       <c r="H6" s="101">
         <f>G6-F6</f>
@@ -4176,10 +4176,10 @@
         <v>30</v>
       </c>
       <c r="F7" s="100" t="n">
-        <v>3.840973312069803</v>
+        <v>4.696214229179318</v>
       </c>
       <c r="G7" s="100" t="n">
-        <v>2.611380326955709</v>
+        <v>3.180420093234884</v>
       </c>
       <c r="H7" s="101">
         <f>G7-F7</f>
@@ -4215,10 +4215,10 @@
         <v>30</v>
       </c>
       <c r="F8" s="100" t="n">
-        <v>2.437790821299018</v>
+        <v>2.923807338058453</v>
       </c>
       <c r="G8" s="100" t="n">
-        <v>1.734658316379735</v>
+        <v>2.058032373410724</v>
       </c>
       <c r="H8" s="101">
         <f>G8-F8</f>
@@ -4254,10 +4254,10 @@
         <v>30</v>
       </c>
       <c r="F9" s="100" t="n">
-        <v>3.67523902935652</v>
+        <v>4.445550738342776</v>
       </c>
       <c r="G9" s="100" t="n">
-        <v>2.542071709751747</v>
+        <v>3.054603308830421</v>
       </c>
       <c r="H9" s="101">
         <f>G9-F9</f>
@@ -4293,10 +4293,10 @@
         <v>30</v>
       </c>
       <c r="F10" s="100" t="n">
-        <v>3.84091807921999</v>
+        <v>4.696158996035751</v>
       </c>
       <c r="G10" s="100" t="n">
-        <v>2.611343577441835</v>
+        <v>3.18038334352556</v>
       </c>
       <c r="H10" s="101">
         <f>G10-F10</f>
@@ -4332,10 +4332,10 @@
         <v>30</v>
       </c>
       <c r="F11" s="100" t="n">
-        <v>2.437737965759786</v>
+        <v>2.923754482170276</v>
       </c>
       <c r="G11" s="100" t="n">
-        <v>1.734623148623972</v>
+        <v>2.057997205422789</v>
       </c>
       <c r="H11" s="101">
         <f>G11-F11</f>
@@ -4371,10 +4371,10 @@
         <v>30</v>
       </c>
       <c r="F12" s="100" t="n">
-        <v>3.675187653863974</v>
+        <v>4.44549936268872</v>
       </c>
       <c r="G12" s="100" t="n">
-        <v>2.542037526754084</v>
+        <v>3.054569125725295</v>
       </c>
       <c r="H12" s="101">
         <f>G12-F12</f>
@@ -4410,10 +4410,10 @@
         <v>30</v>
       </c>
       <c r="F13" s="100" t="n">
-        <v>3.840929914725353</v>
+        <v>4.696170831625423</v>
       </c>
       <c r="G13" s="100" t="n">
-        <v>2.611351452267597</v>
+        <v>3.180391218407416</v>
       </c>
       <c r="H13" s="101">
         <f>G13-F13</f>
@@ -4449,10 +4449,10 @@
         <v>30</v>
       </c>
       <c r="F14" s="100" t="n">
-        <v>2.437749291834332</v>
+        <v>2.923765808342443</v>
       </c>
       <c r="G14" s="100" t="n">
-        <v>1.734630684496829</v>
+        <v>2.058004741360597</v>
       </c>
       <c r="H14" s="101">
         <f>G14-F14</f>
@@ -4488,10 +4488,10 @@
         <v>30</v>
       </c>
       <c r="F15" s="100" t="n">
-        <v>3.675198662845537</v>
+        <v>4.44551037171547</v>
       </c>
       <c r="G15" s="100" t="n">
-        <v>2.542044851647188</v>
+        <v>3.054576450648465</v>
       </c>
       <c r="H15" s="101">
         <f>G15-F15</f>
@@ -4559,7 +4559,7 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="106" t="inlineStr">
         <is>
-          <t>• New-build capital cost raised to current market levels (20 Oct 2026): CCGT US$1,200/kW (was 900), gas engine US$1,100/kW (was 850), OCGT US$700/kW (was 520). Equipment cost (F15) recalibrated and the GATP re-solved; existing Lots 1 and 2 unchanged.</t>
+          <t>• Capital cost raised to market +25% (20 Oct 2026): existing CCGT US$600/kW (was 450); new CCGT US$1,500/kW (was 1,200, originally 900), gas engine US$1,375/kW (1,100; 850), OCGT US$875/kW (700; 520). Equipment cost (F15) recalibrated and the GATP re-solved for all 22 models.</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4735,7 @@
     <row r="2">
       <c r="A2" s="70" t="inlineStr">
         <is>
-          <t>Read from each model after the 20 Oct 2026 re-solve (CLLC out of the GATP; new-build capex CCGT US$1,200/kW, gas engine US$1,100/kW, OCGT US$700/kW). Values identical across Fin42 and Fin90 except capacity factor and results.</t>
+          <t>Read from each model after the 20 Oct 2026 re-solve (CLLC out of the GATP; capex at market +25%: existing CCGT US$600/kW, new CCGT US$1,500/kW, gas engine US$1,375/kW, OCGT US$875/kW). Values identical across Fin42 and Fin90 except capacity factor and results.</t>
         </is>
       </c>
       <c r="B2" s="69" t="n"/>
@@ -7057,74 +7057,74 @@
       </c>
       <c r="F35" s="123" t="inlineStr">
         <is>
-          <t>New-build raised 20 Oct 2026 to market levels: CCGT US$1,200/kW, gas engine US$1,100/kW, OCGT US$700/kW (were 900/850/520). Existing plants unchanged (brownfield US$450/kW).</t>
+          <t>Raised 20 Oct 2026 to market +25%: existing CCGT US$600/kW (was 450); new CCGT US$1,500/kW, gas engine US$1,375/kW, OCGT US$875/kW (were 1,200/1,100/700; originally 900/850/520).</t>
         </is>
       </c>
       <c r="G35" s="130" t="n">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="H35" s="130" t="n">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="I35" s="132" t="n">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="J35" s="132" t="n">
-        <v>700</v>
+        <v>875</v>
       </c>
       <c r="K35" s="132" t="n">
-        <v>1100</v>
+        <v>1375</v>
       </c>
       <c r="L35" s="132" t="n">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="M35" s="132" t="n">
-        <v>700</v>
+        <v>875</v>
       </c>
       <c r="N35" s="132" t="n">
-        <v>1100</v>
+        <v>1375</v>
       </c>
       <c r="O35" s="132" t="n">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="P35" s="132" t="n">
-        <v>700</v>
+        <v>875</v>
       </c>
       <c r="Q35" s="132" t="n">
-        <v>1100</v>
+        <v>1375</v>
       </c>
       <c r="R35" s="130" t="n">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="S35" s="130" t="n">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="T35" s="132" t="n">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="U35" s="132" t="n">
-        <v>700</v>
+        <v>875</v>
       </c>
       <c r="V35" s="132" t="n">
-        <v>1100</v>
+        <v>1375</v>
       </c>
       <c r="W35" s="132" t="n">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="X35" s="132" t="n">
-        <v>700</v>
+        <v>875</v>
       </c>
       <c r="Y35" s="132" t="n">
-        <v>1100</v>
+        <v>1375</v>
       </c>
       <c r="Z35" s="132" t="n">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="AA35" s="132" t="n">
-        <v>700</v>
+        <v>875</v>
       </c>
       <c r="AB35" s="132" t="n">
-        <v>1100</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1">
@@ -7159,70 +7159,70 @@
         </is>
       </c>
       <c r="G36" s="133" t="n">
-        <v>450.0000000000019</v>
+        <v>599.9999999999998</v>
       </c>
       <c r="H36" s="133" t="n">
-        <v>450.0000000000015</v>
+        <v>599.9999999999999</v>
       </c>
       <c r="I36" s="134" t="n">
-        <v>1200.000000002668</v>
+        <v>1500.000000001293</v>
       </c>
       <c r="J36" s="134" t="n">
-        <v>700.0000000013767</v>
+        <v>875.000000000624</v>
       </c>
       <c r="K36" s="134" t="n">
-        <v>1100.000000000433</v>
+        <v>1375.000000000261</v>
       </c>
       <c r="L36" s="134" t="n">
-        <v>1200</v>
+        <v>1500.000000006675</v>
       </c>
       <c r="M36" s="134" t="n">
-        <v>700.0000000071039</v>
+        <v>875.0000000032207</v>
       </c>
       <c r="N36" s="134" t="n">
-        <v>1100.000000002231</v>
+        <v>1375.000000001347</v>
       </c>
       <c r="O36" s="134" t="n">
-        <v>1200</v>
+        <v>1500.000000005169</v>
       </c>
       <c r="P36" s="134" t="n">
-        <v>700.0000000055021</v>
+        <v>875.0000000024945</v>
       </c>
       <c r="Q36" s="134" t="n">
-        <v>1100.000000001727</v>
+        <v>1375.000000001044</v>
       </c>
       <c r="R36" s="133" t="n">
-        <v>450.0000000000019</v>
+        <v>599.9999999999998</v>
       </c>
       <c r="S36" s="133" t="n">
-        <v>450.0000000000015</v>
+        <v>599.9999999999999</v>
       </c>
       <c r="T36" s="134" t="n">
-        <v>1200.000000002668</v>
+        <v>1500.000000001293</v>
       </c>
       <c r="U36" s="134" t="n">
-        <v>700.0000000013767</v>
+        <v>875.000000000624</v>
       </c>
       <c r="V36" s="134" t="n">
-        <v>1100.000000000433</v>
+        <v>1375.000000000261</v>
       </c>
       <c r="W36" s="134" t="n">
-        <v>1200</v>
+        <v>1500.000000006675</v>
       </c>
       <c r="X36" s="134" t="n">
-        <v>700.0000000071039</v>
+        <v>875.0000000032207</v>
       </c>
       <c r="Y36" s="134" t="n">
-        <v>1100.000000002231</v>
+        <v>1375.000000001347</v>
       </c>
       <c r="Z36" s="134" t="n">
-        <v>1200</v>
+        <v>1500.000000005169</v>
       </c>
       <c r="AA36" s="134" t="n">
-        <v>700.0000000055021</v>
+        <v>875.0000000024945</v>
       </c>
       <c r="AB36" s="134" t="n">
-        <v>1100.000000001727</v>
+        <v>1375.000000001044</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
@@ -7253,70 +7253,70 @@
       </c>
       <c r="F37" s="123" t="inlineStr"/>
       <c r="G37" s="133" t="n">
-        <v>310.7645790319978</v>
+        <v>414.5423506083426</v>
       </c>
       <c r="H37" s="133" t="n">
-        <v>309.740854777321</v>
+        <v>413.5186263536663</v>
       </c>
       <c r="I37" s="134" t="n">
-        <v>757.8216299537</v>
+        <v>947.47493048312</v>
       </c>
       <c r="J37" s="134" t="n">
-        <v>455.2927785943799</v>
+        <v>569.3142583809845</v>
       </c>
       <c r="K37" s="134" t="n">
-        <v>726.5443341700756</v>
+        <v>908.3788890384991</v>
       </c>
       <c r="L37" s="134" t="n">
-        <v>756.8141744443094</v>
+        <v>946.4674749875754</v>
       </c>
       <c r="M37" s="134" t="n">
-        <v>454.2833269729815</v>
+        <v>568.3048067619046</v>
       </c>
       <c r="N37" s="134" t="n">
-        <v>725.5339346888293</v>
+        <v>907.3684895586309</v>
       </c>
       <c r="O37" s="134" t="n">
-        <v>757.030057770256</v>
+        <v>946.6833583101202</v>
       </c>
       <c r="P37" s="134" t="n">
-        <v>454.4996380358925</v>
+        <v>568.5211178241669</v>
       </c>
       <c r="Q37" s="134" t="n">
-        <v>725.7504488639092</v>
+        <v>907.5850037333259</v>
       </c>
       <c r="R37" s="133" t="n">
-        <v>310.7645790319978</v>
+        <v>414.5423506083426</v>
       </c>
       <c r="S37" s="133" t="n">
-        <v>309.740854777321</v>
+        <v>413.5186263536663</v>
       </c>
       <c r="T37" s="134" t="n">
-        <v>757.8216299537</v>
+        <v>947.47493048312</v>
       </c>
       <c r="U37" s="134" t="n">
-        <v>455.2927785943799</v>
+        <v>569.3142583809845</v>
       </c>
       <c r="V37" s="134" t="n">
-        <v>726.5443341700756</v>
+        <v>908.3788890384991</v>
       </c>
       <c r="W37" s="134" t="n">
-        <v>756.8141744443094</v>
+        <v>946.4674749875754</v>
       </c>
       <c r="X37" s="134" t="n">
-        <v>454.2833269729815</v>
+        <v>568.3048067619046</v>
       </c>
       <c r="Y37" s="134" t="n">
-        <v>725.5339346888293</v>
+        <v>907.3684895586309</v>
       </c>
       <c r="Z37" s="134" t="n">
-        <v>757.030057770256</v>
+        <v>946.6833583101202</v>
       </c>
       <c r="AA37" s="134" t="n">
-        <v>454.4996380358925</v>
+        <v>568.5211178241669</v>
       </c>
       <c r="AB37" s="134" t="n">
-        <v>725.7504488639092</v>
+        <v>907.5850037333259</v>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1">
@@ -7347,70 +7347,70 @@
       </c>
       <c r="F38" s="123" t="inlineStr"/>
       <c r="G38" s="133" t="n">
-        <v>380.6655928127032</v>
+        <v>507.5362606554534</v>
       </c>
       <c r="H38" s="133" t="n">
-        <v>380.7620535247044</v>
+        <v>507.6327213674551</v>
       </c>
       <c r="I38" s="134" t="n">
-        <v>927.502479497927</v>
+        <v>1159.357919552818</v>
       </c>
       <c r="J38" s="134" t="n">
-        <v>557.6541311411593</v>
+        <v>697.047963454307</v>
       </c>
       <c r="K38" s="134" t="n">
-        <v>889.265279526212</v>
+        <v>1111.562126554527</v>
       </c>
       <c r="L38" s="134" t="n">
-        <v>927.6052130907536</v>
+        <v>1159.460653162571</v>
       </c>
       <c r="M38" s="134" t="n">
-        <v>557.7544244420073</v>
+        <v>697.1482567579897</v>
       </c>
       <c r="N38" s="134" t="n">
-        <v>889.3644140470044</v>
+        <v>1111.661261077004</v>
       </c>
       <c r="O38" s="134" t="n">
-        <v>927.583198752497</v>
+        <v>1159.438638820156</v>
       </c>
       <c r="P38" s="134" t="n">
-        <v>557.732933021843</v>
+        <v>697.1267653370321</v>
       </c>
       <c r="Q38" s="134" t="n">
-        <v>889.3431709360505</v>
+        <v>1111.640017965579</v>
       </c>
       <c r="R38" s="133" t="n">
-        <v>380.6655928127032</v>
+        <v>507.5362606554534</v>
       </c>
       <c r="S38" s="133" t="n">
-        <v>380.7620535247044</v>
+        <v>507.6327213674551</v>
       </c>
       <c r="T38" s="134" t="n">
-        <v>927.502479497927</v>
+        <v>1159.357919552818</v>
       </c>
       <c r="U38" s="134" t="n">
-        <v>557.6541311411593</v>
+        <v>697.047963454307</v>
       </c>
       <c r="V38" s="134" t="n">
-        <v>889.265279526212</v>
+        <v>1111.562126554527</v>
       </c>
       <c r="W38" s="134" t="n">
-        <v>927.6052130907536</v>
+        <v>1159.460653162571</v>
       </c>
       <c r="X38" s="134" t="n">
-        <v>557.7544244420073</v>
+        <v>697.1482567579897</v>
       </c>
       <c r="Y38" s="134" t="n">
-        <v>889.3644140470044</v>
+        <v>1111.661261077004</v>
       </c>
       <c r="Z38" s="134" t="n">
-        <v>927.583198752497</v>
+        <v>1159.438638820156</v>
       </c>
       <c r="AA38" s="134" t="n">
-        <v>557.732933021843</v>
+        <v>697.1267653370321</v>
       </c>
       <c r="AB38" s="134" t="n">
-        <v>889.3431709360505</v>
+        <v>1111.640017965579</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
@@ -7539,70 +7539,70 @@
         </is>
       </c>
       <c r="G40" s="136" t="n">
-        <v>247.621178511552</v>
+        <v>330.3126299668069</v>
       </c>
       <c r="H40" s="136" t="n">
-        <v>246.805461973961</v>
+        <v>329.4969134292162</v>
       </c>
       <c r="I40" s="137" t="n">
-        <v>603.8419362180877</v>
+        <v>754.9601039706135</v>
       </c>
       <c r="J40" s="137" t="n">
-        <v>362.7830905134501</v>
+        <v>453.6368592677167</v>
       </c>
       <c r="K40" s="137" t="n">
-        <v>578.9197881833272</v>
+        <v>723.8078797119515</v>
       </c>
       <c r="L40" s="137" t="n">
-        <v>603.039182824151</v>
+        <v>754.1573505877096</v>
       </c>
       <c r="M40" s="137" t="n">
-        <v>361.9787465920171</v>
+        <v>452.8325153481312</v>
       </c>
       <c r="N40" s="137" t="n">
-        <v>578.114688995083</v>
+        <v>723.0027805248055</v>
       </c>
       <c r="O40" s="137" t="n">
-        <v>603.2112014105625</v>
+        <v>754.3293691714105</v>
       </c>
       <c r="P40" s="137" t="n">
-        <v>362.1511060046952</v>
+        <v>453.0048747602923</v>
       </c>
       <c r="Q40" s="137" t="n">
-        <v>578.2872102501269</v>
+        <v>723.1753017795427</v>
       </c>
       <c r="R40" s="136" t="n">
-        <v>247.621178511552</v>
+        <v>330.3126299668069</v>
       </c>
       <c r="S40" s="136" t="n">
-        <v>246.805461973961</v>
+        <v>329.4969134292162</v>
       </c>
       <c r="T40" s="137" t="n">
-        <v>603.8419362180877</v>
+        <v>754.9601039706135</v>
       </c>
       <c r="U40" s="137" t="n">
-        <v>362.7830905134501</v>
+        <v>453.6368592677167</v>
       </c>
       <c r="V40" s="137" t="n">
-        <v>578.9197881833272</v>
+        <v>723.8078797119515</v>
       </c>
       <c r="W40" s="137" t="n">
-        <v>603.039182824151</v>
+        <v>754.1573505877096</v>
       </c>
       <c r="X40" s="137" t="n">
-        <v>361.9787465920171</v>
+        <v>452.8325153481312</v>
       </c>
       <c r="Y40" s="137" t="n">
-        <v>578.114688995083</v>
+        <v>723.0027805248055</v>
       </c>
       <c r="Z40" s="137" t="n">
-        <v>603.2112014105625</v>
+        <v>754.3293691714105</v>
       </c>
       <c r="AA40" s="137" t="n">
-        <v>362.1511060046952</v>
+        <v>453.0048747602923</v>
       </c>
       <c r="AB40" s="137" t="n">
-        <v>578.2872102501269</v>
+        <v>723.1753017795427</v>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1">
@@ -9203,70 +9203,70 @@
       </c>
       <c r="F59" s="123" t="inlineStr"/>
       <c r="G59" s="126" t="n">
-        <v>435070.4106447972</v>
+        <v>580359.2908516801</v>
       </c>
       <c r="H59" s="126" t="n">
-        <v>154870.4273886605</v>
+        <v>206759.3131768332</v>
       </c>
       <c r="I59" s="126" t="n">
-        <v>757821.6299537</v>
+        <v>947474.93048312</v>
       </c>
       <c r="J59" s="126" t="n">
-        <v>455292.7785943799</v>
+        <v>569314.2583809845</v>
       </c>
       <c r="K59" s="126" t="n">
-        <v>726544.3341700756</v>
+        <v>908378.8890384991</v>
       </c>
       <c r="L59" s="126" t="n">
-        <v>332998.2367554961</v>
+        <v>416445.6889945332</v>
       </c>
       <c r="M59" s="126" t="n">
-        <v>199884.6638681118</v>
+        <v>250054.114975238</v>
       </c>
       <c r="N59" s="126" t="n">
-        <v>319234.9312630849</v>
+        <v>399242.1354057976</v>
       </c>
       <c r="O59" s="126" t="n">
-        <v>378515.028885128</v>
+        <v>473341.6791550601</v>
       </c>
       <c r="P59" s="126" t="n">
-        <v>227249.8190179462</v>
+        <v>284260.5589120834</v>
       </c>
       <c r="Q59" s="126" t="n">
-        <v>362875.2244319546</v>
+        <v>453792.501866663</v>
       </c>
       <c r="R59" s="126" t="n">
-        <v>435070.4106447972</v>
+        <v>580359.2908516801</v>
       </c>
       <c r="S59" s="126" t="n">
-        <v>154870.4273886605</v>
+        <v>206759.3131768332</v>
       </c>
       <c r="T59" s="126" t="n">
-        <v>757821.6299537</v>
+        <v>947474.93048312</v>
       </c>
       <c r="U59" s="126" t="n">
-        <v>455292.7785943799</v>
+        <v>569314.2583809845</v>
       </c>
       <c r="V59" s="126" t="n">
-        <v>726544.3341700756</v>
+        <v>908378.8890384991</v>
       </c>
       <c r="W59" s="126" t="n">
-        <v>332998.2367554961</v>
+        <v>416445.6889945332</v>
       </c>
       <c r="X59" s="126" t="n">
-        <v>199884.6638681118</v>
+        <v>250054.114975238</v>
       </c>
       <c r="Y59" s="126" t="n">
-        <v>319234.9312630849</v>
+        <v>399242.1354057976</v>
       </c>
       <c r="Z59" s="126" t="n">
-        <v>378515.028885128</v>
+        <v>473341.6791550601</v>
       </c>
       <c r="AA59" s="126" t="n">
-        <v>227249.8190179462</v>
+        <v>284260.5589120834</v>
       </c>
       <c r="AB59" s="126" t="n">
-        <v>362875.2244319546</v>
+        <v>453792.501866663</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
@@ -9485,70 +9485,70 @@
       </c>
       <c r="F62" s="123" t="inlineStr"/>
       <c r="G62" s="126" t="n">
-        <v>76981.6492033269</v>
+        <v>102628.4154867779</v>
       </c>
       <c r="H62" s="126" t="n">
-        <v>27520.02851381328</v>
+        <v>36679.5879007601</v>
       </c>
       <c r="I62" s="126" t="n">
-        <v>133954.5233663569</v>
+        <v>167432.611067474</v>
       </c>
       <c r="J62" s="126" t="n">
-        <v>80551.35353143782</v>
+        <v>100678.7179877973</v>
       </c>
       <c r="K62" s="126" t="n">
-        <v>128433.3747843129</v>
+        <v>160531.2774202566</v>
       </c>
       <c r="L62" s="126" t="n">
-        <v>58963.60691368263</v>
+        <v>73693.96550324962</v>
       </c>
       <c r="M62" s="126" t="n">
-        <v>35466.05714843821</v>
+        <v>44322.09750941646</v>
       </c>
       <c r="N62" s="126" t="n">
-        <v>56534.07287949516</v>
+        <v>70657.15003941741</v>
       </c>
       <c r="O62" s="126" t="n">
-        <v>66998.3479624046</v>
+        <v>83737.39181388501</v>
       </c>
       <c r="P62" s="126" t="n">
-        <v>40296.6246181497</v>
+        <v>50360.30684647681</v>
       </c>
       <c r="Q62" s="126" t="n">
-        <v>64237.56951220073</v>
+        <v>80286.52083026024</v>
       </c>
       <c r="R62" s="126" t="n">
-        <v>76981.6492033269</v>
+        <v>102628.4154867779</v>
       </c>
       <c r="S62" s="126" t="n">
-        <v>27520.02851381328</v>
+        <v>36679.5879007601</v>
       </c>
       <c r="T62" s="126" t="n">
-        <v>133954.5233663569</v>
+        <v>167432.611067474</v>
       </c>
       <c r="U62" s="126" t="n">
-        <v>80551.35353143782</v>
+        <v>100678.7179877973</v>
       </c>
       <c r="V62" s="126" t="n">
-        <v>128433.3747843129</v>
+        <v>160531.2774202566</v>
       </c>
       <c r="W62" s="126" t="n">
-        <v>58963.60691368263</v>
+        <v>73693.96550324962</v>
       </c>
       <c r="X62" s="126" t="n">
-        <v>35466.05714843821</v>
+        <v>44322.09750941646</v>
       </c>
       <c r="Y62" s="126" t="n">
-        <v>56534.07287949516</v>
+        <v>70657.15003941741</v>
       </c>
       <c r="Z62" s="126" t="n">
-        <v>66998.3479624046</v>
+        <v>83737.39181388501</v>
       </c>
       <c r="AA62" s="126" t="n">
-        <v>40296.6246181497</v>
+        <v>50360.30684647681</v>
       </c>
       <c r="AB62" s="126" t="n">
-        <v>64237.56951220073</v>
+        <v>80286.52083026024</v>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
@@ -9579,70 +9579,70 @@
       </c>
       <c r="F63" s="123" t="inlineStr"/>
       <c r="G63" s="126" t="n">
-        <v>20053.56008966067</v>
+        <v>26736.84857917728</v>
       </c>
       <c r="H63" s="126" t="n">
-        <v>7164.360859878385</v>
+        <v>9551.249606134326</v>
       </c>
       <c r="I63" s="126" t="n">
-        <v>34900.1161778702</v>
+        <v>43624.16800222352</v>
       </c>
       <c r="J63" s="126" t="n">
-        <v>20983.78901534147</v>
+        <v>26228.77708552528</v>
       </c>
       <c r="K63" s="126" t="n">
-        <v>33461.36057182348</v>
+        <v>41825.75009577096</v>
       </c>
       <c r="L63" s="126" t="n">
-        <v>15358.24009075282</v>
+        <v>19196.82289374853</v>
       </c>
       <c r="M63" s="126" t="n">
-        <v>9235.015737933145</v>
+        <v>11542.81048886095</v>
       </c>
       <c r="N63" s="126" t="n">
-        <v>14725.1280381019</v>
+        <v>18405.45942866669</v>
       </c>
       <c r="O63" s="126" t="n">
-        <v>17452.01252871589</v>
+        <v>21814.03844113276</v>
       </c>
       <c r="P63" s="126" t="n">
-        <v>10493.81287482553</v>
+        <v>13116.30690995584</v>
       </c>
       <c r="Q63" s="126" t="n">
-        <v>16732.58152386991</v>
+        <v>20914.7762858665</v>
       </c>
       <c r="R63" s="126" t="n">
-        <v>20053.56008966067</v>
+        <v>26736.84857917728</v>
       </c>
       <c r="S63" s="126" t="n">
-        <v>7164.360859878385</v>
+        <v>9551.249606134326</v>
       </c>
       <c r="T63" s="126" t="n">
-        <v>34900.1161778702</v>
+        <v>43624.16800222352</v>
       </c>
       <c r="U63" s="126" t="n">
-        <v>20983.78901534147</v>
+        <v>26228.77708552528</v>
       </c>
       <c r="V63" s="126" t="n">
-        <v>33461.36057182348</v>
+        <v>41825.75009577096</v>
       </c>
       <c r="W63" s="126" t="n">
-        <v>15358.24009075282</v>
+        <v>19196.82289374853</v>
       </c>
       <c r="X63" s="126" t="n">
-        <v>9235.015737933145</v>
+        <v>11542.81048886095</v>
       </c>
       <c r="Y63" s="126" t="n">
-        <v>14725.1280381019</v>
+        <v>18405.45942866669</v>
       </c>
       <c r="Z63" s="126" t="n">
-        <v>17452.01252871589</v>
+        <v>21814.03844113276</v>
       </c>
       <c r="AA63" s="126" t="n">
-        <v>10493.81287482553</v>
+        <v>13116.30690995584</v>
       </c>
       <c r="AB63" s="126" t="n">
-        <v>16732.58152386991</v>
+        <v>20914.7762858665</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1">
@@ -9673,70 +9673,70 @@
       </c>
       <c r="F64" s="123" t="inlineStr"/>
       <c r="G64" s="126" t="n">
-        <v>37891.91776882572</v>
+        <v>50544.84852129683</v>
       </c>
       <c r="H64" s="126" t="n">
-        <v>13489.8370319167</v>
+        <v>18008.74087208496</v>
       </c>
       <c r="I64" s="126" t="n">
-        <v>65999.70428611556</v>
+        <v>82516.24756980907</v>
       </c>
       <c r="J64" s="126" t="n">
-        <v>39653.04512387666</v>
+        <v>49582.95776398968</v>
       </c>
       <c r="K64" s="126" t="n">
-        <v>63275.82440548581</v>
+        <v>79111.44808074881</v>
       </c>
       <c r="L64" s="126" t="n">
-        <v>29002.64732957065</v>
+        <v>36269.92637492636</v>
       </c>
       <c r="M64" s="126" t="n">
-        <v>17410.04080965132</v>
+        <v>21779.2023713899</v>
       </c>
       <c r="N64" s="126" t="n">
-        <v>27804.02737274662</v>
+        <v>34771.70178991518</v>
       </c>
       <c r="O64" s="126" t="n">
-        <v>32966.617717881</v>
+        <v>41224.88936018253</v>
       </c>
       <c r="P64" s="126" t="n">
-        <v>19793.21984336982</v>
+        <v>24758.17616349904</v>
       </c>
       <c r="Q64" s="126" t="n">
-        <v>31604.57705484878</v>
+        <v>39522.38889252355</v>
       </c>
       <c r="R64" s="126" t="n">
-        <v>37891.91776882572</v>
+        <v>50544.84852129683</v>
       </c>
       <c r="S64" s="126" t="n">
-        <v>13489.8370319167</v>
+        <v>18008.74087208496</v>
       </c>
       <c r="T64" s="126" t="n">
-        <v>65999.70428611556</v>
+        <v>82516.24756980907</v>
       </c>
       <c r="U64" s="126" t="n">
-        <v>39653.04512387666</v>
+        <v>49582.95776398968</v>
       </c>
       <c r="V64" s="126" t="n">
-        <v>63275.82440548581</v>
+        <v>79111.44808074881</v>
       </c>
       <c r="W64" s="126" t="n">
-        <v>29002.64732957065</v>
+        <v>36269.92637492636</v>
       </c>
       <c r="X64" s="126" t="n">
-        <v>17410.04080965132</v>
+        <v>21779.2023713899</v>
       </c>
       <c r="Y64" s="126" t="n">
-        <v>27804.02737274662</v>
+        <v>34771.70178991518</v>
       </c>
       <c r="Z64" s="126" t="n">
-        <v>32966.617717881</v>
+        <v>41224.88936018253</v>
       </c>
       <c r="AA64" s="126" t="n">
-        <v>19793.21984336982</v>
+        <v>24758.17616349904</v>
       </c>
       <c r="AB64" s="126" t="n">
-        <v>31604.57705484878</v>
+        <v>39522.38889252355</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
@@ -9767,70 +9767,70 @@
       </c>
       <c r="F65" s="123" t="inlineStr"/>
       <c r="G65" s="126" t="n">
-        <v>11108.31234256933</v>
+        <v>14811.0831234257</v>
       </c>
       <c r="H65" s="126" t="n">
-        <v>3967.254408060466</v>
+        <v>5289.672544080604</v>
       </c>
       <c r="I65" s="126" t="n">
-        <v>122830.4167780296</v>
+        <v>153539.6743896757</v>
       </c>
       <c r="J65" s="126" t="n">
-        <v>52394.35660067869</v>
+        <v>65494.04242620258</v>
       </c>
       <c r="K65" s="126" t="n">
-        <v>67241.38235307336</v>
+        <v>84052.56024733675</v>
       </c>
       <c r="L65" s="126" t="n">
-        <v>54041.67973966443</v>
+        <v>67553.75308367999</v>
       </c>
       <c r="M65" s="126" t="n">
-        <v>23051.06035763631</v>
+        <v>28814.92211804088</v>
       </c>
       <c r="N65" s="126" t="n">
-        <v>29584.34387253252</v>
+        <v>36981.26214483411</v>
       </c>
       <c r="O65" s="126" t="n">
-        <v>61411.90156313884</v>
+        <v>76766.53036481881</v>
       </c>
       <c r="P65" s="126" t="n">
-        <v>26194.98495407817</v>
+        <v>32744.8278645272</v>
       </c>
       <c r="Q65" s="126" t="n">
-        <v>33619.02656644283</v>
+        <v>42024.61551261343</v>
       </c>
       <c r="R65" s="126" t="n">
-        <v>11108.31234256933</v>
+        <v>14811.0831234257</v>
       </c>
       <c r="S65" s="126" t="n">
-        <v>3967.254408060466</v>
+        <v>5289.672544080604</v>
       </c>
       <c r="T65" s="126" t="n">
-        <v>122830.4167780296</v>
+        <v>153539.6743896757</v>
       </c>
       <c r="U65" s="126" t="n">
-        <v>52394.35660067869</v>
+        <v>65494.04242620258</v>
       </c>
       <c r="V65" s="126" t="n">
-        <v>67241.38235307336</v>
+        <v>84052.56024733675</v>
       </c>
       <c r="W65" s="126" t="n">
-        <v>54041.67973966443</v>
+        <v>67553.75308367999</v>
       </c>
       <c r="X65" s="126" t="n">
-        <v>23051.06035763631</v>
+        <v>28814.92211804088</v>
       </c>
       <c r="Y65" s="126" t="n">
-        <v>29584.34387253252</v>
+        <v>36981.26214483411</v>
       </c>
       <c r="Z65" s="126" t="n">
-        <v>61411.90156313884</v>
+        <v>76766.53036481881</v>
       </c>
       <c r="AA65" s="126" t="n">
-        <v>26194.98495407817</v>
+        <v>32744.8278645272</v>
       </c>
       <c r="AB65" s="126" t="n">
-        <v>33619.02656644283</v>
+        <v>42024.61551261343</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
@@ -9861,70 +9861,70 @@
       </c>
       <c r="F66" s="123" t="inlineStr"/>
       <c r="G66" s="126" t="n">
-        <v>47988.26629412113</v>
+        <v>64013.62978094031</v>
       </c>
       <c r="H66" s="126" t="n">
-        <v>17082.20814096925</v>
+        <v>22805.55224340469</v>
       </c>
       <c r="I66" s="126" t="n">
-        <v>83587.72578389311</v>
+        <v>104506.4848322881</v>
       </c>
       <c r="J66" s="126" t="n">
-        <v>50218.7934789601</v>
+        <v>62795.36269942258</v>
       </c>
       <c r="K66" s="126" t="n">
-        <v>80137.84005895934</v>
+        <v>100194.1914609464</v>
       </c>
       <c r="L66" s="126" t="n">
-        <v>36729.70551413122</v>
+        <v>45933.95949609701</v>
       </c>
       <c r="M66" s="126" t="n">
-        <v>22047.27842465274</v>
+        <v>27580.96888176876</v>
       </c>
       <c r="N66" s="126" t="n">
-        <v>35211.61291831826</v>
+        <v>44036.40753525947</v>
       </c>
       <c r="O66" s="126" t="n">
-        <v>41750.20768602961</v>
+        <v>52209.58721080312</v>
       </c>
       <c r="P66" s="126" t="n">
-        <v>25065.65503767947</v>
+        <v>31353.9396480028</v>
       </c>
       <c r="Q66" s="126" t="n">
-        <v>40025.13725484459</v>
+        <v>50053.31295589292</v>
       </c>
       <c r="R66" s="126" t="n">
-        <v>47988.26629412113</v>
+        <v>64013.62978094031</v>
       </c>
       <c r="S66" s="126" t="n">
-        <v>17082.20814096925</v>
+        <v>22805.55224340469</v>
       </c>
       <c r="T66" s="126" t="n">
-        <v>83587.72578389311</v>
+        <v>104506.4848322881</v>
       </c>
       <c r="U66" s="126" t="n">
-        <v>50218.7934789601</v>
+        <v>62795.36269942258</v>
       </c>
       <c r="V66" s="126" t="n">
-        <v>80137.84005895934</v>
+        <v>100194.1914609464</v>
       </c>
       <c r="W66" s="126" t="n">
-        <v>36729.70551413122</v>
+        <v>45933.95949609701</v>
       </c>
       <c r="X66" s="126" t="n">
-        <v>22047.27842465274</v>
+        <v>27580.96888176876</v>
       </c>
       <c r="Y66" s="126" t="n">
-        <v>35211.61291831826</v>
+        <v>44036.40753525947</v>
       </c>
       <c r="Z66" s="126" t="n">
-        <v>41750.20768602961</v>
+        <v>52209.58721080312</v>
       </c>
       <c r="AA66" s="126" t="n">
-        <v>25065.65503767947</v>
+        <v>31353.9396480028</v>
       </c>
       <c r="AB66" s="126" t="n">
-        <v>40025.13725484459</v>
+        <v>50053.31295589292</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
@@ -9955,70 +9955,70 @@
       </c>
       <c r="F67" s="123" t="inlineStr"/>
       <c r="G67" s="126" t="n">
-        <v>630000.0000000031</v>
+        <v>840000.0000000003</v>
       </c>
       <c r="H67" s="126" t="n">
-        <v>225000.0000000008</v>
+        <v>299999.9999999999</v>
       </c>
       <c r="I67" s="126" t="n">
-        <v>1200000.000002668</v>
+        <v>1500000.000001293</v>
       </c>
       <c r="J67" s="126" t="n">
-        <v>700000.0000013767</v>
+        <v>875000.000000624</v>
       </c>
       <c r="K67" s="126" t="n">
-        <v>1100000.000000433</v>
+        <v>1375000.000000261</v>
       </c>
       <c r="L67" s="126" t="n">
-        <v>528000</v>
+        <v>660000.0000029369</v>
       </c>
       <c r="M67" s="126" t="n">
-        <v>308000.0000031258</v>
+        <v>385000.0000014171</v>
       </c>
       <c r="N67" s="126" t="n">
-        <v>484000.0000009815</v>
+        <v>605000.0000005927</v>
       </c>
       <c r="O67" s="126" t="n">
-        <v>600000</v>
+        <v>750000.0000025844</v>
       </c>
       <c r="P67" s="126" t="n">
-        <v>350000.0000027511</v>
+        <v>437500.0000012473</v>
       </c>
       <c r="Q67" s="126" t="n">
-        <v>550000.0000008636</v>
+        <v>687500.0000005218</v>
       </c>
       <c r="R67" s="126" t="n">
-        <v>630000.0000000031</v>
+        <v>840000.0000000003</v>
       </c>
       <c r="S67" s="126" t="n">
-        <v>225000.0000000008</v>
+        <v>299999.9999999999</v>
       </c>
       <c r="T67" s="126" t="n">
-        <v>1200000.000002668</v>
+        <v>1500000.000001293</v>
       </c>
       <c r="U67" s="126" t="n">
-        <v>700000.0000013767</v>
+        <v>875000.000000624</v>
       </c>
       <c r="V67" s="126" t="n">
-        <v>1100000.000000433</v>
+        <v>1375000.000000261</v>
       </c>
       <c r="W67" s="126" t="n">
-        <v>528000</v>
+        <v>660000.0000029369</v>
       </c>
       <c r="X67" s="126" t="n">
-        <v>308000.0000031258</v>
+        <v>385000.0000014171</v>
       </c>
       <c r="Y67" s="126" t="n">
-        <v>484000.0000009815</v>
+        <v>605000.0000005927</v>
       </c>
       <c r="Z67" s="126" t="n">
-        <v>600000</v>
+        <v>750000.0000025844</v>
       </c>
       <c r="AA67" s="126" t="n">
-        <v>350000.0000027511</v>
+        <v>437500.0000012473</v>
       </c>
       <c r="AB67" s="126" t="n">
-        <v>550000.0000008636</v>
+        <v>687500.0000005218</v>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1">
@@ -10049,70 +10049,70 @@
       </c>
       <c r="F68" s="123" t="inlineStr"/>
       <c r="G68" s="126" t="n">
-        <v>441000.0000000022</v>
+        <v>588000.0000000002</v>
       </c>
       <c r="H68" s="126" t="n">
-        <v>157500.0000000005</v>
+        <v>210000</v>
       </c>
       <c r="I68" s="126" t="n">
-        <v>840000.0000018671</v>
+        <v>1050000.000000905</v>
       </c>
       <c r="J68" s="126" t="n">
-        <v>490000.0000009636</v>
+        <v>612500.0000004368</v>
       </c>
       <c r="K68" s="126" t="n">
-        <v>770000.0000003028</v>
+        <v>962500.0000001823</v>
       </c>
       <c r="L68" s="126" t="n">
-        <v>369600</v>
+        <v>462000.0000020558</v>
       </c>
       <c r="M68" s="126" t="n">
-        <v>215600.000002188</v>
+        <v>269500.000000992</v>
       </c>
       <c r="N68" s="126" t="n">
-        <v>338800.000000687</v>
+        <v>423500.0000004149</v>
       </c>
       <c r="O68" s="126" t="n">
-        <v>420000</v>
+        <v>525000.0000018091</v>
       </c>
       <c r="P68" s="126" t="n">
-        <v>245000.0000019257</v>
+        <v>306250.0000008731</v>
       </c>
       <c r="Q68" s="126" t="n">
-        <v>385000.0000006044</v>
+        <v>481250.0000003652</v>
       </c>
       <c r="R68" s="126" t="n">
-        <v>441000.0000000022</v>
+        <v>588000.0000000002</v>
       </c>
       <c r="S68" s="126" t="n">
-        <v>157500.0000000005</v>
+        <v>210000</v>
       </c>
       <c r="T68" s="126" t="n">
-        <v>840000.0000018671</v>
+        <v>1050000.000000905</v>
       </c>
       <c r="U68" s="126" t="n">
-        <v>490000.0000009636</v>
+        <v>612500.0000004368</v>
       </c>
       <c r="V68" s="126" t="n">
-        <v>770000.0000003028</v>
+        <v>962500.0000001823</v>
       </c>
       <c r="W68" s="126" t="n">
-        <v>369600</v>
+        <v>462000.0000020558</v>
       </c>
       <c r="X68" s="126" t="n">
-        <v>215600.000002188</v>
+        <v>269500.000000992</v>
       </c>
       <c r="Y68" s="126" t="n">
-        <v>338800.000000687</v>
+        <v>423500.0000004149</v>
       </c>
       <c r="Z68" s="126" t="n">
-        <v>420000</v>
+        <v>525000.0000018091</v>
       </c>
       <c r="AA68" s="126" t="n">
-        <v>245000.0000019257</v>
+        <v>306250.0000008731</v>
       </c>
       <c r="AB68" s="126" t="n">
-        <v>385000.0000006044</v>
+        <v>481250.0000003652</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
@@ -10143,70 +10143,70 @@
       </c>
       <c r="F69" s="123" t="inlineStr"/>
       <c r="G69" s="126" t="n">
-        <v>189000.000000001</v>
+        <v>252000.0000000002</v>
       </c>
       <c r="H69" s="126" t="n">
-        <v>67500.00000000022</v>
+        <v>90000</v>
       </c>
       <c r="I69" s="126" t="n">
-        <v>360000.0000008002</v>
+        <v>450000.0000003878</v>
       </c>
       <c r="J69" s="126" t="n">
-        <v>210000.000000413</v>
+        <v>262500.0000001873</v>
       </c>
       <c r="K69" s="126" t="n">
-        <v>330000.0000001298</v>
+        <v>412500.0000000783</v>
       </c>
       <c r="L69" s="126" t="n">
-        <v>158400</v>
+        <v>198000.0000008811</v>
       </c>
       <c r="M69" s="126" t="n">
-        <v>92400.00000093774</v>
+        <v>115500.0000004251</v>
       </c>
       <c r="N69" s="126" t="n">
-        <v>145200.0000002945</v>
+        <v>181500.0000001778</v>
       </c>
       <c r="O69" s="126" t="n">
-        <v>180000</v>
+        <v>225000.0000007753</v>
       </c>
       <c r="P69" s="126" t="n">
-        <v>105000.0000008253</v>
+        <v>131250.0000003742</v>
       </c>
       <c r="Q69" s="126" t="n">
-        <v>165000.0000002591</v>
+        <v>206250.0000001566</v>
       </c>
       <c r="R69" s="126" t="n">
-        <v>189000.000000001</v>
+        <v>252000.0000000002</v>
       </c>
       <c r="S69" s="126" t="n">
-        <v>67500.00000000022</v>
+        <v>90000</v>
       </c>
       <c r="T69" s="126" t="n">
-        <v>360000.0000008002</v>
+        <v>450000.0000003878</v>
       </c>
       <c r="U69" s="126" t="n">
-        <v>210000.000000413</v>
+        <v>262500.0000001873</v>
       </c>
       <c r="V69" s="126" t="n">
-        <v>330000.0000001298</v>
+        <v>412500.0000000783</v>
       </c>
       <c r="W69" s="126" t="n">
-        <v>158400</v>
+        <v>198000.0000008811</v>
       </c>
       <c r="X69" s="126" t="n">
-        <v>92400.00000093774</v>
+        <v>115500.0000004251</v>
       </c>
       <c r="Y69" s="126" t="n">
-        <v>145200.0000002945</v>
+        <v>181500.0000001778</v>
       </c>
       <c r="Z69" s="126" t="n">
-        <v>180000</v>
+        <v>225000.0000007753</v>
       </c>
       <c r="AA69" s="126" t="n">
-        <v>105000.0000008253</v>
+        <v>131250.0000003742</v>
       </c>
       <c r="AB69" s="126" t="n">
-        <v>165000.0000002591</v>
+        <v>206250.0000001566</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
@@ -10237,70 +10237,70 @@
       </c>
       <c r="F70" s="123" t="inlineStr"/>
       <c r="G70" s="126" t="n">
-        <v>630000.0000000031</v>
+        <v>840000.0000000005</v>
       </c>
       <c r="H70" s="126" t="n">
-        <v>225000.0000000008</v>
+        <v>300000</v>
       </c>
       <c r="I70" s="126" t="n">
-        <v>1200000.000002667</v>
+        <v>1500000.000001292</v>
       </c>
       <c r="J70" s="126" t="n">
-        <v>700000.0000013766</v>
+        <v>875000.000000624</v>
       </c>
       <c r="K70" s="126" t="n">
-        <v>1100000.000000433</v>
+        <v>1375000.000000261</v>
       </c>
       <c r="L70" s="126" t="n">
-        <v>528000</v>
+        <v>660000.0000029369</v>
       </c>
       <c r="M70" s="126" t="n">
-        <v>308000.0000031258</v>
+        <v>385000.0000014171</v>
       </c>
       <c r="N70" s="126" t="n">
-        <v>484000.0000009814</v>
+        <v>605000.0000005928</v>
       </c>
       <c r="O70" s="126" t="n">
-        <v>600000</v>
+        <v>750000.0000025844</v>
       </c>
       <c r="P70" s="126" t="n">
-        <v>350000.0000027511</v>
+        <v>437500.0000012473</v>
       </c>
       <c r="Q70" s="126" t="n">
-        <v>550000.0000008636</v>
+        <v>687500.0000005218</v>
       </c>
       <c r="R70" s="126" t="n">
-        <v>630000.0000000031</v>
+        <v>840000.0000000005</v>
       </c>
       <c r="S70" s="126" t="n">
-        <v>225000.0000000008</v>
+        <v>300000</v>
       </c>
       <c r="T70" s="126" t="n">
-        <v>1200000.000002667</v>
+        <v>1500000.000001292</v>
       </c>
       <c r="U70" s="126" t="n">
-        <v>700000.0000013766</v>
+        <v>875000.000000624</v>
       </c>
       <c r="V70" s="126" t="n">
-        <v>1100000.000000433</v>
+        <v>1375000.000000261</v>
       </c>
       <c r="W70" s="126" t="n">
-        <v>528000</v>
+        <v>660000.0000029369</v>
       </c>
       <c r="X70" s="126" t="n">
-        <v>308000.0000031258</v>
+        <v>385000.0000014171</v>
       </c>
       <c r="Y70" s="126" t="n">
-        <v>484000.0000009814</v>
+        <v>605000.0000005928</v>
       </c>
       <c r="Z70" s="126" t="n">
-        <v>600000</v>
+        <v>750000.0000025844</v>
       </c>
       <c r="AA70" s="126" t="n">
-        <v>350000.0000027511</v>
+        <v>437500.0000012473</v>
       </c>
       <c r="AB70" s="126" t="n">
-        <v>550000.0000008636</v>
+        <v>687500.0000005218</v>
       </c>
     </row>
     <row r="72">
@@ -10659,70 +10659,70 @@
       </c>
       <c r="F76" s="123" t="inlineStr"/>
       <c r="G76" s="141" t="n">
-        <v>0.0811717235790007</v>
+        <v>0.06087983948007971</v>
       </c>
       <c r="H76" s="141" t="n">
-        <v>0.0676584939577328</v>
+        <v>0.05074631332083004</v>
       </c>
       <c r="I76" s="141" t="n">
-        <v>0.02777098792146538</v>
+        <v>0.02221699321089768</v>
       </c>
       <c r="J76" s="141" t="n">
-        <v>0.05493391116475157</v>
+        <v>0.0439477661902375</v>
       </c>
       <c r="K76" s="141" t="n">
-        <v>0.0419056837595459</v>
+        <v>0.03352484497967969</v>
       </c>
       <c r="L76" s="141" t="n">
-        <v>0.02776937426272354</v>
+        <v>0.02221596043811579</v>
       </c>
       <c r="M76" s="141" t="n">
-        <v>0.05492884260592908</v>
+        <v>0.04394452215847597</v>
       </c>
       <c r="N76" s="141" t="n">
-        <v>0.04190331368273124</v>
+        <v>0.03352332808634563</v>
       </c>
       <c r="O76" s="141" t="n">
-        <v>0.02776972003086109</v>
+        <v>0.02221618173843729</v>
       </c>
       <c r="P76" s="141" t="n">
-        <v>0.05492992864679443</v>
+        <v>0.04394521726774178</v>
       </c>
       <c r="Q76" s="141" t="n">
-        <v>0.04190382153373486</v>
+        <v>0.03352365312334513</v>
       </c>
       <c r="R76" s="141" t="n">
-        <v>0.08162213373687528</v>
+        <v>0.06121765290700435</v>
       </c>
       <c r="S76" s="141" t="n">
-        <v>0.08161203015971229</v>
+        <v>0.0612119692735261</v>
       </c>
       <c r="T76" s="141" t="n">
-        <v>0.03264932634316756</v>
+        <v>0.02611969958569126</v>
       </c>
       <c r="U76" s="141" t="n">
-        <v>0.07319036890307866</v>
+        <v>0.05855314416413949</v>
       </c>
       <c r="V76" s="141" t="n">
-        <v>0.05157309162767646</v>
+        <v>0.04125884001467503</v>
       </c>
       <c r="W76" s="141" t="n">
-        <v>0.03264742922409431</v>
+        <v>0.02611848539281885</v>
       </c>
       <c r="X76" s="141" t="n">
-        <v>0.07318361588509471</v>
+        <v>0.05854882202729678</v>
       </c>
       <c r="Y76" s="141" t="n">
-        <v>0.05157017478733976</v>
+        <v>0.04125697318249647</v>
       </c>
       <c r="Z76" s="141" t="n">
-        <v>0.03264783573094217</v>
+        <v>0.02611874556744557</v>
       </c>
       <c r="AA76" s="141" t="n">
-        <v>0.0731850628552793</v>
+        <v>0.05854974814565452</v>
       </c>
       <c r="AB76" s="141" t="n">
-        <v>0.05157079979674167</v>
+        <v>0.04125737320372161</v>
       </c>
     </row>
     <row r="77" ht="24" customHeight="1">
@@ -10753,70 +10753,70 @@
       </c>
       <c r="F77" s="123" t="inlineStr"/>
       <c r="G77" s="139" t="n">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="H77" s="139" t="n">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="I77" s="139" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J77" s="139" t="n">
-        <v>21</v>
+        <v>26.25</v>
       </c>
       <c r="K77" s="139" t="n">
-        <v>33</v>
+        <v>41.25</v>
       </c>
       <c r="L77" s="139" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="M77" s="139" t="n">
-        <v>21</v>
+        <v>26.25</v>
       </c>
       <c r="N77" s="139" t="n">
-        <v>33</v>
+        <v>41.25</v>
       </c>
       <c r="O77" s="139" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="P77" s="139" t="n">
-        <v>21</v>
+        <v>26.25</v>
       </c>
       <c r="Q77" s="139" t="n">
-        <v>33</v>
+        <v>41.25</v>
       </c>
       <c r="R77" s="139" t="n">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="S77" s="139" t="n">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="T77" s="139" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="U77" s="139" t="n">
-        <v>21</v>
+        <v>26.25</v>
       </c>
       <c r="V77" s="139" t="n">
-        <v>33</v>
+        <v>41.25</v>
       </c>
       <c r="W77" s="139" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="X77" s="139" t="n">
-        <v>21</v>
+        <v>26.25</v>
       </c>
       <c r="Y77" s="139" t="n">
-        <v>33</v>
+        <v>41.25</v>
       </c>
       <c r="Z77" s="139" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="AA77" s="139" t="n">
-        <v>21</v>
+        <v>26.25</v>
       </c>
       <c r="AB77" s="139" t="n">
-        <v>33</v>
+        <v>41.25</v>
       </c>
     </row>
     <row r="78" ht="24" customHeight="1">
@@ -10847,70 +10847,70 @@
       </c>
       <c r="F78" s="123" t="inlineStr"/>
       <c r="G78" s="139" t="n">
-        <v>1.223091976516634</v>
+        <v>1.630789302022179</v>
       </c>
       <c r="H78" s="139" t="n">
-        <v>1.223091976516634</v>
+        <v>1.630789302022179</v>
       </c>
       <c r="I78" s="139" t="n">
-        <v>3.261578604044357</v>
+        <v>4.076973255055447</v>
       </c>
       <c r="J78" s="139" t="n">
-        <v>1.902587519025875</v>
+        <v>2.378234398782344</v>
       </c>
       <c r="K78" s="139" t="n">
-        <v>2.989780387040661</v>
+        <v>3.737225483800826</v>
       </c>
       <c r="L78" s="139" t="n">
-        <v>3.261578604044358</v>
+        <v>4.076973255055448</v>
       </c>
       <c r="M78" s="139" t="n">
-        <v>1.902587519025875</v>
+        <v>2.378234398782344</v>
       </c>
       <c r="N78" s="139" t="n">
-        <v>2.989780387040661</v>
+        <v>3.737225483800827</v>
       </c>
       <c r="O78" s="139" t="n">
-        <v>3.261578604044357</v>
+        <v>4.076973255055447</v>
       </c>
       <c r="P78" s="139" t="n">
-        <v>1.902587519025875</v>
+        <v>2.378234398782344</v>
       </c>
       <c r="Q78" s="139" t="n">
-        <v>2.989780387040661</v>
+        <v>3.737225483800826</v>
       </c>
       <c r="R78" s="139" t="n">
-        <v>0.7690048439773882</v>
+        <v>1.025339791969851</v>
       </c>
       <c r="S78" s="139" t="n">
-        <v>0.7690048439773882</v>
+        <v>1.025339791969851</v>
       </c>
       <c r="T78" s="139" t="n">
-        <v>2.170111239321003</v>
+        <v>2.712639049151254</v>
       </c>
       <c r="U78" s="139" t="n">
-        <v>1.265898222937252</v>
+        <v>1.582372778671565</v>
       </c>
       <c r="V78" s="139" t="n">
-        <v>1.989268636044253</v>
+        <v>2.486585795055316</v>
       </c>
       <c r="W78" s="139" t="n">
-        <v>2.170111239321003</v>
+        <v>2.712639049151254</v>
       </c>
       <c r="X78" s="139" t="n">
-        <v>1.265898222937252</v>
+        <v>1.582372778671564</v>
       </c>
       <c r="Y78" s="139" t="n">
-        <v>1.989268636044253</v>
+        <v>2.486585795055316</v>
       </c>
       <c r="Z78" s="139" t="n">
-        <v>2.170111239321003</v>
+        <v>2.712639049151254</v>
       </c>
       <c r="AA78" s="139" t="n">
-        <v>1.265898222937252</v>
+        <v>1.582372778671565</v>
       </c>
       <c r="AB78" s="139" t="n">
-        <v>1.989268636044253</v>
+        <v>2.486585795055316</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
@@ -11261,70 +11261,70 @@
       </c>
       <c r="F84" s="123" t="inlineStr"/>
       <c r="G84" s="128" t="n">
-        <v>0.4897879746905529</v>
+        <v>0.4895628596114459</v>
       </c>
       <c r="H84" s="128" t="n">
-        <v>0.4914088032601224</v>
+        <v>0.4907784810386232</v>
       </c>
       <c r="I84" s="128" t="n">
-        <v>0.4894048771121579</v>
+        <v>0.489301405072798</v>
       </c>
       <c r="J84" s="128" t="n">
-        <v>0.4897480495016082</v>
+        <v>0.4895759434087582</v>
       </c>
       <c r="K84" s="128" t="n">
-        <v>0.4894271248846355</v>
+        <v>0.4893192030608538</v>
       </c>
       <c r="L84" s="128" t="n">
-        <v>0.4900633295905272</v>
+        <v>0.4898281691724303</v>
       </c>
       <c r="M84" s="128" t="n">
-        <v>0.490843259166844</v>
+        <v>0.4904521150256014</v>
       </c>
       <c r="N84" s="128" t="n">
-        <v>0.4901138968664241</v>
+        <v>0.4898686218055564</v>
       </c>
       <c r="O84" s="128" t="n">
-        <v>0.4899222334971803</v>
+        <v>0.4897152917055201</v>
       </c>
       <c r="P84" s="128" t="n">
-        <v>0.4906085729711289</v>
+        <v>0.4902643649822608</v>
       </c>
       <c r="Q84" s="128" t="n">
-        <v>0.4899667319161581</v>
+        <v>0.4897508895210251</v>
       </c>
       <c r="R84" s="128" t="n">
-        <v>0.4897879746905529</v>
+        <v>0.4895628596114459</v>
       </c>
       <c r="S84" s="128" t="n">
-        <v>0.4914088032601224</v>
+        <v>0.4907784810386232</v>
       </c>
       <c r="T84" s="128" t="n">
-        <v>0.4894048771121579</v>
+        <v>0.489301405072798</v>
       </c>
       <c r="U84" s="128" t="n">
-        <v>0.4897480495016082</v>
+        <v>0.4895759434087582</v>
       </c>
       <c r="V84" s="128" t="n">
-        <v>0.4894271248846355</v>
+        <v>0.4893192030608538</v>
       </c>
       <c r="W84" s="128" t="n">
-        <v>0.4900633295905272</v>
+        <v>0.4898281691724303</v>
       </c>
       <c r="X84" s="128" t="n">
-        <v>0.490843259166844</v>
+        <v>0.4904521150256014</v>
       </c>
       <c r="Y84" s="128" t="n">
-        <v>0.4901138968664241</v>
+        <v>0.4898686218055564</v>
       </c>
       <c r="Z84" s="128" t="n">
-        <v>0.4899222334971803</v>
+        <v>0.4897152917055201</v>
       </c>
       <c r="AA84" s="128" t="n">
-        <v>0.4906085729711289</v>
+        <v>0.4902643649822608</v>
       </c>
       <c r="AB84" s="128" t="n">
-        <v>0.4899667319161581</v>
+        <v>0.4897508895210251</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
@@ -11355,70 +11355,70 @@
       </c>
       <c r="F85" s="123" t="inlineStr"/>
       <c r="G85" s="128" t="n">
-        <v>0.5102120253094471</v>
+        <v>0.5104371403885539</v>
       </c>
       <c r="H85" s="128" t="n">
-        <v>0.5085911967398776</v>
+        <v>0.5092215189613769</v>
       </c>
       <c r="I85" s="128" t="n">
-        <v>0.5105951228878421</v>
+        <v>0.5106985949272019</v>
       </c>
       <c r="J85" s="128" t="n">
-        <v>0.510251950498392</v>
+        <v>0.510424056591242</v>
       </c>
       <c r="K85" s="128" t="n">
-        <v>0.5105728751153646</v>
+        <v>0.5106807969391461</v>
       </c>
       <c r="L85" s="128" t="n">
-        <v>0.5099366704094728</v>
+        <v>0.5101718308275697</v>
       </c>
       <c r="M85" s="128" t="n">
-        <v>0.5091567408331559</v>
+        <v>0.5095478849743985</v>
       </c>
       <c r="N85" s="128" t="n">
-        <v>0.5098861031335759</v>
+        <v>0.5101313781944437</v>
       </c>
       <c r="O85" s="128" t="n">
-        <v>0.5100777665028198</v>
+        <v>0.5102847082944798</v>
       </c>
       <c r="P85" s="128" t="n">
-        <v>0.5093914270288711</v>
+        <v>0.5097356350177393</v>
       </c>
       <c r="Q85" s="128" t="n">
-        <v>0.510033268083842</v>
+        <v>0.510249110478975</v>
       </c>
       <c r="R85" s="128" t="n">
-        <v>0.5102120253094471</v>
+        <v>0.5104371403885539</v>
       </c>
       <c r="S85" s="128" t="n">
-        <v>0.5085911967398776</v>
+        <v>0.5092215189613769</v>
       </c>
       <c r="T85" s="128" t="n">
-        <v>0.5105951228878421</v>
+        <v>0.5106985949272019</v>
       </c>
       <c r="U85" s="128" t="n">
-        <v>0.510251950498392</v>
+        <v>0.510424056591242</v>
       </c>
       <c r="V85" s="128" t="n">
-        <v>0.5105728751153646</v>
+        <v>0.5106807969391461</v>
       </c>
       <c r="W85" s="128" t="n">
-        <v>0.5099366704094728</v>
+        <v>0.5101718308275697</v>
       </c>
       <c r="X85" s="128" t="n">
-        <v>0.5091567408331559</v>
+        <v>0.5095478849743985</v>
       </c>
       <c r="Y85" s="128" t="n">
-        <v>0.5098861031335759</v>
+        <v>0.5101313781944437</v>
       </c>
       <c r="Z85" s="128" t="n">
-        <v>0.5100777665028198</v>
+        <v>0.5102847082944798</v>
       </c>
       <c r="AA85" s="128" t="n">
-        <v>0.5093914270288711</v>
+        <v>0.5097356350177393</v>
       </c>
       <c r="AB85" s="128" t="n">
-        <v>0.510033268083842</v>
+        <v>0.510249110478975</v>
       </c>
     </row>
     <row r="86" ht="24" customHeight="1">
@@ -12225,70 +12225,70 @@
       </c>
       <c r="F94" s="123" t="inlineStr"/>
       <c r="G94" s="126" t="n">
-        <v>119566.4240550489</v>
+        <v>159232.8020736146</v>
       </c>
       <c r="H94" s="126" t="n">
-        <v>43066.9807335277</v>
+        <v>57233.54431158697</v>
       </c>
       <c r="I94" s="126" t="n">
-        <v>227285.8525350946</v>
+        <v>283952.1076094415</v>
       </c>
       <c r="J94" s="126" t="n">
-        <v>132823.6346513869</v>
+        <v>165878.9504827817</v>
       </c>
       <c r="K94" s="126" t="n">
-        <v>208369.8373731809</v>
+        <v>260313.9042087232</v>
       </c>
       <c r="L94" s="126" t="n">
-        <v>100353.4380237983</v>
+        <v>125286.5916543615</v>
       </c>
       <c r="M94" s="126" t="n">
-        <v>58779.72382398446</v>
+        <v>73324.0642851264</v>
       </c>
       <c r="N94" s="126" t="n">
-        <v>92015.12608353581</v>
+        <v>114870.5161924741</v>
       </c>
       <c r="O94" s="126" t="n">
-        <v>113953.3400983082</v>
+        <v>142286.4687796304</v>
       </c>
       <c r="P94" s="126" t="n">
-        <v>66713.00054041948</v>
+        <v>83240.65967997638</v>
       </c>
       <c r="Q94" s="126" t="n">
-        <v>104481.702554051</v>
+        <v>130453.7365458037</v>
       </c>
       <c r="R94" s="126" t="n">
-        <v>119566.4240550489</v>
+        <v>159232.8020736146</v>
       </c>
       <c r="S94" s="126" t="n">
-        <v>43066.9807335277</v>
+        <v>57233.54431158697</v>
       </c>
       <c r="T94" s="126" t="n">
-        <v>227285.8525350946</v>
+        <v>283952.1076094415</v>
       </c>
       <c r="U94" s="126" t="n">
-        <v>132823.6346513869</v>
+        <v>165878.9504827817</v>
       </c>
       <c r="V94" s="126" t="n">
-        <v>208369.8373731809</v>
+        <v>260313.9042087232</v>
       </c>
       <c r="W94" s="126" t="n">
-        <v>100353.4380237983</v>
+        <v>125286.5916543615</v>
       </c>
       <c r="X94" s="126" t="n">
-        <v>58779.72382398446</v>
+        <v>73324.0642851264</v>
       </c>
       <c r="Y94" s="126" t="n">
-        <v>92015.12608353581</v>
+        <v>114870.5161924741</v>
       </c>
       <c r="Z94" s="126" t="n">
-        <v>113953.3400983082</v>
+        <v>142286.4687796304</v>
       </c>
       <c r="AA94" s="126" t="n">
-        <v>66713.00054041948</v>
+        <v>83240.65967997638</v>
       </c>
       <c r="AB94" s="126" t="n">
-        <v>104481.702554051</v>
+        <v>130453.7365458037</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
@@ -12319,70 +12319,70 @@
       </c>
       <c r="F95" s="123" t="inlineStr"/>
       <c r="G95" s="126" t="n">
-        <v>321433.5759449532</v>
+        <v>428767.1979263856</v>
       </c>
       <c r="H95" s="126" t="n">
-        <v>114433.0192664728</v>
+        <v>152766.455688413</v>
       </c>
       <c r="I95" s="126" t="n">
-        <v>612714.1474667725</v>
+        <v>766047.892391463</v>
       </c>
       <c r="J95" s="126" t="n">
-        <v>357176.3653495767</v>
+        <v>446621.0495176552</v>
       </c>
       <c r="K95" s="126" t="n">
-        <v>561630.1626271219</v>
+        <v>702186.0957914591</v>
       </c>
       <c r="L95" s="126" t="n">
-        <v>269246.5619762017</v>
+        <v>336713.4083476944</v>
       </c>
       <c r="M95" s="126" t="n">
-        <v>156820.2761782036</v>
+        <v>196175.9357158656</v>
       </c>
       <c r="N95" s="126" t="n">
-        <v>246784.8739171512</v>
+        <v>308629.4838079407</v>
       </c>
       <c r="O95" s="126" t="n">
-        <v>306046.6599016918</v>
+        <v>382713.5312221787</v>
       </c>
       <c r="P95" s="126" t="n">
-        <v>178286.9994615063</v>
+        <v>223009.3403208967</v>
       </c>
       <c r="Q95" s="126" t="n">
-        <v>280518.2974465535</v>
+        <v>350796.2634545615</v>
       </c>
       <c r="R95" s="126" t="n">
-        <v>321433.5759449532</v>
+        <v>428767.1979263856</v>
       </c>
       <c r="S95" s="126" t="n">
-        <v>114433.0192664728</v>
+        <v>152766.455688413</v>
       </c>
       <c r="T95" s="126" t="n">
-        <v>612714.1474667725</v>
+        <v>766047.892391463</v>
       </c>
       <c r="U95" s="126" t="n">
-        <v>357176.3653495767</v>
+        <v>446621.0495176552</v>
       </c>
       <c r="V95" s="126" t="n">
-        <v>561630.1626271219</v>
+        <v>702186.0957914591</v>
       </c>
       <c r="W95" s="126" t="n">
-        <v>269246.5619762017</v>
+        <v>336713.4083476944</v>
       </c>
       <c r="X95" s="126" t="n">
-        <v>156820.2761782036</v>
+        <v>196175.9357158656</v>
       </c>
       <c r="Y95" s="126" t="n">
-        <v>246784.8739171512</v>
+        <v>308629.4838079407</v>
       </c>
       <c r="Z95" s="126" t="n">
-        <v>306046.6599016918</v>
+        <v>382713.5312221787</v>
       </c>
       <c r="AA95" s="126" t="n">
-        <v>178286.9994615063</v>
+        <v>223009.3403208967</v>
       </c>
       <c r="AB95" s="126" t="n">
-        <v>280518.2974465535</v>
+        <v>350796.2634545615</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1">
@@ -12413,70 +12413,70 @@
       </c>
       <c r="F96" s="123" t="inlineStr"/>
       <c r="G96" s="126" t="n">
-        <v>441000.0000000021</v>
+        <v>588000.0000000002</v>
       </c>
       <c r="H96" s="126" t="n">
-        <v>157500.0000000005</v>
+        <v>210000</v>
       </c>
       <c r="I96" s="126" t="n">
-        <v>840000.0000018671</v>
+        <v>1050000.000000905</v>
       </c>
       <c r="J96" s="126" t="n">
-        <v>490000.0000009636</v>
+        <v>612500.0000004369</v>
       </c>
       <c r="K96" s="126" t="n">
-        <v>770000.0000003028</v>
+        <v>962500.0000001823</v>
       </c>
       <c r="L96" s="126" t="n">
-        <v>369600</v>
+        <v>462000.0000020558</v>
       </c>
       <c r="M96" s="126" t="n">
-        <v>215600.000002188</v>
+        <v>269500.000000992</v>
       </c>
       <c r="N96" s="126" t="n">
-        <v>338800.000000687</v>
+        <v>423500.0000004148</v>
       </c>
       <c r="O96" s="126" t="n">
-        <v>420000</v>
+        <v>525000.0000018091</v>
       </c>
       <c r="P96" s="126" t="n">
-        <v>245000.0000019257</v>
+        <v>306250.0000008731</v>
       </c>
       <c r="Q96" s="126" t="n">
-        <v>385000.0000006045</v>
+        <v>481250.0000003652</v>
       </c>
       <c r="R96" s="126" t="n">
-        <v>441000.0000000021</v>
+        <v>588000.0000000002</v>
       </c>
       <c r="S96" s="126" t="n">
-        <v>157500.0000000005</v>
+        <v>210000</v>
       </c>
       <c r="T96" s="126" t="n">
-        <v>840000.0000018671</v>
+        <v>1050000.000000905</v>
       </c>
       <c r="U96" s="126" t="n">
-        <v>490000.0000009636</v>
+        <v>612500.0000004369</v>
       </c>
       <c r="V96" s="126" t="n">
-        <v>770000.0000003028</v>
+        <v>962500.0000001823</v>
       </c>
       <c r="W96" s="126" t="n">
-        <v>369600</v>
+        <v>462000.0000020558</v>
       </c>
       <c r="X96" s="126" t="n">
-        <v>215600.000002188</v>
+        <v>269500.000000992</v>
       </c>
       <c r="Y96" s="126" t="n">
-        <v>338800.000000687</v>
+        <v>423500.0000004148</v>
       </c>
       <c r="Z96" s="126" t="n">
-        <v>420000</v>
+        <v>525000.0000018091</v>
       </c>
       <c r="AA96" s="126" t="n">
-        <v>245000.0000019257</v>
+        <v>306250.0000008731</v>
       </c>
       <c r="AB96" s="126" t="n">
-        <v>385000.0000006045</v>
+        <v>481250.0000003652</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1">
@@ -12507,70 +12507,70 @@
       </c>
       <c r="F97" s="123" t="inlineStr"/>
       <c r="G97" s="126" t="n">
-        <v>189000.000000001</v>
+        <v>252000.0000000002</v>
       </c>
       <c r="H97" s="126" t="n">
-        <v>67500.00000000022</v>
+        <v>90000</v>
       </c>
       <c r="I97" s="126" t="n">
-        <v>360000.0000008002</v>
+        <v>450000.0000003878</v>
       </c>
       <c r="J97" s="126" t="n">
-        <v>210000.000000413</v>
+        <v>262500.0000001873</v>
       </c>
       <c r="K97" s="126" t="n">
-        <v>330000.0000001298</v>
+        <v>412500.0000000783</v>
       </c>
       <c r="L97" s="126" t="n">
-        <v>158400</v>
+        <v>198000.0000008811</v>
       </c>
       <c r="M97" s="126" t="n">
-        <v>92400.00000093774</v>
+        <v>115500.0000004251</v>
       </c>
       <c r="N97" s="126" t="n">
-        <v>145200.0000002945</v>
+        <v>181500.0000001778</v>
       </c>
       <c r="O97" s="126" t="n">
-        <v>180000</v>
+        <v>225000.0000007753</v>
       </c>
       <c r="P97" s="126" t="n">
-        <v>105000.0000008253</v>
+        <v>131250.0000003742</v>
       </c>
       <c r="Q97" s="126" t="n">
-        <v>165000.0000002591</v>
+        <v>206250.0000001566</v>
       </c>
       <c r="R97" s="126" t="n">
-        <v>189000.000000001</v>
+        <v>252000.0000000002</v>
       </c>
       <c r="S97" s="126" t="n">
-        <v>67500.00000000022</v>
+        <v>90000</v>
       </c>
       <c r="T97" s="126" t="n">
-        <v>360000.0000008002</v>
+        <v>450000.0000003878</v>
       </c>
       <c r="U97" s="126" t="n">
-        <v>210000.000000413</v>
+        <v>262500.0000001873</v>
       </c>
       <c r="V97" s="126" t="n">
-        <v>330000.0000001298</v>
+        <v>412500.0000000783</v>
       </c>
       <c r="W97" s="126" t="n">
-        <v>158400</v>
+        <v>198000.0000008811</v>
       </c>
       <c r="X97" s="126" t="n">
-        <v>92400.00000093774</v>
+        <v>115500.0000004251</v>
       </c>
       <c r="Y97" s="126" t="n">
-        <v>145200.0000002945</v>
+        <v>181500.0000001778</v>
       </c>
       <c r="Z97" s="126" t="n">
-        <v>180000</v>
+        <v>225000.0000007753</v>
       </c>
       <c r="AA97" s="126" t="n">
-        <v>105000.0000008253</v>
+        <v>131250.0000003742</v>
       </c>
       <c r="AB97" s="126" t="n">
-        <v>165000.0000002591</v>
+        <v>206250.0000001566</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1">
@@ -12803,28 +12803,28 @@
         <v>0.08400000000000002</v>
       </c>
       <c r="I100" s="141" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08399999999999999</v>
       </c>
       <c r="J100" s="141" t="n">
         <v>0.08400000000000002</v>
       </c>
       <c r="K100" s="141" t="n">
-        <v>0.08400000000000002</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L100" s="141" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08399999999999999</v>
       </c>
       <c r="M100" s="141" t="n">
         <v>0.08399999999999999</v>
       </c>
       <c r="N100" s="141" t="n">
+        <v>0.08400000000000002</v>
+      </c>
+      <c r="O100" s="141" t="n">
         <v>0.08399999999999999</v>
       </c>
-      <c r="O100" s="141" t="n">
+      <c r="P100" s="141" t="n">
         <v>0.08400000000000002</v>
-      </c>
-      <c r="P100" s="141" t="n">
-        <v>0.08400000000000001</v>
       </c>
       <c r="Q100" s="141" t="n">
         <v>0.08400000000000002</v>
@@ -12836,28 +12836,28 @@
         <v>0.08400000000000002</v>
       </c>
       <c r="T100" s="141" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08399999999999999</v>
       </c>
       <c r="U100" s="141" t="n">
         <v>0.08400000000000002</v>
       </c>
       <c r="V100" s="141" t="n">
-        <v>0.08400000000000002</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="W100" s="141" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08399999999999999</v>
       </c>
       <c r="X100" s="141" t="n">
         <v>0.08399999999999999</v>
       </c>
       <c r="Y100" s="141" t="n">
+        <v>0.08400000000000002</v>
+      </c>
+      <c r="Z100" s="141" t="n">
         <v>0.08399999999999999</v>
       </c>
-      <c r="Z100" s="141" t="n">
+      <c r="AA100" s="141" t="n">
         <v>0.08400000000000002</v>
-      </c>
-      <c r="AA100" s="141" t="n">
-        <v>0.08400000000000001</v>
       </c>
       <c r="AB100" s="141" t="n">
         <v>0.08400000000000002</v>
@@ -12903,7 +12903,7 @@
         <v>0.09800000000000002</v>
       </c>
       <c r="K101" s="141" t="n">
-        <v>0.09800000000000002</v>
+        <v>0.098</v>
       </c>
       <c r="L101" s="141" t="n">
         <v>0.098</v>
@@ -12912,13 +12912,13 @@
         <v>0.098</v>
       </c>
       <c r="N101" s="141" t="n">
+        <v>0.09800000000000002</v>
+      </c>
+      <c r="O101" s="141" t="n">
         <v>0.098</v>
       </c>
-      <c r="O101" s="141" t="n">
+      <c r="P101" s="141" t="n">
         <v>0.09800000000000002</v>
-      </c>
-      <c r="P101" s="141" t="n">
-        <v>0.098</v>
       </c>
       <c r="Q101" s="141" t="n">
         <v>0.09800000000000002</v>
@@ -12936,7 +12936,7 @@
         <v>0.09800000000000002</v>
       </c>
       <c r="V101" s="141" t="n">
-        <v>0.09800000000000002</v>
+        <v>0.098</v>
       </c>
       <c r="W101" s="141" t="n">
         <v>0.098</v>
@@ -12945,13 +12945,13 @@
         <v>0.098</v>
       </c>
       <c r="Y101" s="141" t="n">
+        <v>0.09800000000000002</v>
+      </c>
+      <c r="Z101" s="141" t="n">
         <v>0.098</v>
       </c>
-      <c r="Z101" s="141" t="n">
+      <c r="AA101" s="141" t="n">
         <v>0.09800000000000002</v>
-      </c>
-      <c r="AA101" s="141" t="n">
-        <v>0.098</v>
       </c>
       <c r="AB101" s="141" t="n">
         <v>0.09800000000000002</v>
@@ -16357,70 +16357,70 @@
         </is>
       </c>
       <c r="G144" s="145" t="n">
-        <v>1.71709536116388</v>
+        <v>2.12354528738614</v>
       </c>
       <c r="H144" s="145" t="n">
-        <v>1.63932447237903</v>
+        <v>2.045774398601298</v>
       </c>
       <c r="I144" s="146" t="n">
-        <v>3.840973312069803</v>
+        <v>4.696214229179318</v>
       </c>
       <c r="J144" s="146" t="n">
-        <v>2.437790821299018</v>
+        <v>2.923807338058453</v>
       </c>
       <c r="K144" s="146" t="n">
-        <v>3.67523902935652</v>
+        <v>4.445550738342776</v>
       </c>
       <c r="L144" s="146" t="n">
-        <v>3.84091807921999</v>
+        <v>4.696158996035751</v>
       </c>
       <c r="M144" s="146" t="n">
-        <v>2.437737965759786</v>
+        <v>2.923754482170276</v>
       </c>
       <c r="N144" s="146" t="n">
-        <v>3.675187653863974</v>
+        <v>4.44549936268872</v>
       </c>
       <c r="O144" s="146" t="n">
-        <v>3.840929914725353</v>
+        <v>4.696170831625423</v>
       </c>
       <c r="P144" s="146" t="n">
-        <v>2.437749291834332</v>
+        <v>2.923765808342443</v>
       </c>
       <c r="Q144" s="146" t="n">
-        <v>3.675198662845537</v>
+        <v>4.44551037171547</v>
       </c>
       <c r="R144" s="145" t="n">
-        <v>1.09260513458614</v>
+        <v>1.348155794798428</v>
       </c>
       <c r="S144" s="145" t="n">
-        <v>1.09257346731619</v>
+        <v>1.348124127528474</v>
       </c>
       <c r="T144" s="146" t="n">
-        <v>2.611380326955709</v>
+        <v>3.180420093234884</v>
       </c>
       <c r="U144" s="146" t="n">
-        <v>1.734658316379735</v>
+        <v>2.058032373410724</v>
       </c>
       <c r="V144" s="146" t="n">
-        <v>2.542071709751747</v>
+        <v>3.054603308830421</v>
       </c>
       <c r="W144" s="146" t="n">
-        <v>2.611343577441835</v>
+        <v>3.18038334352556</v>
       </c>
       <c r="X144" s="146" t="n">
-        <v>1.734623148623972</v>
+        <v>2.057997205422789</v>
       </c>
       <c r="Y144" s="146" t="n">
-        <v>2.542037526754084</v>
+        <v>3.054569125725295</v>
       </c>
       <c r="Z144" s="146" t="n">
-        <v>2.611351452267597</v>
+        <v>3.180391218407416</v>
       </c>
       <c r="AA144" s="146" t="n">
-        <v>1.734630684496829</v>
+        <v>2.058004741360597</v>
       </c>
       <c r="AB144" s="146" t="n">
-        <v>2.542044851647188</v>
+        <v>3.054576450648465</v>
       </c>
     </row>
     <row r="145" ht="24" customHeight="1">
@@ -16451,70 +16451,70 @@
       </c>
       <c r="F145" s="123" t="inlineStr"/>
       <c r="G145" s="147" t="n">
-        <v>0.02736145326604436</v>
+        <v>0.03383812364373351</v>
       </c>
       <c r="H145" s="147" t="n">
-        <v>0.02612219504715135</v>
+        <v>0.03259886542484061</v>
       </c>
       <c r="I145" s="147" t="n">
-        <v>0.06120487781359238</v>
+        <v>0.07483291205907511</v>
       </c>
       <c r="J145" s="147" t="n">
-        <v>0.03884554180156508</v>
+        <v>0.04659008442313808</v>
       </c>
       <c r="K145" s="147" t="n">
-        <v>0.05856394654465741</v>
+        <v>0.07083865667574059</v>
       </c>
       <c r="L145" s="147" t="n">
-        <v>0.06120399769296943</v>
+        <v>0.07483203193377129</v>
       </c>
       <c r="M145" s="147" t="n">
-        <v>0.03884469956274756</v>
+        <v>0.04658924217876021</v>
       </c>
       <c r="N145" s="147" t="n">
-        <v>0.0585631278899862</v>
+        <v>0.07083783801849576</v>
       </c>
       <c r="O145" s="147" t="n">
-        <v>0.06120418628856768</v>
+        <v>0.07483222053071296</v>
       </c>
       <c r="P145" s="147" t="n">
-        <v>0.0388448800407026</v>
+        <v>0.0465894226582708</v>
       </c>
       <c r="Q145" s="147" t="n">
-        <v>0.05856330331514974</v>
+        <v>0.07083801344437934</v>
       </c>
       <c r="R145" s="147" t="n">
-        <v>0.01741036928080407</v>
+        <v>0.02148250039515629</v>
       </c>
       <c r="S145" s="147" t="n">
-        <v>0.01740986467136513</v>
+        <v>0.02148199578571728</v>
       </c>
       <c r="T145" s="147" t="n">
-        <v>0.04161164393772244</v>
+        <v>0.05067913973540194</v>
       </c>
       <c r="U145" s="147" t="n">
-        <v>0.027641314238953</v>
+        <v>0.03279419296020659</v>
       </c>
       <c r="V145" s="147" t="n">
-        <v>0.04050722974300063</v>
+        <v>0.04867428307780006</v>
       </c>
       <c r="W145" s="147" t="n">
-        <v>0.04161105834409196</v>
+        <v>0.05067855413865702</v>
       </c>
       <c r="X145" s="147" t="n">
-        <v>0.02764075385021308</v>
+        <v>0.03279363256776704</v>
       </c>
       <c r="Y145" s="147" t="n">
-        <v>0.04050668504611645</v>
+        <v>0.04867373837920351</v>
       </c>
       <c r="Z145" s="147" t="n">
-        <v>0.04161118382732482</v>
+        <v>0.05067867962278373</v>
       </c>
       <c r="AA145" s="147" t="n">
-        <v>0.02764087393232247</v>
+        <v>0.03279375265091142</v>
       </c>
       <c r="AB145" s="147" t="n">
-        <v>0.04050680176632016</v>
+        <v>0.04867385509988631</v>
       </c>
     </row>
     <row r="146" ht="15" customHeight="1">
@@ -16545,10 +16545,10 @@
       </c>
       <c r="F146" s="123" t="inlineStr"/>
       <c r="G146" s="148" t="n">
-        <v>0.1400000000000007</v>
+        <v>0.14</v>
       </c>
       <c r="H146" s="148" t="n">
-        <v>0.1399999999999994</v>
+        <v>0.1400000000000002</v>
       </c>
       <c r="I146" s="148" t="n">
         <v>0.1400000000000002</v>
@@ -16557,58 +16557,58 @@
         <v>0.1400000000000001</v>
       </c>
       <c r="K146" s="148" t="n">
-        <v>0.1400000000000002</v>
+        <v>0.14</v>
       </c>
       <c r="L146" s="148" t="n">
         <v>0.1400000000000001</v>
       </c>
       <c r="M146" s="148" t="n">
-        <v>0.1400000000000002</v>
+        <v>0.1400000000000001</v>
       </c>
       <c r="N146" s="148" t="n">
         <v>0.1400000000000001</v>
       </c>
       <c r="O146" s="148" t="n">
-        <v>0.14</v>
+        <v>0.1400000000000002</v>
       </c>
       <c r="P146" s="148" t="n">
         <v>0.14</v>
       </c>
       <c r="Q146" s="148" t="n">
+        <v>0.1400000000000001</v>
+      </c>
+      <c r="R146" s="148" t="n">
         <v>0.1400000000000002</v>
       </c>
-      <c r="R146" s="148" t="n">
-        <v>0.1399999999999984</v>
-      </c>
       <c r="S146" s="148" t="n">
-        <v>0.1400000000000003</v>
+        <v>0.1400000000000001</v>
       </c>
       <c r="T146" s="148" t="n">
-        <v>0.1400000000000001</v>
+        <v>0.1400000000000002</v>
       </c>
       <c r="U146" s="148" t="n">
-        <v>0.1400000000000001</v>
+        <v>0.1400000000000002</v>
       </c>
       <c r="V146" s="148" t="n">
-        <v>0.1400000000000002</v>
+        <v>0.14</v>
       </c>
       <c r="W146" s="148" t="n">
-        <v>0.1400000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="X146" s="148" t="n">
         <v>0.1400000000000002</v>
       </c>
       <c r="Y146" s="148" t="n">
-        <v>0.1400000000000002</v>
+        <v>0.14</v>
       </c>
       <c r="Z146" s="148" t="n">
-        <v>0.1400000000000002</v>
+        <v>0.1400000000000001</v>
       </c>
       <c r="AA146" s="148" t="n">
-        <v>0.1400000000000002</v>
+        <v>0.14</v>
       </c>
       <c r="AB146" s="148" t="n">
-        <v>0.1400000000000002</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="147" ht="15" customHeight="1">
@@ -16639,70 +16639,70 @@
       </c>
       <c r="F147" s="123" t="inlineStr"/>
       <c r="G147" s="149" t="n">
-        <v>9.294465971293588</v>
+        <v>9.304655023369707</v>
       </c>
       <c r="H147" s="149" t="n">
-        <v>9.301157128290461</v>
+        <v>9.309661987010314</v>
       </c>
       <c r="I147" s="149" t="n">
-        <v>8.26053907119373</v>
+        <v>8.263155178732774</v>
       </c>
       <c r="J147" s="149" t="n">
-        <v>8.779169047304672</v>
+        <v>8.78464917363274</v>
       </c>
       <c r="K147" s="149" t="n">
-        <v>8.603345435319053</v>
+        <v>8.607543752935813</v>
       </c>
       <c r="L147" s="149" t="n">
-        <v>8.260508913610217</v>
+        <v>8.263131103550545</v>
       </c>
       <c r="M147" s="149" t="n">
-        <v>8.779140022290076</v>
+        <v>8.78462613791806</v>
       </c>
       <c r="N147" s="149" t="n">
-        <v>8.603322091946325</v>
+        <v>8.607525165824706</v>
       </c>
       <c r="O147" s="149" t="n">
-        <v>8.260515375934466</v>
+        <v>8.2631362625084</v>
       </c>
       <c r="P147" s="149" t="n">
-        <v>8.779146241906512</v>
+        <v>8.784631074122894</v>
       </c>
       <c r="Q147" s="149" t="n">
-        <v>8.603327094125458</v>
+        <v>8.607529148794638</v>
       </c>
       <c r="R147" s="149" t="n">
-        <v>9.293795914398222</v>
+        <v>9.304150354362317</v>
       </c>
       <c r="S147" s="149" t="n">
-        <v>9.293826941530417</v>
+        <v>9.304174178363924</v>
       </c>
       <c r="T147" s="149" t="n">
-        <v>8.258234879241172</v>
+        <v>8.261312312569641</v>
       </c>
       <c r="U147" s="149" t="n">
-        <v>8.770015273563908</v>
+        <v>8.777332206387689</v>
       </c>
       <c r="V147" s="149" t="n">
-        <v>8.598470406859159</v>
+        <v>8.603646026475925</v>
       </c>
       <c r="W147" s="149" t="n">
-        <v>8.258204667761646</v>
+        <v>8.261288202912015</v>
       </c>
       <c r="X147" s="149" t="n">
-        <v>8.769985865096366</v>
+        <v>8.777308925661583</v>
       </c>
       <c r="Y147" s="149" t="n">
-        <v>8.598446937988006</v>
+        <v>8.603627359138521</v>
       </c>
       <c r="Z147" s="149" t="n">
-        <v>8.258211141635186</v>
+        <v>8.26129336925753</v>
       </c>
       <c r="AA147" s="149" t="n">
-        <v>8.76999216688346</v>
+        <v>8.777313914369975</v>
       </c>
       <c r="AB147" s="149" t="n">
-        <v>8.598451967060122</v>
+        <v>8.603631359300039</v>
       </c>
     </row>
     <row r="148" ht="15" customHeight="1">
@@ -16733,70 +16733,70 @@
       </c>
       <c r="F148" s="123" t="inlineStr"/>
       <c r="G148" s="149" t="n">
-        <v>7.945131357462766</v>
+        <v>7.949483895568179</v>
       </c>
       <c r="H148" s="149" t="n">
-        <v>7.948802369923402</v>
+        <v>7.952236738937815</v>
       </c>
       <c r="I148" s="149" t="n">
-        <v>7.589419494649696</v>
+        <v>7.590447831606477</v>
       </c>
       <c r="J148" s="149" t="n">
-        <v>7.771672791417888</v>
+        <v>7.773829045586591</v>
       </c>
       <c r="K148" s="149" t="n">
-        <v>7.711424795595276</v>
+        <v>7.713095356621857</v>
       </c>
       <c r="L148" s="149" t="n">
-        <v>7.589674281009808</v>
+        <v>7.590651679602107</v>
       </c>
       <c r="M148" s="149" t="n">
-        <v>7.772117993610947</v>
+        <v>7.774185272714031</v>
       </c>
       <c r="N148" s="149" t="n">
-        <v>7.711699345282875</v>
+        <v>7.713315027363903</v>
       </c>
       <c r="O148" s="149" t="n">
-        <v>7.589619682930309</v>
+        <v>7.590607997247229</v>
       </c>
       <c r="P148" s="149" t="n">
-        <v>7.772022589828367</v>
+        <v>7.774108936209268</v>
       </c>
       <c r="Q148" s="149" t="n">
-        <v>7.711640511887304</v>
+        <v>7.713267954217387</v>
       </c>
       <c r="R148" s="149" t="n">
-        <v>7.945059764526371</v>
+        <v>7.949429724025213</v>
       </c>
       <c r="S148" s="149" t="n">
-        <v>7.945761329735673</v>
+        <v>7.949956107134365</v>
       </c>
       <c r="T148" s="149" t="n">
-        <v>7.58849720586591</v>
+        <v>7.589710011097772</v>
       </c>
       <c r="U148" s="149" t="n">
-        <v>7.767982845896669</v>
+        <v>7.770877413497884</v>
       </c>
       <c r="V148" s="149" t="n">
-        <v>7.709459418046734</v>
+        <v>7.711523175013582</v>
       </c>
       <c r="W148" s="149" t="n">
-        <v>7.588751961630682</v>
+        <v>7.589913839513043</v>
       </c>
       <c r="X148" s="149" t="n">
-        <v>7.768427883730142</v>
+        <v>7.771233535460249</v>
       </c>
       <c r="Y148" s="149" t="n">
-        <v>7.709733911168515</v>
+        <v>7.711742809559393</v>
       </c>
       <c r="Z148" s="149" t="n">
-        <v>7.588697370107456</v>
+        <v>7.589870161354023</v>
       </c>
       <c r="AA148" s="149" t="n">
-        <v>7.768332515168451</v>
+        <v>7.771157221491362</v>
       </c>
       <c r="AB148" s="149" t="n">
-        <v>7.709675089894425</v>
+        <v>7.711695744169331</v>
       </c>
     </row>
     <row r="149" ht="24" customHeight="1">
@@ -16827,70 +16827,70 @@
       </c>
       <c r="F149" s="123" t="inlineStr"/>
       <c r="G149" s="147" t="n">
-        <v>0.02550868504155448</v>
+        <v>0.03136446444908701</v>
       </c>
       <c r="H149" s="147" t="n">
-        <v>0.02426388904929457</v>
+        <v>0.03011966845682712</v>
       </c>
       <c r="I149" s="147" t="n">
-        <v>0.05187676437249567</v>
+        <v>0.06317071078409252</v>
       </c>
       <c r="J149" s="147" t="n">
-        <v>0.03444739418441105</v>
+        <v>0.04108978039149466</v>
       </c>
       <c r="K149" s="147" t="n">
-        <v>0.05081112274515391</v>
+        <v>0.06114398880759384</v>
       </c>
       <c r="L149" s="147" t="n">
-        <v>0.05187546974319215</v>
+        <v>0.06316941615502715</v>
       </c>
       <c r="M149" s="147" t="n">
-        <v>0.03444556044704591</v>
+        <v>0.04108794665395479</v>
       </c>
       <c r="N149" s="147" t="n">
-        <v>0.05080983529091389</v>
+        <v>0.06114270135330013</v>
       </c>
       <c r="O149" s="147" t="n">
-        <v>0.05187574716371444</v>
+        <v>0.06316969357551092</v>
       </c>
       <c r="P149" s="147" t="n">
-        <v>0.03444595339073448</v>
+        <v>0.04108833959769228</v>
       </c>
       <c r="Q149" s="147" t="n">
-        <v>0.05081011117395205</v>
+        <v>0.06114297723635339</v>
       </c>
       <c r="R149" s="147" t="n">
-        <v>0.01624341879946173</v>
+        <v>0.01992517194322811</v>
       </c>
       <c r="S149" s="147" t="n">
-        <v>0.01624121794704754</v>
+        <v>0.01992297109081393</v>
       </c>
       <c r="T149" s="147" t="n">
-        <v>0.03540489373627916</v>
+        <v>0.04291938994179882</v>
       </c>
       <c r="U149" s="147" t="n">
-        <v>0.02471682581843091</v>
+        <v>0.02913637803956356</v>
       </c>
       <c r="V149" s="147" t="n">
-        <v>0.03535010494402219</v>
+        <v>0.04222514047089693</v>
       </c>
       <c r="W149" s="147" t="n">
-        <v>0.03540403234676708</v>
+        <v>0.0429185285524452</v>
       </c>
       <c r="X149" s="147" t="n">
-        <v>0.02471560573007825</v>
+        <v>0.02913515795109464</v>
       </c>
       <c r="Y149" s="147" t="n">
-        <v>0.03534924832848243</v>
+        <v>0.04222428385532143</v>
       </c>
       <c r="Z149" s="147" t="n">
-        <v>0.03540421693020552</v>
+        <v>0.042918713135858</v>
       </c>
       <c r="AA149" s="147" t="n">
-        <v>0.02471586717756076</v>
+        <v>0.02913541939860969</v>
       </c>
       <c r="AB149" s="147" t="n">
-        <v>0.03534943188894641</v>
+        <v>0.04222446741579546</v>
       </c>
     </row>
     <row r="150" ht="24" customHeight="1">
@@ -16921,70 +16921,70 @@
       </c>
       <c r="F150" s="123" t="inlineStr"/>
       <c r="G150" s="150" t="n">
-        <v>1.875832822406664e-12</v>
+        <v>0</v>
       </c>
       <c r="H150" s="150" t="n">
         <v>0</v>
       </c>
       <c r="I150" s="150" t="n">
-        <v>2.667547960299999e-09</v>
+        <v>1.292619344894774e-09</v>
       </c>
       <c r="J150" s="150" t="n">
-        <v>1.37674760480877e-09</v>
+        <v>6.240270522539504e-10</v>
       </c>
       <c r="K150" s="150" t="n">
-        <v>4.326921043684706e-10</v>
+        <v>2.607976057333872e-10</v>
       </c>
       <c r="L150" s="150" t="n">
-        <v>0</v>
+        <v>6.67478161631152e-09</v>
       </c>
       <c r="M150" s="150" t="n">
-        <v>7.103949428710621e-09</v>
+        <v>3.220748112653382e-09</v>
       </c>
       <c r="N150" s="150" t="n">
-        <v>2.23076312977355e-09</v>
+        <v>1.346961653325707e-09</v>
       </c>
       <c r="O150" s="150" t="n">
-        <v>0</v>
+        <v>5.168885763850994e-09</v>
       </c>
       <c r="P150" s="150" t="n">
-        <v>5.502101885213051e-09</v>
+        <v>2.494516593287699e-09</v>
       </c>
       <c r="Q150" s="150" t="n">
-        <v>1.727130438666791e-09</v>
+        <v>1.043645170284435e-09</v>
       </c>
       <c r="R150" s="150" t="n">
-        <v>1.875832822406664e-12</v>
+        <v>0</v>
       </c>
       <c r="S150" s="150" t="n">
         <v>0</v>
       </c>
       <c r="T150" s="150" t="n">
-        <v>2.667547960299999e-09</v>
+        <v>1.292619344894774e-09</v>
       </c>
       <c r="U150" s="150" t="n">
-        <v>1.37674760480877e-09</v>
+        <v>6.240270522539504e-10</v>
       </c>
       <c r="V150" s="150" t="n">
-        <v>4.326921043684706e-10</v>
+        <v>2.607976057333872e-10</v>
       </c>
       <c r="W150" s="150" t="n">
-        <v>0</v>
+        <v>6.67478161631152e-09</v>
       </c>
       <c r="X150" s="150" t="n">
-        <v>7.103949428710621e-09</v>
+        <v>3.220748112653382e-09</v>
       </c>
       <c r="Y150" s="150" t="n">
-        <v>2.23076312977355e-09</v>
+        <v>1.346961653325707e-09</v>
       </c>
       <c r="Z150" s="150" t="n">
-        <v>0</v>
+        <v>5.168885763850994e-09</v>
       </c>
       <c r="AA150" s="150" t="n">
-        <v>5.502101885213051e-09</v>
+        <v>2.494516593287699e-09</v>
       </c>
       <c r="AB150" s="150" t="n">
-        <v>1.727130438666791e-09</v>
+        <v>1.043645170284435e-09</v>
       </c>
     </row>
     <row r="152">
@@ -17049,70 +17049,70 @@
       </c>
       <c r="F153" s="123" t="inlineStr"/>
       <c r="G153" s="150" t="n">
-        <v>1.113210815556326</v>
+        <v>1.486830198990387</v>
       </c>
       <c r="H153" s="150" t="n">
-        <v>1.114523660438694</v>
+        <v>1.488143043872764</v>
       </c>
       <c r="I153" s="151" t="n">
-        <v>3.153855737078547</v>
+        <v>3.94390173844531</v>
       </c>
       <c r="J153" s="151" t="n">
-        <v>1.784194928369909</v>
+        <v>2.23213977590294</v>
       </c>
       <c r="K153" s="151" t="n">
-        <v>2.831870076237649</v>
+        <v>3.542161243792975</v>
       </c>
       <c r="L153" s="151" t="n">
-        <v>3.153836591657454</v>
+        <v>3.943882592731354</v>
       </c>
       <c r="M153" s="151" t="n">
-        <v>1.784178234915861</v>
+        <v>2.232123082103706</v>
       </c>
       <c r="N153" s="151" t="n">
-        <v>2.831854894884217</v>
+        <v>3.542146062279643</v>
       </c>
       <c r="O153" s="151" t="n">
-        <v>3.153840694143365</v>
+        <v>3.94388669530116</v>
       </c>
       <c r="P153" s="151" t="n">
-        <v>1.784181811973243</v>
+        <v>2.232126659257657</v>
       </c>
       <c r="Q153" s="151" t="n">
-        <v>2.831858147979329</v>
+        <v>3.54214931541949</v>
       </c>
       <c r="R153" s="150" t="n">
-        <v>0.700014289580048</v>
+        <v>0.9349231281474634</v>
       </c>
       <c r="S153" s="150" t="n">
-        <v>0.700005694569188</v>
+        <v>0.9349145331365989</v>
       </c>
       <c r="T153" s="151" t="n">
-        <v>2.097771885348189</v>
+        <v>2.623433816359344</v>
       </c>
       <c r="U153" s="151" t="n">
-        <v>1.185488649618506</v>
+        <v>1.483531489065016</v>
       </c>
       <c r="V153" s="151" t="n">
-        <v>1.882837601322518</v>
+        <v>2.355434166676148</v>
       </c>
       <c r="W153" s="151" t="n">
-        <v>2.097759146825363</v>
+        <v>2.62342107764166</v>
       </c>
       <c r="X153" s="151" t="n">
-        <v>1.185477542526925</v>
+        <v>1.483520381743764</v>
       </c>
       <c r="Y153" s="151" t="n">
-        <v>1.882827500316316</v>
+        <v>2.355424065563553</v>
       </c>
       <c r="Z153" s="151" t="n">
-        <v>2.097761876439413</v>
+        <v>2.623423807311532</v>
       </c>
       <c r="AA153" s="151" t="n">
-        <v>1.185479922543897</v>
+        <v>1.483522761824987</v>
       </c>
       <c r="AB153" s="151" t="n">
-        <v>1.882829664783011</v>
+        <v>2.355426230060016</v>
       </c>
     </row>
     <row r="154" ht="15" customHeight="1">
@@ -17143,70 +17143,70 @@
       </c>
       <c r="F154" s="123" t="inlineStr"/>
       <c r="G154" s="150" t="n">
-        <v>0.04248573913293401</v>
+        <v>0.04777779558966159</v>
       </c>
       <c r="H154" s="150" t="n">
-        <v>0.03800360248121382</v>
+        <v>0.04329565893794141</v>
       </c>
       <c r="I154" s="151" t="n">
-        <v>0.06085164375219657</v>
+        <v>0.07052284750191348</v>
       </c>
       <c r="J154" s="151" t="n">
-        <v>0.04962773710894557</v>
+        <v>0.05544216248294227</v>
       </c>
       <c r="K154" s="151" t="n">
-        <v>0.06917736992517988</v>
+        <v>0.07844986359632908</v>
       </c>
       <c r="L154" s="151" t="n">
-        <v>0.06080210844138251</v>
+        <v>0.07047331219180548</v>
       </c>
       <c r="M154" s="151" t="n">
-        <v>0.04957810000815011</v>
+        <v>0.05539252538226503</v>
       </c>
       <c r="N154" s="151" t="n">
-        <v>0.06912768448910267</v>
+        <v>0.07840017816032213</v>
       </c>
       <c r="O154" s="151" t="n">
-        <v>0.06081272315097044</v>
+        <v>0.07048392690121993</v>
       </c>
       <c r="P154" s="151" t="n">
-        <v>0.04958873652980943</v>
+        <v>0.05540316190389129</v>
       </c>
       <c r="Q154" s="151" t="n">
-        <v>0.06913833136828895</v>
+        <v>0.07841082503948879</v>
       </c>
       <c r="R154" s="150" t="n">
-        <v>0.02680534643415587</v>
+        <v>0.03013266533409306</v>
       </c>
       <c r="S154" s="150" t="n">
-        <v>0.02677369187463278</v>
+        <v>0.03010101077456997</v>
       </c>
       <c r="T154" s="151" t="n">
-        <v>0.04308338807996767</v>
+        <v>0.04951818254697807</v>
       </c>
       <c r="U154" s="151" t="n">
-        <v>0.03885971245045097</v>
+        <v>0.04272837587578042</v>
       </c>
       <c r="V154" s="151" t="n">
-        <v>0.05095879864154527</v>
+        <v>0.05712830892326653</v>
       </c>
       <c r="W154" s="151" t="n">
-        <v>0.04305042945845613</v>
+        <v>0.04948522392593631</v>
       </c>
       <c r="X154" s="151" t="n">
-        <v>0.03882668610235376</v>
+        <v>0.04269534952776186</v>
       </c>
       <c r="Y154" s="151" t="n">
-        <v>0.05092574013327326</v>
+        <v>0.05709525041504129</v>
       </c>
       <c r="Z154" s="151" t="n">
-        <v>0.04305749202029362</v>
+        <v>0.04949228648765837</v>
       </c>
       <c r="AA154" s="151" t="n">
-        <v>0.03883376317698627</v>
+        <v>0.04270242660237237</v>
       </c>
       <c r="AB154" s="151" t="n">
-        <v>0.05093282409934952</v>
+        <v>0.05710233438110449</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -17331,70 +17331,70 @@
       </c>
       <c r="F156" s="123" t="inlineStr"/>
       <c r="G156" s="150" t="n">
-        <v>0.1083414537470186</v>
+        <v>0.1328416046460465</v>
       </c>
       <c r="H156" s="150" t="n">
-        <v>0.107633003568228</v>
+        <v>0.1321331544672561</v>
       </c>
       <c r="I156" s="151" t="n">
-        <v>0.2339831193583159</v>
+        <v>0.2839542902423469</v>
       </c>
       <c r="J156" s="151" t="n">
-        <v>0.1504877984741485</v>
+        <v>0.1794067985308676</v>
       </c>
       <c r="K156" s="151" t="n">
-        <v>0.2174797461027427</v>
+        <v>0.2629041647027586</v>
       </c>
       <c r="L156" s="151" t="n">
-        <v>0.2340260628416754</v>
+        <v>0.2839972337237082</v>
       </c>
       <c r="M156" s="151" t="n">
-        <v>0.1505308275318445</v>
+        <v>0.1794498275846172</v>
       </c>
       <c r="N156" s="151" t="n">
-        <v>0.2175228191925891</v>
+        <v>0.2629472377908854</v>
       </c>
       <c r="O156" s="151" t="n">
-        <v>0.2340168606654816</v>
+        <v>0.2839880315481977</v>
       </c>
       <c r="P156" s="151" t="n">
-        <v>0.1505216070182965</v>
+        <v>0.1794406070721735</v>
       </c>
       <c r="Q156" s="151" t="n">
-        <v>0.2175135892442209</v>
+        <v>0.2629380078429988</v>
       </c>
       <c r="R156" s="150" t="n">
-        <v>0.07938208693776358</v>
+        <v>0.09478627164445091</v>
       </c>
       <c r="S156" s="150" t="n">
-        <v>0.07940951372560666</v>
+        <v>0.09481369843229404</v>
       </c>
       <c r="T156" s="151" t="n">
-        <v>0.1662610335270309</v>
+        <v>0.199509657197482</v>
       </c>
       <c r="U156" s="151" t="n">
-        <v>0.1112574539563226</v>
+        <v>0.1304988872227758</v>
       </c>
       <c r="V156" s="151" t="n">
-        <v>0.1556768036022249</v>
+        <v>0.185900217878147</v>
       </c>
       <c r="W156" s="151" t="n">
-        <v>0.166289606235896</v>
+        <v>0.1995382299050175</v>
       </c>
       <c r="X156" s="151" t="n">
-        <v>0.1112860836025951</v>
+        <v>0.1305275168664224</v>
       </c>
       <c r="Y156" s="151" t="n">
-        <v>0.1557054625455575</v>
+        <v>0.1859288768203355</v>
       </c>
       <c r="Z156" s="151" t="n">
-        <v>0.1662834835117771</v>
+        <v>0.1995321071813534</v>
       </c>
       <c r="AA156" s="151" t="n">
-        <v>0.1112799486776057</v>
+        <v>0.1305213819421677</v>
       </c>
       <c r="AB156" s="151" t="n">
-        <v>0.1556993213430528</v>
+        <v>0.1859227356181512</v>
       </c>
     </row>
     <row r="157" ht="15" customHeight="1">
@@ -17425,70 +17425,70 @@
       </c>
       <c r="F157" s="123" t="inlineStr"/>
       <c r="G157" s="152" t="n">
-        <v>1.264038008436278</v>
+        <v>1.667449599226095</v>
       </c>
       <c r="H157" s="152" t="n">
-        <v>1.260160266488136</v>
+        <v>1.663571857277961</v>
       </c>
       <c r="I157" s="153" t="n">
-        <v>3.448690500189059</v>
+        <v>4.29837887618957</v>
       </c>
       <c r="J157" s="153" t="n">
-        <v>1.984310463953003</v>
+        <v>2.46698873691675</v>
       </c>
       <c r="K157" s="153" t="n">
-        <v>3.118527192265571</v>
+        <v>3.883515272092063</v>
       </c>
       <c r="L157" s="153" t="n">
-        <v>3.448664762940512</v>
+        <v>4.298353138646868</v>
       </c>
       <c r="M157" s="153" t="n">
-        <v>1.984287162455855</v>
+        <v>2.466965435070589</v>
       </c>
       <c r="N157" s="153" t="n">
-        <v>3.118505398565909</v>
+        <v>3.883493478230851</v>
       </c>
       <c r="O157" s="153" t="n">
-        <v>3.448670277959817</v>
+        <v>4.298358653750578</v>
       </c>
       <c r="P157" s="153" t="n">
-        <v>1.984292155521349</v>
+        <v>2.466970428233721</v>
       </c>
       <c r="Q157" s="153" t="n">
-        <v>3.118510068591839</v>
+        <v>3.883498148301978</v>
       </c>
       <c r="R157" s="152" t="n">
-        <v>0.8062017229519675</v>
+        <v>1.059842065126007</v>
       </c>
       <c r="S157" s="152" t="n">
-        <v>0.8061889001694275</v>
+        <v>1.059829242343463</v>
       </c>
       <c r="T157" s="153" t="n">
-        <v>2.307116306955187</v>
+        <v>2.872461656103805</v>
       </c>
       <c r="U157" s="153" t="n">
-        <v>1.33560581602528</v>
+        <v>1.656758752163572</v>
       </c>
       <c r="V157" s="153" t="n">
-        <v>2.089473203566288</v>
+        <v>2.598462693477561</v>
       </c>
       <c r="W157" s="153" t="n">
-        <v>2.307099182519715</v>
+        <v>2.872444531472614</v>
       </c>
       <c r="X157" s="153" t="n">
-        <v>1.335590312231874</v>
+        <v>1.656743248137948</v>
       </c>
       <c r="Y157" s="153" t="n">
-        <v>2.089458702995147</v>
+        <v>2.59844819279893</v>
       </c>
       <c r="Z157" s="153" t="n">
-        <v>2.307102851971484</v>
+        <v>2.872448200980544</v>
       </c>
       <c r="AA157" s="153" t="n">
-        <v>1.335593634398488</v>
+        <v>1.656746570369527</v>
       </c>
       <c r="AB157" s="153" t="n">
-        <v>2.089461810225414</v>
+        <v>2.598451300059271</v>
       </c>
     </row>
     <row r="158" ht="15" customHeight="1">
@@ -17613,70 +17613,70 @@
       </c>
       <c r="F159" s="123" t="inlineStr"/>
       <c r="G159" s="150" t="n">
-        <v>0.2122220862959302</v>
+        <v>0.215260421728373</v>
       </c>
       <c r="H159" s="150" t="n">
-        <v>0.1383289394592217</v>
+        <v>0.1413672748916645</v>
       </c>
       <c r="I159" s="151" t="n">
-        <v>0.1514475454490726</v>
+        <v>0.1570000865580744</v>
       </c>
       <c r="J159" s="151" t="n">
-        <v>0.3041660054372468</v>
+        <v>0.3075042492329361</v>
       </c>
       <c r="K159" s="151" t="n">
-        <v>0.2668663304445173</v>
+        <v>0.2721899596042816</v>
       </c>
       <c r="L159" s="151" t="n">
-        <v>0.1514180498478056</v>
+        <v>0.1569705909572128</v>
       </c>
       <c r="M159" s="151" t="n">
-        <v>0.304136451395162</v>
+        <v>0.3074746951909192</v>
       </c>
       <c r="N159" s="151" t="n">
-        <v>0.2668367486516327</v>
+        <v>0.2721603778114374</v>
       </c>
       <c r="O159" s="151" t="n">
-        <v>0.1514243703338647</v>
+        <v>0.1569769114431724</v>
       </c>
       <c r="P159" s="151" t="n">
-        <v>0.3041427844042148</v>
+        <v>0.307481028199953</v>
       </c>
       <c r="Q159" s="151" t="n">
-        <v>0.2668430876072663</v>
+        <v>0.2721667167670597</v>
       </c>
       <c r="R159" s="150" t="n">
-        <v>0.1349810410827771</v>
+        <v>0.1368913591210255</v>
       </c>
       <c r="S159" s="150" t="n">
-        <v>0.1349621965953671</v>
+        <v>0.1368725146336156</v>
       </c>
       <c r="T159" s="151" t="n">
-        <v>0.1440228049458968</v>
+        <v>0.1477172220764529</v>
       </c>
       <c r="U159" s="151" t="n">
-        <v>0.299705284602134</v>
+        <v>0.3019264054948317</v>
       </c>
       <c r="V159" s="151" t="n">
-        <v>0.259748028548601</v>
+        <v>0.2632901377160011</v>
       </c>
       <c r="W159" s="151" t="n">
-        <v>0.1440031798674944</v>
+        <v>0.1476975969983202</v>
       </c>
       <c r="X159" s="151" t="n">
-        <v>0.2996856206397765</v>
+        <v>0.3019067415325195</v>
       </c>
       <c r="Y159" s="151" t="n">
-        <v>0.2597283461220796</v>
+        <v>0.2632704552895065</v>
       </c>
       <c r="Z159" s="151" t="n">
-        <v>0.1440073852414866</v>
+        <v>0.1477018023722461</v>
       </c>
       <c r="AA159" s="151" t="n">
-        <v>0.299689834346019</v>
+        <v>0.3019109552387494</v>
       </c>
       <c r="AB159" s="151" t="n">
-        <v>0.2597325637849158</v>
+        <v>0.2632746729523353</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1">
@@ -17707,70 +17707,70 @@
       </c>
       <c r="F160" s="123" t="inlineStr"/>
       <c r="G160" s="152" t="n">
-        <v>0.4530573527276018</v>
+        <v>0.4560956881600446</v>
       </c>
       <c r="H160" s="152" t="n">
-        <v>0.3791642058908935</v>
+        <v>0.3822025413233363</v>
       </c>
       <c r="I160" s="153" t="n">
-        <v>0.3922828118807444</v>
+        <v>0.3978353529897461</v>
       </c>
       <c r="J160" s="153" t="n">
-        <v>0.4534803573460149</v>
+        <v>0.4568186011417041</v>
       </c>
       <c r="K160" s="153" t="n">
-        <v>0.5567118370909494</v>
+        <v>0.5620354662507137</v>
       </c>
       <c r="L160" s="153" t="n">
-        <v>0.3922533162794773</v>
+        <v>0.3978058573888845</v>
       </c>
       <c r="M160" s="153" t="n">
-        <v>0.4534508033039301</v>
+        <v>0.4567890470996873</v>
       </c>
       <c r="N160" s="153" t="n">
-        <v>0.5566822552980648</v>
+        <v>0.5620058844578695</v>
       </c>
       <c r="O160" s="153" t="n">
-        <v>0.3922596367655365</v>
+        <v>0.3978121778748441</v>
       </c>
       <c r="P160" s="153" t="n">
-        <v>0.4534571363129829</v>
+        <v>0.456795380108721</v>
       </c>
       <c r="Q160" s="153" t="n">
-        <v>0.5566885942536983</v>
+        <v>0.5620122234134919</v>
       </c>
       <c r="R160" s="152" t="n">
-        <v>0.2864034116341725</v>
+        <v>0.2883137296724209</v>
       </c>
       <c r="S160" s="152" t="n">
-        <v>0.2863845671467626</v>
+        <v>0.2882948851850111</v>
       </c>
       <c r="T160" s="153" t="n">
-        <v>0.3042640200005229</v>
+        <v>0.3079584371310791</v>
       </c>
       <c r="U160" s="153" t="n">
-        <v>0.3990525003544551</v>
+        <v>0.4012736212471528</v>
       </c>
       <c r="V160" s="153" t="n">
-        <v>0.4525985061854596</v>
+        <v>0.4561406153528597</v>
       </c>
       <c r="W160" s="153" t="n">
-        <v>0.3042443949221205</v>
+        <v>0.3079388120529464</v>
       </c>
       <c r="X160" s="153" t="n">
-        <v>0.3990328363920976</v>
+        <v>0.4012539572848405</v>
       </c>
       <c r="Y160" s="153" t="n">
-        <v>0.4525788237589382</v>
+        <v>0.4561209329263651</v>
       </c>
       <c r="Z160" s="153" t="n">
-        <v>0.3042486002961127</v>
+        <v>0.3079430174268722</v>
       </c>
       <c r="AA160" s="153" t="n">
-        <v>0.3990370500983401</v>
+        <v>0.4012581709910705</v>
       </c>
       <c r="AB160" s="153" t="n">
-        <v>0.4525830414217744</v>
+        <v>0.4561251505891939</v>
       </c>
     </row>
     <row r="161" ht="15" customHeight="1">
@@ -17801,70 +17801,70 @@
       </c>
       <c r="F161" s="123" t="inlineStr"/>
       <c r="G161" s="152" t="n">
-        <v>1.71709536116388</v>
+        <v>2.12354528738614</v>
       </c>
       <c r="H161" s="152" t="n">
-        <v>1.63932447237903</v>
+        <v>2.045774398601298</v>
       </c>
       <c r="I161" s="153" t="n">
-        <v>3.840973312069803</v>
+        <v>4.696214229179318</v>
       </c>
       <c r="J161" s="153" t="n">
-        <v>2.437790821299018</v>
+        <v>2.923807338058453</v>
       </c>
       <c r="K161" s="153" t="n">
-        <v>3.67523902935652</v>
+        <v>4.445550738342776</v>
       </c>
       <c r="L161" s="153" t="n">
-        <v>3.84091807921999</v>
+        <v>4.696158996035751</v>
       </c>
       <c r="M161" s="153" t="n">
-        <v>2.437737965759786</v>
+        <v>2.923754482170276</v>
       </c>
       <c r="N161" s="153" t="n">
-        <v>3.675187653863974</v>
+        <v>4.44549936268872</v>
       </c>
       <c r="O161" s="153" t="n">
-        <v>3.840929914725353</v>
+        <v>4.696170831625423</v>
       </c>
       <c r="P161" s="153" t="n">
-        <v>2.437749291834332</v>
+        <v>2.923765808342443</v>
       </c>
       <c r="Q161" s="153" t="n">
-        <v>3.675198662845537</v>
+        <v>4.44551037171547</v>
       </c>
       <c r="R161" s="152" t="n">
-        <v>1.09260513458614</v>
+        <v>1.348155794798428</v>
       </c>
       <c r="S161" s="152" t="n">
-        <v>1.09257346731619</v>
+        <v>1.348124127528474</v>
       </c>
       <c r="T161" s="153" t="n">
-        <v>2.611380326955709</v>
+        <v>3.180420093234884</v>
       </c>
       <c r="U161" s="153" t="n">
-        <v>1.734658316379735</v>
+        <v>2.058032373410724</v>
       </c>
       <c r="V161" s="153" t="n">
-        <v>2.542071709751747</v>
+        <v>3.054603308830421</v>
       </c>
       <c r="W161" s="153" t="n">
-        <v>2.611343577441835</v>
+        <v>3.18038334352556</v>
       </c>
       <c r="X161" s="153" t="n">
-        <v>1.734623148623972</v>
+        <v>2.057997205422789</v>
       </c>
       <c r="Y161" s="153" t="n">
-        <v>2.542037526754084</v>
+        <v>3.054569125725295</v>
       </c>
       <c r="Z161" s="153" t="n">
-        <v>2.611351452267597</v>
+        <v>3.180391218407416</v>
       </c>
       <c r="AA161" s="153" t="n">
-        <v>1.734630684496829</v>
+        <v>2.058004741360597</v>
       </c>
       <c r="AB161" s="153" t="n">
-        <v>2.542044851647188</v>
+        <v>3.054576450648465</v>
       </c>
     </row>
     <row r="162" ht="15" customHeight="1">
@@ -18092,7 +18092,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -18375,7 +18374,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
@@ -19445,12 +19443,12 @@
     <row r="17">
       <c r="A17" s="19" t="inlineStr">
         <is>
-          <t>New-build capital cost (working assumption, 20 Oct 2026): CCGT US$1,200/kW, gas engine US$1,100/kW, OCGT US$700/kW</t>
+          <t>Capital cost (working assumption, 20 Oct 2026, market +25%): existing CCGT US$600/kW; new CCGT US$1,500/kW, gas engine US$1,375/kW, OCGT US$875/kW</t>
         </is>
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>Market-level working values chosen 20 Oct 2026 in response to Wärtsilä and Quezon Power comments (GAIR matrix rows 119, 412); to be sourced in the Reference Parameters Resolution</t>
+          <t>Market-level working values raised 20 Oct 2026 (+25%, EPC and turbine cost inflation), in response to Wärtsilä and Quezon Power comments (GAIR matrix rows 119, 412); to be sourced in the Reference Parameters Resolution</t>
         </is>
       </c>
       <c r="C17" s="19" t="inlineStr">

--- a/FinModel_Summary.xlsx
+++ b/FinModel_Summary.xlsx
@@ -11,14 +11,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GATP_Summary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GATP_Composition" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rates" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOR_Conditions" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historical_CF" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuel_WhatIf" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOR_Conditions" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historical_CF" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Parameters'!$A$9:$AB$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Parameters'!$A$9:$AB$164</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,7 +36,7 @@
     <numFmt numFmtId="169" formatCode="0.00000"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="51">
+  <fonts count="57">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -279,8 +280,41 @@
       <color rgb="001E7B4F"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3A5F"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="0052606D"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="0052606D"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="26">
+  <fills count="32">
     <fill>
       <patternFill/>
     </fill>
@@ -422,8 +456,38 @@
         <bgColor rgb="00DCE6F0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3A5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F8A8A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006C3FA0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6F0FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D3EEEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E9E1F4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -506,11 +570,25 @@
         <color rgb="00C0392B"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9DEE5"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9DEE5"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9DEE5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9DEE5"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="168">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -858,6 +936,46 @@
     </xf>
     <xf numFmtId="165" fontId="36" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="26" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="27" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="28" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="54" fillId="29" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="29" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="54" fillId="29" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="54" fillId="29" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="54" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="55" fillId="30" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="55" fillId="31" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1798,6 +1916,287 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="55" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Reference for every assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="67" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="B3" s="67" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="C3" s="67" t="inlineStr">
+        <is>
+          <t>File / location</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>Lots, capacity factor bands, delivery year, supply period</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>DOE Terms of Reference (Annex B), Sec. 1.1, 1.2, 4.2, 18.3</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>GAIR RCM/Terms of Reference/Annex B - Terms of Reference.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>30-year cost recovery; zero construction for existing plants</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>ERC basis (plant economic life); instruction of 20 Oct 2026; GAIR Table 1</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>franz_som_working draft_1.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>Historical capacity factor (Fin90)</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>Meralco Breakdown of Generation Charge, Jan 2024–Sep 2026 (First Gen Santa Rita, San Lorenzo; SPPC Ilijan; EERI)</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>xxxxxxx/*_gc_table.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>Capital cost, fixed and variable O&amp;M, heat rate, construction, unit size</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>Draft Resolution 2 values (DOE/EPC 2026 benchmarks, LTSA, cheat sheet)</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>claudenumbers/01_master_numbers_cheat_sheet.md; whisper/scripts/cases.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>Lazard comparison (CCGT capex, O&amp;M, heat rate)</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>Lazard LCOE v19 (June 2026) as cited in the GAIR workbook</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>mid_merit_gas_rates.xlsx, O&amp;M Rebasing tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>First Gen historical O&amp;M (Santa Rita / San Lorenzo 1996 PPA, re-based May 2026)</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>ERC Case No. 2004-74 PPA rates, CPI re-basing</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>mid_merit_gas_rates.xlsx, O&amp;M Rebasing tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>Existing-plant capital cost US$450/kW; brownfield US$600/kW (San Gabriel, EERI)</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>GAIR workbook / cheat sheet</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>mid_merit_gas_rates.xlsx; cheat sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>Financing: 70:30, Kd 8%, 15-yr tenor, Re 14%</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>Draft Resolution 2 (Annex A.9–A.12)</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>cheat sheet; whisper/scripts/engine.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>Logistics caps (CLLC)</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>Draft Resolution 2 caps; BOG removed per working Rules Sec. 17</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>cases.py; franz_som_working draft_1.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>PhP/US$ 62.756</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>BSP reference rate, 25 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>whisper/scripts/cases.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>Taxes (CIT 25%, VAT 12%, RPT 2%, LBT 1%, WHT, GRT, DST)</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>CREATE Act (RA 11534), NIRC, LGC — model defaults</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>whisper/ERC Mid-Merit Financial Model.xlsm (Sensitivity Analysis)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>ER 1-94 PhP 0.03/kWh</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>DOE DC2025-10-0023; GAIR 8.8.3</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>naruto C90</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>Model template</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>naruto.xlsm (blank ERC Mid-Merit Financial Model)</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>GAIR RCM/whisper/naruto.xlsm</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>Capital cost (working assumption, 20 Oct 2026, market +25%): existing CCGT US$600/kW; new CCGT US$1,500/kW, gas engine US$1,375/kW, OCGT US$875/kW</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>Market-level working values raised 20 Oct 2026 (+25%, EPC and turbine cost inflation), in response to Wärtsilä and Quezon Power comments (GAIR matrix rows 119, 412); to be sourced in the Reference Parameters Resolution</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>models Fin42/Fin90, cell O34</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -4023,6 +4422,7 @@
       <c r="I2" s="69" t="n"/>
       <c r="J2" s="69" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="79" t="inlineStr">
         <is>
@@ -4510,6 +4910,573 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00B45309"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="154" t="inlineStr">
+        <is>
+          <t>What if: draft GATP + fuel actually billed to MERALCO (URR bills, July and August 2026 supply)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="155" t="inlineStr">
+        <is>
+          <t>All PhP/kWh, excl. VAT. CLLC certified = lower of the billed logistics and the cap (Sec. 17, 23). Cap: LNG US$2.20/MMBtu (regas 1.50 + pipeline 0.40 + storage 0.30), Malampaya US$0.40 (pipeline). GATP linked to the Rates sheet. Blue cells are inputs from the bills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="156" t="inlineStr">
+        <is>
+          <t>Plant – supply month</t>
+        </is>
+      </c>
+      <c r="B4" s="156" t="inlineStr">
+        <is>
+          <t>Fuel mix</t>
+        </is>
+      </c>
+      <c r="C4" s="156" t="inlineStr">
+        <is>
+          <t>LNG share</t>
+        </is>
+      </c>
+      <c r="D4" s="156" t="inlineStr">
+        <is>
+          <t>Malampaya share</t>
+        </is>
+      </c>
+      <c r="E4" s="156" t="inlineStr">
+        <is>
+          <t>Heat rate (Btu/kWh)</t>
+        </is>
+      </c>
+      <c r="F4" s="156" t="inlineStr">
+        <is>
+          <t>Bill FX (PhP/US$)</t>
+        </is>
+      </c>
+      <c r="G4" s="156" t="inlineStr">
+        <is>
+          <t>Billed fuel commodity</t>
+        </is>
+      </c>
+      <c r="H4" s="156" t="inlineStr">
+        <is>
+          <t>Billed logistics</t>
+        </is>
+      </c>
+      <c r="I4" s="156" t="inlineStr">
+        <is>
+          <t>CLLC cap</t>
+        </is>
+      </c>
+      <c r="J4" s="156" t="inlineStr">
+        <is>
+          <t>CLLC certified</t>
+        </is>
+      </c>
+      <c r="K4" s="157" t="inlineStr">
+        <is>
+          <t>GATP Case A</t>
+        </is>
+      </c>
+      <c r="L4" s="158" t="inlineStr">
+        <is>
+          <t>GATP Case B</t>
+        </is>
+      </c>
+      <c r="M4" s="157" t="inlineStr">
+        <is>
+          <t>All-in Case A</t>
+        </is>
+      </c>
+      <c r="N4" s="158" t="inlineStr">
+        <is>
+          <t>All-in Case B</t>
+        </is>
+      </c>
+      <c r="O4" s="156" t="inlineStr">
+        <is>
+          <t>MERALCO actual</t>
+        </is>
+      </c>
+      <c r="P4" s="156" t="inlineStr">
+        <is>
+          <t>Actual minus all-in A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="159" t="inlineStr">
+        <is>
+          <t>Santa Rita – Jul 2026 supply</t>
+        </is>
+      </c>
+      <c r="B5" s="159" t="inlineStr">
+        <is>
+          <t>LNG 58% / Malampaya 27% / liquid 15%</t>
+        </is>
+      </c>
+      <c r="C5" s="160" t="n">
+        <v>0.5815</v>
+      </c>
+      <c r="D5" s="160" t="n">
+        <v>0.2712</v>
+      </c>
+      <c r="E5" s="161" t="n">
+        <v>6350</v>
+      </c>
+      <c r="F5" s="162" t="n">
+        <v>61.945</v>
+      </c>
+      <c r="G5" s="163" t="n">
+        <v>7.7128</v>
+      </c>
+      <c r="H5" s="163" t="n">
+        <v>1.2633</v>
+      </c>
+      <c r="I5" s="164">
+        <f>(C5*2.2+D5*0.4)*E5/1000000*F5</f>
+        <v/>
+      </c>
+      <c r="J5" s="164">
+        <f>MIN(H5,I5)</f>
+        <v/>
+      </c>
+      <c r="K5" s="164">
+        <f>Rates!F5</f>
+        <v/>
+      </c>
+      <c r="L5" s="164">
+        <f>Rates!G5</f>
+        <v/>
+      </c>
+      <c r="M5" s="165">
+        <f>K5+G5+J5</f>
+        <v/>
+      </c>
+      <c r="N5" s="166">
+        <f>L5+G5+J5</f>
+        <v/>
+      </c>
+      <c r="O5" s="163" t="n">
+        <v>10.7708</v>
+      </c>
+      <c r="P5" s="164">
+        <f>O5-M5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="159" t="inlineStr">
+        <is>
+          <t>Santa Rita – Aug 2026 supply</t>
+        </is>
+      </c>
+      <c r="B6" s="159" t="inlineStr">
+        <is>
+          <t>100% Malampaya</t>
+        </is>
+      </c>
+      <c r="C6" s="160" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="160" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="161" t="n">
+        <v>6350</v>
+      </c>
+      <c r="F6" s="162" t="n">
+        <v>62</v>
+      </c>
+      <c r="G6" s="163" t="n">
+        <v>6.6064</v>
+      </c>
+      <c r="H6" s="163" t="n">
+        <v>1.0785</v>
+      </c>
+      <c r="I6" s="164">
+        <f>(C6*2.2+D6*0.4)*E6/1000000*F6</f>
+        <v/>
+      </c>
+      <c r="J6" s="164">
+        <f>MIN(H6,I6)</f>
+        <v/>
+      </c>
+      <c r="K6" s="164">
+        <f>Rates!F5</f>
+        <v/>
+      </c>
+      <c r="L6" s="164">
+        <f>Rates!G5</f>
+        <v/>
+      </c>
+      <c r="M6" s="165">
+        <f>K6+G6+J6</f>
+        <v/>
+      </c>
+      <c r="N6" s="166">
+        <f>L6+G6+J6</f>
+        <v/>
+      </c>
+      <c r="O6" s="163" t="n">
+        <v>6.9472</v>
+      </c>
+      <c r="P6" s="164">
+        <f>O6-M6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="159" t="inlineStr">
+        <is>
+          <t>San Lorenzo – Jul 2026 supply</t>
+        </is>
+      </c>
+      <c r="B7" s="159" t="inlineStr">
+        <is>
+          <t>LNG 65% / Malampaya 35%</t>
+        </is>
+      </c>
+      <c r="C7" s="160" t="n">
+        <v>0.6466</v>
+      </c>
+      <c r="D7" s="160" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="E7" s="161" t="n">
+        <v>6350</v>
+      </c>
+      <c r="F7" s="162" t="n">
+        <v>61.945</v>
+      </c>
+      <c r="G7" s="163" t="n">
+        <v>7.4562</v>
+      </c>
+      <c r="H7" s="163" t="n">
+        <v>1.1113</v>
+      </c>
+      <c r="I7" s="164">
+        <f>(C7*2.2+D7*0.4)*E7/1000000*F7</f>
+        <v/>
+      </c>
+      <c r="J7" s="164">
+        <f>MIN(H7,I7)</f>
+        <v/>
+      </c>
+      <c r="K7" s="164">
+        <f>Rates!F5</f>
+        <v/>
+      </c>
+      <c r="L7" s="164">
+        <f>Rates!G5</f>
+        <v/>
+      </c>
+      <c r="M7" s="165">
+        <f>K7+G7+J7</f>
+        <v/>
+      </c>
+      <c r="N7" s="166">
+        <f>L7+G7+J7</f>
+        <v/>
+      </c>
+      <c r="O7" s="163" t="n">
+        <v>10.6771</v>
+      </c>
+      <c r="P7" s="164">
+        <f>O7-M7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="159" t="inlineStr">
+        <is>
+          <t>San Lorenzo – Aug 2026 supply</t>
+        </is>
+      </c>
+      <c r="B8" s="159" t="inlineStr">
+        <is>
+          <t>100% Malampaya</t>
+        </is>
+      </c>
+      <c r="C8" s="160" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="160" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="161" t="n">
+        <v>6350</v>
+      </c>
+      <c r="F8" s="162" t="n">
+        <v>62.498</v>
+      </c>
+      <c r="G8" s="163" t="n">
+        <v>6.4776</v>
+      </c>
+      <c r="H8" s="163" t="n">
+        <v>1.0884</v>
+      </c>
+      <c r="I8" s="164">
+        <f>(C8*2.2+D8*0.4)*E8/1000000*F8</f>
+        <v/>
+      </c>
+      <c r="J8" s="164">
+        <f>MIN(H8,I8)</f>
+        <v/>
+      </c>
+      <c r="K8" s="164">
+        <f>Rates!F5</f>
+        <v/>
+      </c>
+      <c r="L8" s="164">
+        <f>Rates!G5</f>
+        <v/>
+      </c>
+      <c r="M8" s="165">
+        <f>K8+G8+J8</f>
+        <v/>
+      </c>
+      <c r="N8" s="166">
+        <f>L8+G8+J8</f>
+        <v/>
+      </c>
+      <c r="O8" s="163" t="n">
+        <v>9.814399999999999</v>
+      </c>
+      <c r="P8" s="164">
+        <f>O8-M8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="159" t="inlineStr">
+        <is>
+          <t>Ilijan (2024 PSA) – Jul 2026 supply</t>
+        </is>
+      </c>
+      <c r="B9" s="159" t="inlineStr">
+        <is>
+          <t>100% LNG (Brent-linked)</t>
+        </is>
+      </c>
+      <c r="C9" s="160" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="160" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="161" t="n">
+        <v>6350</v>
+      </c>
+      <c r="F9" s="162" t="n">
+        <v>61.847</v>
+      </c>
+      <c r="G9" s="163" t="n">
+        <v>9.636100000000001</v>
+      </c>
+      <c r="H9" s="163" t="n">
+        <v>0.5239</v>
+      </c>
+      <c r="I9" s="164">
+        <f>(C9*2.2+D9*0.4)*E9/1000000*F9</f>
+        <v/>
+      </c>
+      <c r="J9" s="164">
+        <f>MIN(H9,I9)</f>
+        <v/>
+      </c>
+      <c r="K9" s="164">
+        <f>Rates!F6</f>
+        <v/>
+      </c>
+      <c r="L9" s="164">
+        <f>Rates!G6</f>
+        <v/>
+      </c>
+      <c r="M9" s="165">
+        <f>K9+G9+J9</f>
+        <v/>
+      </c>
+      <c r="N9" s="166">
+        <f>L9+G9+J9</f>
+        <v/>
+      </c>
+      <c r="O9" s="163" t="n">
+        <v>13.0017</v>
+      </c>
+      <c r="P9" s="164">
+        <f>O9-M9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="159" t="inlineStr">
+        <is>
+          <t>Ilijan (2024 PSA) – Aug 2026 supply</t>
+        </is>
+      </c>
+      <c r="B10" s="159" t="inlineStr">
+        <is>
+          <t>100% LNG (Brent-linked)</t>
+        </is>
+      </c>
+      <c r="C10" s="160" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="160" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="161" t="n">
+        <v>6350</v>
+      </c>
+      <c r="F10" s="162" t="n">
+        <v>61.738</v>
+      </c>
+      <c r="G10" s="163" t="n">
+        <v>10.2713</v>
+      </c>
+      <c r="H10" s="163" t="n">
+        <v>0.5256999999999999</v>
+      </c>
+      <c r="I10" s="164">
+        <f>(C10*2.2+D10*0.4)*E10/1000000*F10</f>
+        <v/>
+      </c>
+      <c r="J10" s="164">
+        <f>MIN(H10,I10)</f>
+        <v/>
+      </c>
+      <c r="K10" s="164">
+        <f>Rates!F6</f>
+        <v/>
+      </c>
+      <c r="L10" s="164">
+        <f>Rates!G6</f>
+        <v/>
+      </c>
+      <c r="M10" s="165">
+        <f>K10+G10+J10</f>
+        <v/>
+      </c>
+      <c r="N10" s="166">
+        <f>L10+G10+J10</f>
+        <v/>
+      </c>
+      <c r="O10" s="163" t="n">
+        <v>15.4438</v>
+      </c>
+      <c r="P10" s="164">
+        <f>O10-M10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="159" t="inlineStr">
+        <is>
+          <t>EERI Batangas – Aug 2026 supply</t>
+        </is>
+      </c>
+      <c r="B11" s="159" t="inlineStr">
+        <is>
+          <t>100% LNG (Brent-linked</t>
+        </is>
+      </c>
+      <c r="C11" s="160" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="160" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="161" t="n">
+        <v>6100</v>
+      </c>
+      <c r="F11" s="162" t="n">
+        <v>61.8507</v>
+      </c>
+      <c r="G11" s="163" t="n">
+        <v>8.849</v>
+      </c>
+      <c r="H11" s="163" t="n">
+        <v>0.453</v>
+      </c>
+      <c r="I11" s="164">
+        <f>(C11*2.2+D11*0.4)*E11/1000000*F11</f>
+        <v/>
+      </c>
+      <c r="J11" s="164">
+        <f>MIN(H11,I11)</f>
+        <v/>
+      </c>
+      <c r="K11" s="164">
+        <f>Rates!F7</f>
+        <v/>
+      </c>
+      <c r="L11" s="164">
+        <f>Rates!G7</f>
+        <v/>
+      </c>
+      <c r="M11" s="165">
+        <f>K11+G11+J11</f>
+        <v/>
+      </c>
+      <c r="N11" s="166">
+        <f>L11+G11+J11</f>
+        <v/>
+      </c>
+      <c r="O11" s="163" t="n">
+        <v>15.8623</v>
+      </c>
+      <c r="P11" s="164">
+        <f>O11-M11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="167" t="inlineStr">
+        <is>
+          <t>Sources: MERALCO URR power-supply bills in URRnew/ (Santa Rita PB-41000020/21; San Lorenzo PB-41000019/20; SPPC 211 MECO 2607/2608 Final; EERI 802 EERI 2608 Final). MERALCO actual = Breakdown of Generation Charge for the following billing month (Aug and Sep 2026). No September supply-month bills were available. Ilijan and EERI fuel commodity includes ocean freight (delivered LNG); their logistics are the PHLNG terminal fee and PhP import costs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A13:P13"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4659,7 +5626,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18065,7 +19032,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18397,7 +19364,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19179,285 +20146,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="18" t="inlineStr">
-        <is>
-          <t>Reference for every assumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="67" t="inlineStr">
-        <is>
-          <t>Assumption</t>
-        </is>
-      </c>
-      <c r="B3" s="67" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="C3" s="67" t="inlineStr">
-        <is>
-          <t>File / location</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>Lots, capacity factor bands, delivery year, supply period</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>DOE Terms of Reference (Annex B), Sec. 1.1, 1.2, 4.2, 18.3</t>
-        </is>
-      </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>GAIR RCM/Terms of Reference/Annex B - Terms of Reference.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>30-year cost recovery; zero construction for existing plants</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>ERC basis (plant economic life); instruction of 20 Oct 2026; GAIR Table 1</t>
-        </is>
-      </c>
-      <c r="C5" s="19" t="inlineStr">
-        <is>
-          <t>franz_som_working draft_1.docx</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>Historical capacity factor (Fin90)</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>Meralco Breakdown of Generation Charge, Jan 2024–Sep 2026 (First Gen Santa Rita, San Lorenzo; SPPC Ilijan; EERI)</t>
-        </is>
-      </c>
-      <c r="C6" s="19" t="inlineStr">
-        <is>
-          <t>xxxxxxx/*_gc_table.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>Capital cost, fixed and variable O&amp;M, heat rate, construction, unit size</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>Draft Resolution 2 values (DOE/EPC 2026 benchmarks, LTSA, cheat sheet)</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="inlineStr">
-        <is>
-          <t>claudenumbers/01_master_numbers_cheat_sheet.md; whisper/scripts/cases.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>Lazard comparison (CCGT capex, O&amp;M, heat rate)</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>Lazard LCOE v19 (June 2026) as cited in the GAIR workbook</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>mid_merit_gas_rates.xlsx, O&amp;M Rebasing tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>First Gen historical O&amp;M (Santa Rita / San Lorenzo 1996 PPA, re-based May 2026)</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>ERC Case No. 2004-74 PPA rates, CPI re-basing</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>mid_merit_gas_rates.xlsx, O&amp;M Rebasing tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>Existing-plant capital cost US$450/kW; brownfield US$600/kW (San Gabriel, EERI)</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>GAIR workbook / cheat sheet</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>mid_merit_gas_rates.xlsx; cheat sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>Financing: 70:30, Kd 8%, 15-yr tenor, Re 14%</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>Draft Resolution 2 (Annex A.9–A.12)</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>cheat sheet; whisper/scripts/engine.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>Logistics caps (CLLC)</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>Draft Resolution 2 caps; BOG removed per working Rules Sec. 17</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>cases.py; franz_som_working draft_1.docx</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>PhP/US$ 62.756</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>BSP reference rate, 25 Sep 2026</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>whisper/scripts/cases.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>Taxes (CIT 25%, VAT 12%, RPT 2%, LBT 1%, WHT, GRT, DST)</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>CREATE Act (RA 11534), NIRC, LGC — model defaults</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>whisper/ERC Mid-Merit Financial Model.xlsm (Sensitivity Analysis)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>ER 1-94 PhP 0.03/kWh</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>DOE DC2025-10-0023; GAIR 8.8.3</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>naruto C90</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>Model template</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>naruto.xlsm (blank ERC Mid-Merit Financial Model)</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>GAIR RCM/whisper/naruto.xlsm</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>Capital cost (working assumption, 20 Oct 2026, market +25%): existing CCGT US$600/kW; new CCGT US$1,500/kW, gas engine US$1,375/kW, OCGT US$875/kW</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>Market-level working values raised 20 Oct 2026 (+25%, EPC and turbine cost inflation), in response to Wärtsilä and Quezon Power comments (GAIR matrix rows 119, 412); to be sourced in the Reference Parameters Resolution</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>models Fin42/Fin90, cell O34</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>